--- a/data/comision_chofer.xlsx
+++ b/data/comision_chofer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882B5BD0-FEDF-4908-9882-5F3C97F40635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C175DB8E-E49D-4938-B78B-610EC1903CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="173">
   <si>
     <t>codigo</t>
   </si>
@@ -70,6 +70,485 @@
   </si>
   <si>
     <t>reparto</t>
+  </si>
+  <si>
+    <t>CAMINO DE LAS SIERRAS S.A</t>
+  </si>
+  <si>
+    <t>4210304</t>
+  </si>
+  <si>
+    <t>Peajes</t>
+  </si>
+  <si>
+    <t>NOX000100011141</t>
+  </si>
+  <si>
+    <t>seba</t>
+  </si>
+  <si>
+    <t>Costo de Distribucion</t>
+  </si>
+  <si>
+    <t>COMPUTACION IDEA SRL</t>
+  </si>
+  <si>
+    <t>4210701</t>
+  </si>
+  <si>
+    <t>Licencias de software</t>
+  </si>
+  <si>
+    <t>FCA000100012048</t>
+  </si>
+  <si>
+    <t>abono gescom</t>
+  </si>
+  <si>
+    <t>Costo de Infraestructura</t>
+  </si>
+  <si>
+    <t>D Y L SRL</t>
+  </si>
+  <si>
+    <t>4211806</t>
+  </si>
+  <si>
+    <t>Insumos de limpieza</t>
+  </si>
+  <si>
+    <t>FCA000600001544</t>
+  </si>
+  <si>
+    <t>ART LIMPIEZA</t>
+  </si>
+  <si>
+    <t>Costo de Operaciones</t>
+  </si>
+  <si>
+    <t>ESTACION FERREYRA S.R.L.</t>
+  </si>
+  <si>
+    <t>4211201</t>
+  </si>
+  <si>
+    <t>Combustibles</t>
+  </si>
+  <si>
+    <t>FCA003700042482</t>
+  </si>
+  <si>
+    <t>GVM984</t>
+  </si>
+  <si>
+    <t>VARIOS</t>
+  </si>
+  <si>
+    <t>4211805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros </t>
+  </si>
+  <si>
+    <t>NOX000100011064</t>
+  </si>
+  <si>
+    <t>insumo computacion- pepe</t>
+  </si>
+  <si>
+    <t>Costo Administrativo</t>
+  </si>
+  <si>
+    <t>Muni Inspeccion Sanitaria</t>
+  </si>
+  <si>
+    <t>4211410</t>
+  </si>
+  <si>
+    <t>Bromatología, SENASA, ITV, RTO</t>
+  </si>
+  <si>
+    <t>NOX000100011106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       229 </t>
+  </si>
+  <si>
+    <t>NILDO SANTIN LOPEZ SA</t>
+  </si>
+  <si>
+    <t>FCA003700001686</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>FCA003700001741</t>
+  </si>
+  <si>
+    <t>SEBASTIAN</t>
+  </si>
+  <si>
+    <t>FCA003700001806</t>
+  </si>
+  <si>
+    <t>ESER S A</t>
+  </si>
+  <si>
+    <t>FCA003600064456</t>
+  </si>
+  <si>
+    <t>santiago</t>
+  </si>
+  <si>
+    <t>OKINET SRL</t>
+  </si>
+  <si>
+    <t>4210904</t>
+  </si>
+  <si>
+    <t>Alquileres de Impresoras</t>
+  </si>
+  <si>
+    <t>NOX000100011140</t>
+  </si>
+  <si>
+    <t>impresoras</t>
+  </si>
+  <si>
+    <t>MASEFER S.R.L.</t>
+  </si>
+  <si>
+    <t>4210204</t>
+  </si>
+  <si>
+    <t>Ropa de trabajo</t>
+  </si>
+  <si>
+    <t>NOX000100011095</t>
+  </si>
+  <si>
+    <t>zapatos gimmena vendedora</t>
+  </si>
+  <si>
+    <t>JFS POWER S.A.S.</t>
+  </si>
+  <si>
+    <t>4211102</t>
+  </si>
+  <si>
+    <t>Reparación y Mantenimiento de Rodados</t>
+  </si>
+  <si>
+    <t>FCA000200002751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       202 CAM 2 MARTES</t>
+  </si>
+  <si>
+    <t>ab451 camion 16_x000D_
+service completo</t>
+  </si>
+  <si>
+    <t>YPF SOCIEDAD ANONIMA</t>
+  </si>
+  <si>
+    <t>FCA142000234113</t>
+  </si>
+  <si>
+    <t>COMBUSTIBLE FLETEROS_x000D_
+16/6 AL 30/6</t>
+  </si>
+  <si>
+    <t>GONZALEZ CECILIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>4210602</t>
+  </si>
+  <si>
+    <t>Personal Tercerizado</t>
+  </si>
+  <si>
+    <t>NOX000100011031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       131 </t>
+  </si>
+  <si>
+    <t>NOX000100011104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       221 CAM 21 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       340 </t>
+  </si>
+  <si>
+    <t>BELEN EMILIANO AGUSTIN</t>
+  </si>
+  <si>
+    <t>NOX000100011037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       132 </t>
+  </si>
+  <si>
+    <t>NOX000100011112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       222 CAM 22 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       332 </t>
+  </si>
+  <si>
+    <t>GUIRAO LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t>NOX000100011113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       133 </t>
+  </si>
+  <si>
+    <t>NOX000100011109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       223 CAM 23 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       333 </t>
+  </si>
+  <si>
+    <t>NOX000100011135</t>
+  </si>
+  <si>
+    <t>JUNCOS LUIS EZEQUIEL</t>
+  </si>
+  <si>
+    <t>NOX000100011043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       134 </t>
+  </si>
+  <si>
+    <t>NOX000100011136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       334 </t>
+  </si>
+  <si>
+    <t>ROMANO RODRIGO ERNESTO</t>
+  </si>
+  <si>
+    <t>NOX000100011033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       135 </t>
+  </si>
+  <si>
+    <t>NOX000100011034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       135  com de cam 505</t>
+  </si>
+  <si>
+    <t>camion 505</t>
+  </si>
+  <si>
+    <t>NOX000100011128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       335 </t>
+  </si>
+  <si>
+    <t>IRIARTE MAURO ALEJANDRO</t>
+  </si>
+  <si>
+    <t>NOX000100011038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       136 </t>
+  </si>
+  <si>
+    <t>NOX000100011110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       226 </t>
+  </si>
+  <si>
+    <t>CANELO PABLO FERNANDO</t>
+  </si>
+  <si>
+    <t>NOX000100011041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       137 </t>
+  </si>
+  <si>
+    <t>NOX000100011111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       227 </t>
+  </si>
+  <si>
+    <t>NOX000100011137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       337 </t>
+  </si>
+  <si>
+    <t>NIETO GUSTAVO ATILIO</t>
+  </si>
+  <si>
+    <t>NOX000100011039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       138 </t>
+  </si>
+  <si>
+    <t>GUEVARA ENRIQUE LEONARDO</t>
+  </si>
+  <si>
+    <t>NOX000100011102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       139 </t>
+  </si>
+  <si>
+    <t>NOX000100011105</t>
+  </si>
+  <si>
+    <t>PALLOTI DUILIO</t>
+  </si>
+  <si>
+    <t>NOX000100011040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       140 </t>
+  </si>
+  <si>
+    <t>NOX000100011103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       230 </t>
+  </si>
+  <si>
+    <t>NOC000100011127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       331 </t>
+  </si>
+  <si>
+    <t>ROMANO MARTIN</t>
+  </si>
+  <si>
+    <t>NOX000100011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       213 CAM 13 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       314 CAM 14 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>ADRIAN ISMAEL TALAVERA</t>
+  </si>
+  <si>
+    <t>NOX000100011107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       212 CAM 12 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       308 CAM 8 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>REFRIGUERIO VTAS</t>
+  </si>
+  <si>
+    <t>4210206</t>
+  </si>
+  <si>
+    <t>Atenciones al personal, almuerzos y alimentos</t>
+  </si>
+  <si>
+    <t>NOX000100011101</t>
+  </si>
+  <si>
+    <t>COMIDA MAXI-NICO-GUS</t>
+  </si>
+  <si>
+    <t>Costo de Ventas y Promocion</t>
+  </si>
+  <si>
+    <t>NOX000100011097</t>
+  </si>
+  <si>
+    <t>COMIDA GUS-AGUS</t>
+  </si>
+  <si>
+    <t>NOX000100011125</t>
+  </si>
+  <si>
+    <t>comida maxi-nico</t>
+  </si>
+  <si>
+    <t>NOX000100011142</t>
+  </si>
+  <si>
+    <t>COMIDA GUS-NICO</t>
+  </si>
+  <si>
+    <t>SANTA ALBINA S A</t>
+  </si>
+  <si>
+    <t>FCA002000081668</t>
+  </si>
+  <si>
+    <t>depo</t>
+  </si>
+  <si>
+    <t>VIATICOS VENDEDORES</t>
+  </si>
+  <si>
+    <t>4210301</t>
+  </si>
+  <si>
+    <t>Movilidad y viáticos</t>
+  </si>
+  <si>
+    <t>NOX000100011098</t>
+  </si>
+  <si>
+    <t>CLAUDIO</t>
+  </si>
+  <si>
+    <t>NOX000100011099</t>
+  </si>
+  <si>
+    <t>GASTOS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>NOX000100011138</t>
+  </si>
+  <si>
+    <t>claudio</t>
   </si>
 </sst>
 </file>
@@ -442,202 +921,1988 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E2" s="2"/>
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2">
+        <v>6000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
+        <v>6000</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E3" s="2"/>
+      <c r="A3">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3">
+        <v>767314.05</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3">
+        <v>634143.85</v>
+      </c>
+      <c r="K3">
+        <v>133170.20000000001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E4" s="2"/>
+      <c r="A4">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4">
+        <v>75979.990000000005</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>62793.38</v>
+      </c>
+      <c r="K4">
+        <v>13186.61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E5" s="2"/>
+      <c r="A5">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>60000.05</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5">
+        <v>50602.63</v>
+      </c>
+      <c r="K5">
+        <v>9397.42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E6" s="2"/>
+      <c r="A6">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6">
+        <v>150500</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6">
+        <v>150500</v>
+      </c>
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E7" s="2"/>
+      <c r="A7">
+        <v>135</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7">
+        <v>8500</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>8500</v>
+      </c>
+      <c r="L7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <v>9881</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E8" s="2"/>
+      <c r="A8">
+        <v>138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8">
+        <v>75007.92</v>
+      </c>
+      <c r="I8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8">
+        <v>63994.78</v>
+      </c>
+      <c r="K8">
+        <v>11013.14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E9" s="2"/>
+      <c r="A9">
+        <v>138</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9">
+        <v>79999.89</v>
+      </c>
+      <c r="I9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9">
+        <v>68253.8</v>
+      </c>
+      <c r="K9">
+        <v>11746.09</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E10" s="2"/>
+      <c r="A10">
+        <v>138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>75001.08</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10">
+        <v>64086.95</v>
+      </c>
+      <c r="K10">
+        <v>10914.13</v>
+      </c>
+      <c r="L10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E11" s="2"/>
+      <c r="A11">
+        <v>153</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>84997.96</v>
+      </c>
+      <c r="I11" t="s">
+        <v>56</v>
+      </c>
+      <c r="J11">
+        <v>72566.28</v>
+      </c>
+      <c r="K11">
+        <v>12431.68</v>
+      </c>
+      <c r="L11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E12" s="2"/>
+      <c r="A12">
+        <v>167</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>625500.88</v>
+      </c>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12">
+        <v>625500.88</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E15" s="2"/>
+      <c r="A13">
+        <v>185</v>
+      </c>
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>30375</v>
+      </c>
+      <c r="I13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13">
+        <v>30375</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>198</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14">
+        <v>220000</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14">
+        <v>181818.18</v>
+      </c>
+      <c r="K14">
+        <v>38181.82</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14">
+        <v>5</v>
+      </c>
+      <c r="N14">
+        <v>9861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>224</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15">
+        <v>2825176.63</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15">
+        <v>2398725.63</v>
+      </c>
+      <c r="K15">
+        <v>426451</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="5:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="2"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E20" s="2"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E21" s="2"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="5:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E31" s="2"/>
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" spans="5:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E32" s="2"/>
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E33" s="2"/>
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E34" s="2"/>
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="5:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E39" s="2"/>
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E40" s="2"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E41" s="2"/>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>251</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16">
+        <v>72191</v>
+      </c>
+      <c r="H16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16">
+        <v>72191</v>
+      </c>
+      <c r="L16" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16">
+        <v>4</v>
+      </c>
+      <c r="N16">
+        <v>9844</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>251</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17">
+        <v>155305</v>
+      </c>
+      <c r="H17" t="s">
+        <v>82</v>
+      </c>
+      <c r="J17">
+        <v>155305</v>
+      </c>
+      <c r="L17" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17">
+        <v>4</v>
+      </c>
+      <c r="N17">
+        <v>9873</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>251</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18">
+        <v>84980</v>
+      </c>
+      <c r="H18" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18">
+        <v>84980</v>
+      </c>
+      <c r="L18" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18">
+        <v>4</v>
+      </c>
+      <c r="N18">
+        <v>9906</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>252</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F19" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19">
+        <v>173490</v>
+      </c>
+      <c r="H19" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19">
+        <v>173490</v>
+      </c>
+      <c r="L19" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19">
+        <v>4</v>
+      </c>
+      <c r="N19">
+        <v>9845</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>252</v>
+      </c>
+      <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20">
+        <v>94200</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J20">
+        <v>94200</v>
+      </c>
+      <c r="L20" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20">
+        <v>4</v>
+      </c>
+      <c r="N20">
+        <v>9874</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>252</v>
+      </c>
+      <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21">
+        <v>100000</v>
+      </c>
+      <c r="H21" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21">
+        <v>100000</v>
+      </c>
+      <c r="L21" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21">
+        <v>4</v>
+      </c>
+      <c r="N21">
+        <v>9898</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>253</v>
+      </c>
+      <c r="B22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22">
+        <v>193540</v>
+      </c>
+      <c r="H22" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22">
+        <v>193540</v>
+      </c>
+      <c r="L22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
+      </c>
+      <c r="N22">
+        <v>9846</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>253</v>
+      </c>
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23">
+        <v>102000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23">
+        <v>102000</v>
+      </c>
+      <c r="L23" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>9875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>253</v>
+      </c>
+      <c r="B24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24">
+        <v>110000</v>
+      </c>
+      <c r="H24" t="s">
+        <v>98</v>
+      </c>
+      <c r="J24">
+        <v>110000</v>
+      </c>
+      <c r="L24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>9899</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>253</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25">
+        <v>40000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25">
+        <v>40000</v>
+      </c>
+      <c r="L25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25">
+        <v>4</v>
+      </c>
+      <c r="N25">
+        <v>9899</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>254</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F26" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26">
+        <v>109236</v>
+      </c>
+      <c r="H26" t="s">
+        <v>102</v>
+      </c>
+      <c r="J26">
+        <v>109236</v>
+      </c>
+      <c r="L26" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>9847</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>254</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F27" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27">
+        <v>102615</v>
+      </c>
+      <c r="H27" t="s">
+        <v>104</v>
+      </c>
+      <c r="J27">
+        <v>102615</v>
+      </c>
+      <c r="L27" t="s">
+        <v>31</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>255</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28">
+        <v>97466</v>
+      </c>
+      <c r="H28" t="s">
+        <v>107</v>
+      </c>
+      <c r="J28">
+        <v>97466</v>
+      </c>
+      <c r="L28" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28">
+        <v>4</v>
+      </c>
+      <c r="N28">
+        <v>9848</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>255</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29">
+        <v>259855</v>
+      </c>
+      <c r="H29" t="s">
+        <v>109</v>
+      </c>
+      <c r="I29" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29">
+        <v>259855</v>
+      </c>
+      <c r="L29" t="s">
+        <v>31</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
+      </c>
+      <c r="N29">
+        <v>9848</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>255</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30">
+        <v>86962</v>
+      </c>
+      <c r="H30" t="s">
+        <v>112</v>
+      </c>
+      <c r="J30">
+        <v>86962</v>
+      </c>
+      <c r="L30" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30">
+        <v>4</v>
+      </c>
+      <c r="N30">
+        <v>9901</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>256</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31">
+        <v>82590.84</v>
+      </c>
+      <c r="H31" t="s">
+        <v>115</v>
+      </c>
+      <c r="J31">
+        <v>82590.84</v>
+      </c>
+      <c r="L31" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>9849</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>256</v>
+      </c>
+      <c r="B32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32">
+        <v>92865</v>
+      </c>
+      <c r="H32" t="s">
+        <v>117</v>
+      </c>
+      <c r="J32">
+        <v>92865</v>
+      </c>
+      <c r="L32" t="s">
+        <v>31</v>
+      </c>
+      <c r="M32">
+        <v>4</v>
+      </c>
+      <c r="N32">
+        <v>9878</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>257</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33">
+        <v>68486</v>
+      </c>
+      <c r="H33" t="s">
+        <v>120</v>
+      </c>
+      <c r="J33">
+        <v>68486</v>
+      </c>
+      <c r="L33" t="s">
+        <v>31</v>
+      </c>
+      <c r="M33">
+        <v>4</v>
+      </c>
+      <c r="N33">
+        <v>9850</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>257</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F34" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34">
+        <v>107325</v>
+      </c>
+      <c r="H34" t="s">
+        <v>122</v>
+      </c>
+      <c r="J34">
+        <v>107325</v>
+      </c>
+      <c r="L34" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <v>9879</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>257</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F35" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35">
+        <v>132990</v>
+      </c>
+      <c r="H35" t="s">
+        <v>124</v>
+      </c>
+      <c r="J35">
+        <v>132990</v>
+      </c>
+      <c r="L35" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35">
+        <v>4</v>
+      </c>
+      <c r="N35">
+        <v>9903</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>258</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F36" t="s">
+        <v>126</v>
+      </c>
+      <c r="G36">
+        <v>160093.70000000001</v>
+      </c>
+      <c r="H36" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36">
+        <v>160093.70000000001</v>
+      </c>
+      <c r="L36" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36">
+        <v>4</v>
+      </c>
+      <c r="N36">
+        <v>9851</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>259</v>
+      </c>
+      <c r="B37" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F37" t="s">
+        <v>129</v>
+      </c>
+      <c r="G37">
+        <v>46583</v>
+      </c>
+      <c r="H37" t="s">
+        <v>130</v>
+      </c>
+      <c r="J37">
+        <v>46583</v>
+      </c>
+      <c r="L37" t="s">
+        <v>31</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+      <c r="N37">
+        <v>9852</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>259</v>
+      </c>
+      <c r="B38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F38" t="s">
+        <v>131</v>
+      </c>
+      <c r="G38">
+        <v>86257</v>
+      </c>
+      <c r="H38" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38">
+        <v>86257</v>
+      </c>
+      <c r="L38" t="s">
+        <v>31</v>
+      </c>
+      <c r="M38">
+        <v>4</v>
+      </c>
+      <c r="N38">
+        <v>9881</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>260</v>
+      </c>
+      <c r="B39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G39">
+        <v>42800</v>
+      </c>
+      <c r="H39" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39">
+        <v>42800</v>
+      </c>
+      <c r="L39" t="s">
+        <v>31</v>
+      </c>
+      <c r="M39">
+        <v>4</v>
+      </c>
+      <c r="N39">
+        <v>9853</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>260</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F40" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40">
+        <v>180500</v>
+      </c>
+      <c r="H40" t="s">
+        <v>136</v>
+      </c>
+      <c r="J40">
+        <v>180500</v>
+      </c>
+      <c r="L40" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40">
+        <v>4</v>
+      </c>
+      <c r="N40">
+        <v>9882</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>260</v>
+      </c>
+      <c r="B41" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F41" t="s">
+        <v>137</v>
+      </c>
+      <c r="G41">
+        <v>158000</v>
+      </c>
+      <c r="H41" t="s">
+        <v>138</v>
+      </c>
+      <c r="J41">
+        <v>158000</v>
+      </c>
+      <c r="L41" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41">
+        <v>4</v>
+      </c>
+      <c r="N41">
+        <v>9897</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>261</v>
+      </c>
+      <c r="B42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F42" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42">
+        <v>75000</v>
+      </c>
+      <c r="H42" t="s">
+        <v>141</v>
+      </c>
+      <c r="J42">
+        <v>75000</v>
+      </c>
+      <c r="L42" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42">
+        <v>4</v>
+      </c>
+      <c r="N42">
+        <v>9871</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>261</v>
+      </c>
+      <c r="B43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F43" t="s">
+        <v>142</v>
+      </c>
+      <c r="G43">
+        <v>75000</v>
+      </c>
+      <c r="H43" t="s">
+        <v>143</v>
+      </c>
+      <c r="J43">
+        <v>75000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+      <c r="N43">
+        <v>9895</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>262</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G44">
+        <v>232872</v>
+      </c>
+      <c r="H44" t="s">
+        <v>146</v>
+      </c>
+      <c r="J44">
+        <v>232872</v>
+      </c>
+      <c r="L44" t="s">
+        <v>31</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="N44">
+        <v>9870</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>262</v>
+      </c>
+      <c r="B45" t="s">
+        <v>144</v>
+      </c>
+      <c r="C45" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F45" t="s">
+        <v>147</v>
+      </c>
+      <c r="G45">
+        <v>170304</v>
+      </c>
+      <c r="H45" t="s">
+        <v>148</v>
+      </c>
+      <c r="J45">
+        <v>170304</v>
+      </c>
+      <c r="L45" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+      <c r="N45">
+        <v>9891</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>355</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46202</v>
+      </c>
+      <c r="F46" t="s">
+        <v>152</v>
+      </c>
+      <c r="G46">
+        <v>30500</v>
+      </c>
+      <c r="I46" t="s">
+        <v>153</v>
+      </c>
+      <c r="J46">
+        <v>30500</v>
+      </c>
+      <c r="L46" t="s">
+        <v>154</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>355</v>
+      </c>
+      <c r="B47" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F47" t="s">
+        <v>155</v>
+      </c>
+      <c r="G47">
+        <v>21000</v>
+      </c>
+      <c r="I47" t="s">
+        <v>156</v>
+      </c>
+      <c r="J47">
+        <v>21000</v>
+      </c>
+      <c r="L47" t="s">
+        <v>154</v>
+      </c>
+      <c r="M47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>355</v>
+      </c>
+      <c r="B48" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F48" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48">
+        <v>18000</v>
+      </c>
+      <c r="I48" t="s">
+        <v>158</v>
+      </c>
+      <c r="J48">
+        <v>18000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>154</v>
+      </c>
+      <c r="M48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>355</v>
+      </c>
+      <c r="B49" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" t="s">
+        <v>151</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F49" t="s">
+        <v>159</v>
+      </c>
+      <c r="G49">
+        <v>22500</v>
+      </c>
+      <c r="I49" t="s">
+        <v>160</v>
+      </c>
+      <c r="J49">
+        <v>22500</v>
+      </c>
+      <c r="L49" t="s">
+        <v>154</v>
+      </c>
+      <c r="M49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>370</v>
+      </c>
+      <c r="B50" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F50" t="s">
+        <v>162</v>
+      </c>
+      <c r="G50">
+        <v>50000.12</v>
+      </c>
+      <c r="I50" t="s">
+        <v>163</v>
+      </c>
+      <c r="J50">
+        <v>42659.02</v>
+      </c>
+      <c r="K50">
+        <v>7341.1</v>
+      </c>
+      <c r="L50" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>396</v>
+      </c>
+      <c r="B51" t="s">
+        <v>164</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F51" t="s">
+        <v>167</v>
+      </c>
+      <c r="G51">
+        <v>73800</v>
+      </c>
+      <c r="I51" t="s">
+        <v>168</v>
+      </c>
+      <c r="J51">
+        <v>73800</v>
+      </c>
+      <c r="L51" t="s">
+        <v>154</v>
+      </c>
+      <c r="M51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>396</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s">
+        <v>165</v>
+      </c>
+      <c r="D52" t="s">
+        <v>166</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46203</v>
+      </c>
+      <c r="F52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52">
+        <v>64300</v>
+      </c>
+      <c r="I52" t="s">
+        <v>170</v>
+      </c>
+      <c r="J52">
+        <v>64300</v>
+      </c>
+      <c r="L52" t="s">
+        <v>154</v>
+      </c>
+      <c r="M52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>396</v>
+      </c>
+      <c r="B53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F53" t="s">
+        <v>171</v>
+      </c>
+      <c r="G53">
+        <v>98000</v>
+      </c>
+      <c r="I53" t="s">
+        <v>172</v>
+      </c>
+      <c r="J53">
+        <v>98000</v>
+      </c>
+      <c r="L53" t="s">
+        <v>154</v>
+      </c>
+      <c r="M53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="5:5" x14ac:dyDescent="0.25">

--- a/data/comision_chofer.xlsx
+++ b/data/comision_chofer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C175DB8E-E49D-4938-B78B-610EC1903CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231B4E9D-C379-4B25-9ABD-A96E71C2D58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="131">
   <si>
     <t>codigo</t>
   </si>
@@ -75,9 +75,6 @@
     <t>CAMINO DE LAS SIERRAS S.A</t>
   </si>
   <si>
-    <t>4210304</t>
-  </si>
-  <si>
     <t>Peajes</t>
   </si>
   <si>
@@ -93,9 +90,6 @@
     <t>COMPUTACION IDEA SRL</t>
   </si>
   <si>
-    <t>4210701</t>
-  </si>
-  <si>
     <t>Licencias de software</t>
   </si>
   <si>
@@ -108,87 +102,18 @@
     <t>Costo de Infraestructura</t>
   </si>
   <si>
-    <t>D Y L SRL</t>
-  </si>
-  <si>
-    <t>4211806</t>
-  </si>
-  <si>
-    <t>Insumos de limpieza</t>
-  </si>
-  <si>
-    <t>FCA000600001544</t>
-  </si>
-  <si>
-    <t>ART LIMPIEZA</t>
-  </si>
-  <si>
     <t>Costo de Operaciones</t>
   </si>
   <si>
-    <t>ESTACION FERREYRA S.R.L.</t>
-  </si>
-  <si>
-    <t>4211201</t>
-  </si>
-  <si>
     <t>Combustibles</t>
   </si>
   <si>
-    <t>FCA003700042482</t>
-  </si>
-  <si>
-    <t>GVM984</t>
-  </si>
-  <si>
-    <t>VARIOS</t>
-  </si>
-  <si>
-    <t>4211805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Otros </t>
-  </si>
-  <si>
-    <t>NOX000100011064</t>
-  </si>
-  <si>
-    <t>insumo computacion- pepe</t>
-  </si>
-  <si>
-    <t>Costo Administrativo</t>
-  </si>
-  <si>
-    <t>Muni Inspeccion Sanitaria</t>
-  </si>
-  <si>
-    <t>4211410</t>
-  </si>
-  <si>
-    <t>Bromatología, SENASA, ITV, RTO</t>
-  </si>
-  <si>
-    <t>NOX000100011106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       229 </t>
-  </si>
-  <si>
     <t>NILDO SANTIN LOPEZ SA</t>
   </si>
   <si>
-    <t>FCA003700001686</t>
-  </si>
-  <si>
     <t>NATALIA</t>
   </si>
   <si>
-    <t>FCA003700001741</t>
-  </si>
-  <si>
-    <t>SEBASTIAN</t>
-  </si>
-  <si>
     <t>FCA003700001806</t>
   </si>
   <si>
@@ -204,9 +129,6 @@
     <t>OKINET SRL</t>
   </si>
   <si>
-    <t>4210904</t>
-  </si>
-  <si>
     <t>Alquileres de Impresoras</t>
   </si>
   <si>
@@ -216,38 +138,7 @@
     <t>impresoras</t>
   </si>
   <si>
-    <t>MASEFER S.R.L.</t>
-  </si>
-  <si>
-    <t>4210204</t>
-  </si>
-  <si>
-    <t>Ropa de trabajo</t>
-  </si>
-  <si>
-    <t>NOX000100011095</t>
-  </si>
-  <si>
-    <t>zapatos gimmena vendedora</t>
-  </si>
-  <si>
-    <t>JFS POWER S.A.S.</t>
-  </si>
-  <si>
-    <t>4211102</t>
-  </si>
-  <si>
-    <t>Reparación y Mantenimiento de Rodados</t>
-  </si>
-  <si>
-    <t>FCA000200002751</t>
-  </si>
-  <si>
     <t xml:space="preserve">       202 CAM 2 MARTES</t>
-  </si>
-  <si>
-    <t>ab451 camion 16_x000D_
-service completo</t>
   </si>
   <si>
     <t>YPF SOCIEDAD ANONIMA</t>
@@ -263,198 +154,63 @@
     <t>GONZALEZ CECILIA GUADALUPE</t>
   </si>
   <si>
-    <t>4210602</t>
-  </si>
-  <si>
     <t>Personal Tercerizado</t>
   </si>
   <si>
-    <t>NOX000100011031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       131 </t>
-  </si>
-  <si>
-    <t>NOX000100011104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       221 CAM 21 MARTES</t>
-  </si>
-  <si>
     <t>NOX000100011126</t>
   </si>
   <si>
-    <t xml:space="preserve">       340 </t>
-  </si>
-  <si>
     <t>BELEN EMILIANO AGUSTIN</t>
   </si>
   <si>
-    <t>NOX000100011037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       132 </t>
-  </si>
-  <si>
-    <t>NOX000100011112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       222 CAM 22 MARTES</t>
-  </si>
-  <si>
     <t>NOX000100011139</t>
   </si>
   <si>
-    <t xml:space="preserve">       332 </t>
-  </si>
-  <si>
     <t>GUIRAO LUIS ANTONIO</t>
   </si>
   <si>
-    <t>NOX000100011113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       133 </t>
-  </si>
-  <si>
-    <t>NOX000100011109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       223 CAM 23 MARTES</t>
-  </si>
-  <si>
     <t>NOX000100011134</t>
   </si>
   <si>
-    <t xml:space="preserve">       333 </t>
-  </si>
-  <si>
     <t>NOX000100011135</t>
   </si>
   <si>
     <t>JUNCOS LUIS EZEQUIEL</t>
   </si>
   <si>
-    <t>NOX000100011043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       134 </t>
-  </si>
-  <si>
     <t>NOX000100011136</t>
   </si>
   <si>
-    <t xml:space="preserve">       334 </t>
-  </si>
-  <si>
     <t>ROMANO RODRIGO ERNESTO</t>
   </si>
   <si>
-    <t>NOX000100011033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       135 </t>
-  </si>
-  <si>
-    <t>NOX000100011034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       135  com de cam 505</t>
-  </si>
-  <si>
-    <t>camion 505</t>
-  </si>
-  <si>
     <t>NOX000100011128</t>
   </si>
   <si>
-    <t xml:space="preserve">       335 </t>
-  </si>
-  <si>
     <t>IRIARTE MAURO ALEJANDRO</t>
   </si>
   <si>
-    <t>NOX000100011038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       136 </t>
-  </si>
-  <si>
-    <t>NOX000100011110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       226 </t>
-  </si>
-  <si>
     <t>CANELO PABLO FERNANDO</t>
   </si>
   <si>
-    <t>NOX000100011041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       137 </t>
-  </si>
-  <si>
-    <t>NOX000100011111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       227 </t>
-  </si>
-  <si>
     <t>NOX000100011137</t>
   </si>
   <si>
-    <t xml:space="preserve">       337 </t>
-  </si>
-  <si>
     <t>NIETO GUSTAVO ATILIO</t>
   </si>
   <si>
-    <t>NOX000100011039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       138 </t>
-  </si>
-  <si>
     <t>GUEVARA ENRIQUE LEONARDO</t>
   </si>
   <si>
-    <t>NOX000100011102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       139 </t>
-  </si>
-  <si>
-    <t>NOX000100011105</t>
-  </si>
-  <si>
     <t>PALLOTI DUILIO</t>
   </si>
   <si>
-    <t>NOX000100011040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       140 </t>
-  </si>
-  <si>
-    <t>NOX000100011103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       230 </t>
-  </si>
-  <si>
     <t>NOC000100011127</t>
   </si>
   <si>
-    <t xml:space="preserve">       331 </t>
-  </si>
-  <si>
     <t>ROMANO MARTIN</t>
   </si>
   <si>
-    <t>NOX000100011108</t>
-  </si>
-  <si>
     <t xml:space="preserve">       213 CAM 13 MARTES</t>
   </si>
   <si>
@@ -467,42 +223,15 @@
     <t>ADRIAN ISMAEL TALAVERA</t>
   </si>
   <si>
-    <t>NOX000100011107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       212 CAM 12 MARTES</t>
-  </si>
-  <si>
-    <t>NOX000100011132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">       308 CAM 8 MIÉRCOLES</t>
-  </si>
-  <si>
     <t>REFRIGUERIO VTAS</t>
   </si>
   <si>
-    <t>4210206</t>
-  </si>
-  <si>
     <t>Atenciones al personal, almuerzos y alimentos</t>
   </si>
   <si>
-    <t>NOX000100011101</t>
-  </si>
-  <si>
-    <t>COMIDA MAXI-NICO-GUS</t>
-  </si>
-  <si>
     <t>Costo de Ventas y Promocion</t>
   </si>
   <si>
-    <t>NOX000100011097</t>
-  </si>
-  <si>
-    <t>COMIDA GUS-AGUS</t>
-  </si>
-  <si>
     <t>NOX000100011125</t>
   </si>
   <si>
@@ -515,40 +244,186 @@
     <t>COMIDA GUS-NICO</t>
   </si>
   <si>
-    <t>SANTA ALBINA S A</t>
-  </si>
-  <si>
-    <t>FCA002000081668</t>
-  </si>
-  <si>
-    <t>depo</t>
-  </si>
-  <si>
     <t>VIATICOS VENDEDORES</t>
   </si>
   <si>
-    <t>4210301</t>
-  </si>
-  <si>
     <t>Movilidad y viáticos</t>
   </si>
   <si>
-    <t>NOX000100011098</t>
-  </si>
-  <si>
     <t>CLAUDIO</t>
   </si>
   <si>
-    <t>NOX000100011099</t>
-  </si>
-  <si>
-    <t>GASTOS ALEJANDRO</t>
-  </si>
-  <si>
     <t>NOX000100011138</t>
   </si>
   <si>
     <t>claudio</t>
+  </si>
+  <si>
+    <t>NOX000100011153</t>
+  </si>
+  <si>
+    <t>NOX000100011177</t>
+  </si>
+  <si>
+    <t>NOX000100011191</t>
+  </si>
+  <si>
+    <t>NOX000100011166</t>
+  </si>
+  <si>
+    <t>NOX000100011178</t>
+  </si>
+  <si>
+    <t>NOX000100011190</t>
+  </si>
+  <si>
+    <t>NOX000100011162</t>
+  </si>
+  <si>
+    <t>NOX000100011179</t>
+  </si>
+  <si>
+    <t>NOX000100011180</t>
+  </si>
+  <si>
+    <t>NOX000100011160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       109 CAM 9 LUNES</t>
+  </si>
+  <si>
+    <t>NOX000100011176</t>
+  </si>
+  <si>
+    <t>NOX000100011170</t>
+  </si>
+  <si>
+    <t>NOX000100011183</t>
+  </si>
+  <si>
+    <t>NOX000100011167</t>
+  </si>
+  <si>
+    <t>NOX000100011169</t>
+  </si>
+  <si>
+    <t>NOX000100011175</t>
+  </si>
+  <si>
+    <t>NOX000100011185</t>
+  </si>
+  <si>
+    <t>NOX000100011163</t>
+  </si>
+  <si>
+    <t>NOX000100011174</t>
+  </si>
+  <si>
+    <t>NOX000100011168</t>
+  </si>
+  <si>
+    <t>NOX000100011164</t>
+  </si>
+  <si>
+    <t>NOX000100011189</t>
+  </si>
+  <si>
+    <t>NOX000100011165</t>
+  </si>
+  <si>
+    <t>NOX000100011187</t>
+  </si>
+  <si>
+    <t>NOX000100011186</t>
+  </si>
+  <si>
+    <t>NOX000100011154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       500 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>NOX000100011155</t>
+  </si>
+  <si>
+    <t>NOX000100011156</t>
+  </si>
+  <si>
+    <t>DIO EL OK FRANCO</t>
+  </si>
+  <si>
+    <t>NOX000100011173</t>
+  </si>
+  <si>
+    <t>NOX000100011184</t>
+  </si>
+  <si>
+    <t>NOX000100011161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       110 CAM 10 LUNES</t>
+  </si>
+  <si>
+    <t>NOX000100011172</t>
+  </si>
+  <si>
+    <t>NOX000100011188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       316 CAM 16 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       108 CAM 8 LUNES</t>
+  </si>
+  <si>
+    <t>NOX000100011171</t>
+  </si>
+  <si>
+    <t>MARTIN RODRIGO ULLA LOPEZ</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>FCA100100006411</t>
+  </si>
+  <si>
+    <t>INTERNET DEDICADO</t>
+  </si>
+  <si>
+    <t>NOX000100011208</t>
+  </si>
+  <si>
+    <t>SUELDO EMPLEADOS</t>
+  </si>
+  <si>
+    <t>Sueldo Bruto</t>
+  </si>
+  <si>
+    <t>NOX000100011192</t>
+  </si>
+  <si>
+    <t>MITO</t>
+  </si>
+  <si>
+    <t>NOX000100011181</t>
+  </si>
+  <si>
+    <t>ssergio avendaño_x000D_
+dif agunaldo</t>
+  </si>
+  <si>
+    <t>NOX000100011182</t>
+  </si>
+  <si>
+    <t>GERMN BRIÑON_x000D_
+DIF AGUINLDO</t>
+  </si>
+  <si>
+    <t>NOX000100011205</t>
   </si>
 </sst>
 </file>
@@ -927,29 +802,29 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>4210304</v>
+      </c>
+      <c r="D2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
       </c>
       <c r="E2" s="2">
         <v>46205</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2">
         <v>6000</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>6000</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>5</v>
@@ -960,25 +835,25 @@
         <v>47</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3">
+        <v>4210701</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
       </c>
       <c r="E3" s="2">
         <v>46204</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G3">
         <v>767314.05</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J3">
         <v>634143.85</v>
@@ -987,7 +862,7 @@
         <v>133170.20000000001</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -995,75 +870,75 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4">
+        <v>4211201</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4">
+        <v>75001.08</v>
+      </c>
+      <c r="I4" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2">
-        <v>46203</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4">
-        <v>75979.990000000005</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
-      </c>
       <c r="J4">
-        <v>62793.38</v>
+        <v>64086.95</v>
       </c>
       <c r="K4">
-        <v>13186.61</v>
+        <v>10914.13</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>4211201</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>60000.05</v>
+        <v>84997.96</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J5">
-        <v>50602.63</v>
+        <v>72566.28</v>
       </c>
       <c r="K5">
-        <v>9397.42</v>
+        <v>12431.68</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1071,1028 +946,1027 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>4210904</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G6">
-        <v>150500</v>
+        <v>625500.88</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J6">
-        <v>150500</v>
+        <v>625500.88</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>4211201</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G7">
-        <v>8500</v>
-      </c>
-      <c r="H7" t="s">
-        <v>47</v>
+        <v>2825176.63</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="J7">
-        <v>8500</v>
+        <v>2398725.63</v>
+      </c>
+      <c r="K7">
+        <v>426451</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M7">
         <v>5</v>
       </c>
-      <c r="N7">
-        <v>9881</v>
-      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>138</v>
+        <v>251</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>4210602</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G8">
-        <v>75007.92</v>
-      </c>
-      <c r="I8" t="s">
-        <v>50</v>
+        <v>84980</v>
+      </c>
+      <c r="H8">
+        <v>340</v>
       </c>
       <c r="J8">
-        <v>63994.78</v>
-      </c>
-      <c r="K8">
-        <v>11013.14</v>
+        <v>84980</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>9906</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>138</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>4210602</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="G9">
-        <v>79999.89</v>
-      </c>
-      <c r="I9" t="s">
-        <v>52</v>
+        <v>97560</v>
+      </c>
+      <c r="H9">
+        <v>131</v>
       </c>
       <c r="J9">
-        <v>68253.8</v>
-      </c>
-      <c r="K9">
-        <v>11746.09</v>
+        <v>97560</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M9">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N9">
+        <v>9922</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>138</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="C10">
+        <v>4210602</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2">
         <v>46206</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G10">
-        <v>75001.08</v>
-      </c>
-      <c r="I10" t="s">
-        <v>50</v>
+        <v>175030</v>
+      </c>
+      <c r="H10">
+        <v>231</v>
       </c>
       <c r="J10">
-        <v>64086.95</v>
-      </c>
-      <c r="K10">
-        <v>10914.13</v>
+        <v>175030</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <v>9951</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>153</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
+        <v>40</v>
+      </c>
+      <c r="C11">
+        <v>4210602</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="G11">
-        <v>84997.96</v>
-      </c>
-      <c r="I11" t="s">
-        <v>56</v>
+        <v>80441</v>
+      </c>
+      <c r="H11">
+        <v>340</v>
       </c>
       <c r="J11">
-        <v>72566.28</v>
-      </c>
-      <c r="K11">
-        <v>12431.68</v>
+        <v>80441</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N11">
+        <v>9977</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>167</v>
+        <v>252</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>58</v>
+        <v>43</v>
+      </c>
+      <c r="C12">
+        <v>4210602</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G12">
-        <v>625500.88</v>
-      </c>
-      <c r="I12" t="s">
-        <v>61</v>
+        <v>100000</v>
+      </c>
+      <c r="H12">
+        <v>332</v>
       </c>
       <c r="J12">
-        <v>625500.88</v>
+        <v>100000</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="N12">
+        <v>9898</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>63</v>
+        <v>43</v>
+      </c>
+      <c r="C13">
+        <v>4210602</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G13">
-        <v>30375</v>
-      </c>
-      <c r="I13" t="s">
-        <v>66</v>
+        <v>141500</v>
+      </c>
+      <c r="H13">
+        <v>132</v>
       </c>
       <c r="J13">
-        <v>30375</v>
+        <v>141500</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="N13">
+        <v>9923</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="C14">
+        <v>4210602</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G14">
-        <v>220000</v>
-      </c>
-      <c r="H14" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>72</v>
-      </c>
+        <v>153917</v>
+      </c>
+      <c r="H14">
+        <v>232</v>
+      </c>
+      <c r="I14" s="1"/>
       <c r="J14">
-        <v>181818.18</v>
-      </c>
-      <c r="K14">
-        <v>38181.82</v>
+        <v>153917</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>9861</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+        <v>9952</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>4210602</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G15">
-        <v>2825176.63</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>75</v>
-      </c>
+        <v>52666</v>
+      </c>
+      <c r="H15">
+        <v>332</v>
+      </c>
+      <c r="I15" s="1"/>
       <c r="J15">
-        <v>2398725.63</v>
-      </c>
-      <c r="K15">
-        <v>426451</v>
+        <v>52666</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M15">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N15">
+        <v>9969</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="C16">
+        <v>4210602</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="G16">
-        <v>72191</v>
-      </c>
-      <c r="H16" t="s">
-        <v>80</v>
+        <v>110000</v>
+      </c>
+      <c r="H16">
+        <v>333</v>
       </c>
       <c r="J16">
-        <v>72191</v>
+        <v>110000</v>
       </c>
       <c r="L16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M16">
         <v>4</v>
       </c>
       <c r="N16">
-        <v>9844</v>
+        <v>9899</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="C17">
+        <v>4210602</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="G17">
-        <v>155305</v>
-      </c>
-      <c r="H17" t="s">
-        <v>82</v>
+        <v>40000</v>
+      </c>
+      <c r="H17">
+        <v>333</v>
       </c>
       <c r="J17">
-        <v>155305</v>
+        <v>40000</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
       <c r="N17">
-        <v>9873</v>
+        <v>9899</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="C18">
+        <v>4210602</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G18">
-        <v>84980</v>
-      </c>
-      <c r="H18" t="s">
-        <v>84</v>
+        <v>131000</v>
+      </c>
+      <c r="H18">
+        <v>133</v>
       </c>
       <c r="J18">
-        <v>84980</v>
+        <v>131000</v>
       </c>
       <c r="L18" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M18">
         <v>4</v>
       </c>
       <c r="N18">
-        <v>9906</v>
+        <v>9924</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="C19">
+        <v>4210602</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G19">
-        <v>173490</v>
-      </c>
-      <c r="H19" t="s">
-        <v>87</v>
+        <v>149000</v>
+      </c>
+      <c r="H19">
+        <v>233</v>
       </c>
       <c r="J19">
-        <v>173490</v>
+        <v>149000</v>
       </c>
       <c r="L19" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M19">
         <v>4</v>
       </c>
       <c r="N19">
-        <v>9845</v>
+        <v>9953</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>77</v>
+        <v>45</v>
+      </c>
+      <c r="C20">
+        <v>4210602</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G20">
-        <v>94200</v>
-      </c>
-      <c r="H20" t="s">
-        <v>89</v>
+        <v>17500</v>
+      </c>
+      <c r="H20">
+        <v>233</v>
       </c>
       <c r="J20">
-        <v>94200</v>
+        <v>17500</v>
       </c>
       <c r="L20" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M20">
         <v>4</v>
       </c>
       <c r="N20">
-        <v>9874</v>
+        <v>9953</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>77</v>
+        <v>48</v>
+      </c>
+      <c r="C21">
+        <v>4210602</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2">
         <v>46204</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="G21">
-        <v>100000</v>
-      </c>
-      <c r="H21" t="s">
-        <v>91</v>
+        <v>102615</v>
+      </c>
+      <c r="H21">
+        <v>334</v>
       </c>
       <c r="J21">
-        <v>100000</v>
+        <v>102615</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M21">
         <v>4</v>
       </c>
       <c r="N21">
-        <v>9898</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" t="s">
-        <v>77</v>
+        <v>48</v>
+      </c>
+      <c r="C22">
+        <v>4210602</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="F22" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G22">
-        <v>193540</v>
+        <v>162500</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="J22">
-        <v>193540</v>
+        <v>162500</v>
       </c>
       <c r="L22" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M22">
         <v>4</v>
       </c>
       <c r="N22">
-        <v>9846</v>
+        <v>9916</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
+        <v>48</v>
+      </c>
+      <c r="C23">
+        <v>4210602</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G23">
-        <v>102000</v>
-      </c>
-      <c r="H23" t="s">
-        <v>96</v>
+        <v>118952</v>
+      </c>
+      <c r="H23">
+        <v>234</v>
       </c>
       <c r="J23">
-        <v>102000</v>
+        <v>118952</v>
       </c>
       <c r="L23" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M23">
         <v>4</v>
       </c>
       <c r="N23">
-        <v>9875</v>
+        <v>9954</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="C24">
+        <v>4210602</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2">
         <v>46204</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="G24">
-        <v>110000</v>
-      </c>
-      <c r="H24" t="s">
-        <v>98</v>
+        <v>86962</v>
+      </c>
+      <c r="H24">
+        <v>335</v>
       </c>
       <c r="J24">
-        <v>110000</v>
+        <v>86962</v>
       </c>
       <c r="L24" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M24">
         <v>4</v>
       </c>
       <c r="N24">
-        <v>9899</v>
+        <v>9901</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="C25">
+        <v>4210602</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="G25">
-        <v>40000</v>
-      </c>
-      <c r="H25" t="s">
-        <v>98</v>
+        <v>92879.86</v>
+      </c>
+      <c r="H25">
+        <v>135</v>
       </c>
       <c r="J25">
-        <v>40000</v>
+        <v>92879.86</v>
       </c>
       <c r="L25" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M25">
         <v>4</v>
       </c>
       <c r="N25">
-        <v>9899</v>
+        <v>9925</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>4210602</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G26">
-        <v>109236</v>
-      </c>
-      <c r="H26" t="s">
-        <v>102</v>
+        <v>122626</v>
+      </c>
+      <c r="H26">
+        <v>235</v>
       </c>
       <c r="J26">
-        <v>109236</v>
+        <v>122626</v>
       </c>
       <c r="L26" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M26">
         <v>4</v>
       </c>
       <c r="N26">
-        <v>9847</v>
+        <v>9955</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C27" t="s">
-        <v>77</v>
+        <v>52</v>
+      </c>
+      <c r="C27">
+        <v>4210602</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2">
         <v>46204</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="G27">
-        <v>102615</v>
-      </c>
-      <c r="H27" t="s">
-        <v>104</v>
+        <v>77471.83</v>
+      </c>
+      <c r="H27">
+        <v>336</v>
       </c>
       <c r="J27">
-        <v>102615</v>
+        <v>77471.83</v>
       </c>
       <c r="L27" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M27">
         <v>4</v>
       </c>
       <c r="N27">
-        <v>9900</v>
+        <v>9902</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" t="s">
-        <v>77</v>
+        <v>52</v>
+      </c>
+      <c r="C28">
+        <v>4210602</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G28">
-        <v>97466</v>
-      </c>
-      <c r="H28" t="s">
-        <v>107</v>
+        <v>186377</v>
+      </c>
+      <c r="H28">
+        <v>136</v>
       </c>
       <c r="J28">
-        <v>97466</v>
+        <v>186377</v>
       </c>
       <c r="L28" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M28">
         <v>4</v>
       </c>
       <c r="N28">
-        <v>9848</v>
+        <v>9926</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" t="s">
-        <v>77</v>
+        <v>52</v>
+      </c>
+      <c r="C29">
+        <v>4210602</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="F29" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="G29">
-        <v>259855</v>
-      </c>
-      <c r="H29" t="s">
-        <v>109</v>
-      </c>
-      <c r="I29" t="s">
-        <v>110</v>
+        <v>118885</v>
+      </c>
+      <c r="H29">
+        <v>236</v>
       </c>
       <c r="J29">
-        <v>259855</v>
+        <v>118885</v>
       </c>
       <c r="L29" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M29">
         <v>4</v>
       </c>
       <c r="N29">
-        <v>9848</v>
+        <v>9956</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
+        <v>52</v>
+      </c>
+      <c r="C30">
+        <v>4210602</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G30">
-        <v>86962</v>
-      </c>
-      <c r="H30" t="s">
-        <v>112</v>
+        <v>99674.94</v>
+      </c>
+      <c r="H30">
+        <v>336</v>
       </c>
       <c r="J30">
-        <v>86962</v>
+        <v>99674.94</v>
       </c>
       <c r="L30" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M30">
         <v>4</v>
       </c>
       <c r="N30">
-        <v>9901</v>
+        <v>9973</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="C31">
+        <v>4210602</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="G31">
-        <v>82590.84</v>
-      </c>
-      <c r="H31" t="s">
-        <v>115</v>
+        <v>132990</v>
+      </c>
+      <c r="H31">
+        <v>337</v>
       </c>
       <c r="J31">
-        <v>82590.84</v>
+        <v>132990</v>
       </c>
       <c r="L31" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
       <c r="N31">
-        <v>9849</v>
+        <v>9903</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="C32">
+        <v>4210602</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F32" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="G32">
-        <v>92865</v>
-      </c>
-      <c r="H32" t="s">
-        <v>117</v>
+        <v>80018</v>
+      </c>
+      <c r="H32">
+        <v>137</v>
       </c>
       <c r="J32">
-        <v>92865</v>
+        <v>80018</v>
       </c>
       <c r="L32" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M32">
         <v>4</v>
       </c>
       <c r="N32">
-        <v>9878</v>
+        <v>9927</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -2100,113 +1974,113 @@
         <v>257</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" t="s">
-        <v>77</v>
+        <v>53</v>
+      </c>
+      <c r="C33">
+        <v>4210602</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="G33">
-        <v>68486</v>
-      </c>
-      <c r="H33" t="s">
-        <v>120</v>
+        <v>158158</v>
+      </c>
+      <c r="H33">
+        <v>237</v>
       </c>
       <c r="J33">
-        <v>68486</v>
+        <v>158158</v>
       </c>
       <c r="L33" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M33">
         <v>4</v>
       </c>
       <c r="N33">
-        <v>9850</v>
+        <v>9957</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
+        <v>55</v>
+      </c>
+      <c r="C34">
+        <v>4210602</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="F34" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="G34">
-        <v>107325</v>
-      </c>
-      <c r="H34" t="s">
-        <v>122</v>
+        <v>89861.83</v>
+      </c>
+      <c r="H34">
+        <v>338</v>
       </c>
       <c r="J34">
-        <v>107325</v>
+        <v>89861.83</v>
       </c>
       <c r="L34" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M34">
         <v>4</v>
       </c>
       <c r="N34">
-        <v>9879</v>
+        <v>9904</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" t="s">
-        <v>77</v>
+        <v>55</v>
+      </c>
+      <c r="C35">
+        <v>4210602</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F35" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="G35">
-        <v>132990</v>
-      </c>
-      <c r="H35" t="s">
-        <v>124</v>
+        <v>108359.99</v>
+      </c>
+      <c r="H35">
+        <v>138</v>
       </c>
       <c r="J35">
-        <v>132990</v>
+        <v>108359.99</v>
       </c>
       <c r="L35" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M35">
         <v>4</v>
       </c>
       <c r="N35">
-        <v>9903</v>
+        <v>9928</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -2214,37 +2088,37 @@
         <v>258</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
-      </c>
-      <c r="C36" t="s">
-        <v>77</v>
+        <v>55</v>
+      </c>
+      <c r="C36">
+        <v>4210602</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="F36" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G36">
-        <v>160093.70000000001</v>
-      </c>
-      <c r="H36" t="s">
-        <v>127</v>
+        <v>105720.54</v>
+      </c>
+      <c r="H36">
+        <v>238</v>
       </c>
       <c r="J36">
-        <v>160093.70000000001</v>
+        <v>105720.54</v>
       </c>
       <c r="L36" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M36">
         <v>4</v>
       </c>
       <c r="N36">
-        <v>9851</v>
+        <v>9958</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -2252,37 +2126,37 @@
         <v>259</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" t="s">
-        <v>77</v>
+        <v>56</v>
+      </c>
+      <c r="C37">
+        <v>4210602</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G37">
-        <v>46583</v>
-      </c>
-      <c r="H37" t="s">
-        <v>130</v>
+        <v>114052</v>
+      </c>
+      <c r="H37">
+        <v>139</v>
       </c>
       <c r="J37">
-        <v>46583</v>
+        <v>114052</v>
       </c>
       <c r="L37" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M37">
         <v>4</v>
       </c>
       <c r="N37">
-        <v>9852</v>
+        <v>9929</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -2290,75 +2164,75 @@
         <v>259</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" t="s">
-        <v>77</v>
+        <v>56</v>
+      </c>
+      <c r="C38">
+        <v>4210602</v>
       </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F38" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="G38">
-        <v>86257</v>
-      </c>
-      <c r="H38" t="s">
-        <v>47</v>
+        <v>90086</v>
+      </c>
+      <c r="H38">
+        <v>239</v>
       </c>
       <c r="J38">
-        <v>86257</v>
+        <v>90086</v>
       </c>
       <c r="L38" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M38">
         <v>4</v>
       </c>
       <c r="N38">
-        <v>9881</v>
+        <v>9959</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
+        <v>56</v>
+      </c>
+      <c r="C39">
+        <v>4210602</v>
       </c>
       <c r="D39" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2">
-        <v>46202</v>
+        <v>46207</v>
       </c>
       <c r="F39" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="G39">
-        <v>42800</v>
-      </c>
-      <c r="H39" t="s">
-        <v>134</v>
+        <v>156498</v>
+      </c>
+      <c r="H39">
+        <v>339</v>
       </c>
       <c r="J39">
-        <v>42800</v>
+        <v>156498</v>
       </c>
       <c r="L39" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M39">
         <v>4</v>
       </c>
       <c r="N39">
-        <v>9853</v>
+        <v>9976</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -2366,37 +2240,37 @@
         <v>260</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="C40">
+        <v>4210602</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="F40" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="G40">
-        <v>180500</v>
-      </c>
-      <c r="H40" t="s">
-        <v>136</v>
+        <v>158000</v>
+      </c>
+      <c r="H40">
+        <v>331</v>
       </c>
       <c r="J40">
-        <v>180500</v>
+        <v>158000</v>
       </c>
       <c r="L40" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M40">
         <v>4</v>
       </c>
       <c r="N40">
-        <v>9882</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -2404,505 +2278,756 @@
         <v>260</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="C41">
+        <v>4210602</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F41" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="G41">
-        <v>158000</v>
+        <v>11400</v>
       </c>
       <c r="H41" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="J41">
-        <v>158000</v>
+        <v>11400</v>
       </c>
       <c r="L41" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M41">
         <v>4</v>
       </c>
       <c r="N41">
-        <v>9897</v>
+        <v>9934</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="C42">
+        <v>4210602</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F42" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42">
+        <v>95300</v>
+      </c>
+      <c r="H42">
         <v>140</v>
       </c>
-      <c r="G42">
-        <v>75000</v>
-      </c>
-      <c r="H42" t="s">
-        <v>141</v>
-      </c>
       <c r="J42">
-        <v>75000</v>
+        <v>95300</v>
       </c>
       <c r="L42" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M42">
         <v>4</v>
       </c>
       <c r="N42">
-        <v>9871</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B43" t="s">
-        <v>139</v>
-      </c>
-      <c r="C43" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="C43">
+        <v>4210602</v>
       </c>
       <c r="D43" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F43" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="G43">
-        <v>75000</v>
-      </c>
-      <c r="H43" t="s">
-        <v>143</v>
+        <v>750000</v>
+      </c>
+      <c r="H43">
+        <v>140</v>
+      </c>
+      <c r="I43" t="s">
+        <v>106</v>
       </c>
       <c r="J43">
-        <v>75000</v>
+        <v>750000</v>
       </c>
       <c r="L43" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M43">
         <v>4</v>
       </c>
       <c r="N43">
-        <v>9895</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="C44">
+        <v>4210602</v>
       </c>
       <c r="D44" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E44" s="2">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="G44">
-        <v>232872</v>
-      </c>
-      <c r="H44" t="s">
-        <v>146</v>
+        <v>89800</v>
+      </c>
+      <c r="H44">
+        <v>240</v>
       </c>
       <c r="J44">
-        <v>232872</v>
+        <v>89800</v>
       </c>
       <c r="L44" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M44">
         <v>4</v>
       </c>
       <c r="N44">
-        <v>9870</v>
+        <v>9960</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
-      </c>
-      <c r="C45" t="s">
-        <v>77</v>
+        <v>57</v>
+      </c>
+      <c r="C45">
+        <v>4210602</v>
       </c>
       <c r="D45" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="E45" s="2">
-        <v>46203</v>
+        <v>46207</v>
       </c>
       <c r="F45" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="G45">
-        <v>170304</v>
-      </c>
-      <c r="H45" t="s">
-        <v>148</v>
+        <v>74500</v>
+      </c>
+      <c r="H45">
+        <v>331</v>
       </c>
       <c r="J45">
-        <v>170304</v>
+        <v>74500</v>
       </c>
       <c r="L45" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M45">
         <v>4</v>
       </c>
       <c r="N45">
-        <v>9891</v>
+        <v>9968</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>355</v>
+        <v>261</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
-      </c>
-      <c r="C46" t="s">
-        <v>150</v>
+        <v>59</v>
+      </c>
+      <c r="C46">
+        <v>4210602</v>
       </c>
       <c r="D46" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="E46" s="2">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="F46" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="G46">
-        <v>30500</v>
-      </c>
-      <c r="I46" t="s">
-        <v>153</v>
+        <v>75000</v>
+      </c>
+      <c r="H46" t="s">
+        <v>62</v>
       </c>
       <c r="J46">
-        <v>30500</v>
+        <v>75000</v>
       </c>
       <c r="L46" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N46">
+        <v>9895</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>355</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
-      </c>
-      <c r="C47" t="s">
-        <v>150</v>
+        <v>59</v>
+      </c>
+      <c r="C47">
+        <v>4210602</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F47" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="G47">
-        <v>21000</v>
-      </c>
-      <c r="I47" t="s">
-        <v>156</v>
+        <v>75000</v>
+      </c>
+      <c r="H47" t="s">
+        <v>110</v>
       </c>
       <c r="J47">
-        <v>21000</v>
+        <v>75000</v>
       </c>
       <c r="L47" t="s">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N47">
+        <v>9917</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
+        <v>261</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48">
+        <v>4210602</v>
+      </c>
+      <c r="D48" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F48" t="s">
+        <v>111</v>
+      </c>
+      <c r="G48">
+        <v>75000</v>
+      </c>
+      <c r="H48" t="s">
+        <v>60</v>
+      </c>
+      <c r="J48">
+        <v>75000</v>
+      </c>
+      <c r="L48" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48">
+        <v>4</v>
+      </c>
+      <c r="N48">
+        <v>9947</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>261</v>
+      </c>
+      <c r="B49" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49">
+        <v>4210602</v>
+      </c>
+      <c r="D49" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F49" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49">
+        <v>75000</v>
+      </c>
+      <c r="H49" t="s">
+        <v>113</v>
+      </c>
+      <c r="J49">
+        <v>75000</v>
+      </c>
+      <c r="L49" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49">
+        <v>4</v>
+      </c>
+      <c r="N49">
+        <v>9991</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>262</v>
+      </c>
+      <c r="B50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50">
+        <v>4210602</v>
+      </c>
+      <c r="D50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F50" t="s">
+        <v>114</v>
+      </c>
+      <c r="G50">
+        <v>262767</v>
+      </c>
+      <c r="H50" t="s">
+        <v>115</v>
+      </c>
+      <c r="J50">
+        <v>262767</v>
+      </c>
+      <c r="L50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="N50">
+        <v>9915</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>262</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51">
+        <v>4210602</v>
+      </c>
+      <c r="D51" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F51" t="s">
+        <v>116</v>
+      </c>
+      <c r="G51">
+        <v>179809</v>
+      </c>
+      <c r="H51" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51">
+        <v>179809</v>
+      </c>
+      <c r="L51" t="s">
+        <v>24</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="N51">
+        <v>9939</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>321</v>
+      </c>
+      <c r="B52" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52">
+        <v>4210803</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F52" t="s">
+        <v>119</v>
+      </c>
+      <c r="G52">
+        <v>270253.5</v>
+      </c>
+      <c r="I52" t="s">
+        <v>120</v>
+      </c>
+      <c r="J52">
+        <v>223350</v>
+      </c>
+      <c r="K52">
+        <v>46903.5</v>
+      </c>
+      <c r="L52" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>355</v>
       </c>
-      <c r="B48" t="s">
-        <v>149</v>
-      </c>
-      <c r="C48" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" s="2">
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53">
+        <v>4210206</v>
+      </c>
+      <c r="D53" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="2">
         <v>46204</v>
       </c>
-      <c r="F48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G48">
+      <c r="F53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G53">
         <v>18000</v>
       </c>
-      <c r="I48" t="s">
-        <v>158</v>
-      </c>
-      <c r="J48">
+      <c r="I53" t="s">
+        <v>68</v>
+      </c>
+      <c r="J53">
         <v>18000</v>
       </c>
-      <c r="L48" t="s">
-        <v>154</v>
-      </c>
-      <c r="M48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>355</v>
-      </c>
-      <c r="B49" t="s">
-        <v>149</v>
-      </c>
-      <c r="C49" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" t="s">
-        <v>151</v>
-      </c>
-      <c r="E49" s="2">
-        <v>46205</v>
-      </c>
-      <c r="F49" t="s">
-        <v>159</v>
-      </c>
-      <c r="G49">
-        <v>22500</v>
-      </c>
-      <c r="I49" t="s">
-        <v>160</v>
-      </c>
-      <c r="J49">
-        <v>22500</v>
-      </c>
-      <c r="L49" t="s">
-        <v>154</v>
-      </c>
-      <c r="M49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>370</v>
-      </c>
-      <c r="B50" t="s">
-        <v>161</v>
-      </c>
-      <c r="C50" t="s">
-        <v>33</v>
-      </c>
-      <c r="D50" t="s">
-        <v>34</v>
-      </c>
-      <c r="E50" s="2">
-        <v>46203</v>
-      </c>
-      <c r="F50" t="s">
-        <v>162</v>
-      </c>
-      <c r="G50">
-        <v>50000.12</v>
-      </c>
-      <c r="I50" t="s">
-        <v>163</v>
-      </c>
-      <c r="J50">
-        <v>42659.02</v>
-      </c>
-      <c r="K50">
-        <v>7341.1</v>
-      </c>
-      <c r="L50" t="s">
-        <v>19</v>
-      </c>
-      <c r="M50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>396</v>
-      </c>
-      <c r="B51" t="s">
-        <v>164</v>
-      </c>
-      <c r="C51" t="s">
-        <v>165</v>
-      </c>
-      <c r="D51" t="s">
-        <v>166</v>
-      </c>
-      <c r="E51" s="2">
-        <v>46203</v>
-      </c>
-      <c r="F51" t="s">
-        <v>167</v>
-      </c>
-      <c r="G51">
-        <v>73800</v>
-      </c>
-      <c r="I51" t="s">
-        <v>168</v>
-      </c>
-      <c r="J51">
-        <v>73800</v>
-      </c>
-      <c r="L51" t="s">
-        <v>154</v>
-      </c>
-      <c r="M51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>396</v>
-      </c>
-      <c r="B52" t="s">
-        <v>164</v>
-      </c>
-      <c r="C52" t="s">
-        <v>165</v>
-      </c>
-      <c r="D52" t="s">
-        <v>166</v>
-      </c>
-      <c r="E52" s="2">
-        <v>46203</v>
-      </c>
-      <c r="F52" t="s">
-        <v>169</v>
-      </c>
-      <c r="G52">
-        <v>64300</v>
-      </c>
-      <c r="I52" t="s">
-        <v>170</v>
-      </c>
-      <c r="J52">
-        <v>64300</v>
-      </c>
-      <c r="L52" t="s">
-        <v>154</v>
-      </c>
-      <c r="M52">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>396</v>
-      </c>
-      <c r="B53" t="s">
-        <v>164</v>
-      </c>
-      <c r="C53" t="s">
-        <v>165</v>
-      </c>
-      <c r="D53" t="s">
-        <v>166</v>
-      </c>
-      <c r="E53" s="2">
-        <v>46205</v>
-      </c>
-      <c r="F53" t="s">
-        <v>171</v>
-      </c>
-      <c r="G53">
-        <v>98000</v>
-      </c>
-      <c r="I53" t="s">
-        <v>172</v>
-      </c>
-      <c r="J53">
-        <v>98000</v>
-      </c>
       <c r="L53" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="M53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>355</v>
+      </c>
+      <c r="B54" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54">
+        <v>4210206</v>
+      </c>
+      <c r="D54" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F54" t="s">
+        <v>69</v>
+      </c>
+      <c r="G54">
+        <v>22500</v>
+      </c>
+      <c r="I54" t="s">
+        <v>70</v>
+      </c>
+      <c r="J54">
+        <v>22500</v>
+      </c>
+      <c r="L54" t="s">
+        <v>66</v>
+      </c>
+      <c r="M54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>355</v>
+      </c>
+      <c r="B55" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55">
+        <v>4210206</v>
+      </c>
+      <c r="D55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F55" t="s">
+        <v>121</v>
+      </c>
+      <c r="G55">
+        <v>21500</v>
+      </c>
+      <c r="I55" t="s">
+        <v>70</v>
+      </c>
+      <c r="J55">
+        <v>21500</v>
+      </c>
+      <c r="L55" t="s">
+        <v>66</v>
+      </c>
+      <c r="M55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>382</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>4210101</v>
+      </c>
+      <c r="D56" t="s">
+        <v>123</v>
+      </c>
+      <c r="E56" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F56" t="s">
+        <v>124</v>
+      </c>
+      <c r="G56">
+        <v>150000</v>
+      </c>
+      <c r="H56">
+        <v>340</v>
+      </c>
+      <c r="I56" t="s">
+        <v>125</v>
+      </c>
+      <c r="J56">
+        <v>150000</v>
+      </c>
+      <c r="L56" t="s">
+        <v>24</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>9977</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>382</v>
+      </c>
+      <c r="B57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C57">
+        <v>4210101</v>
+      </c>
+      <c r="D57" t="s">
+        <v>123</v>
+      </c>
+      <c r="E57" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F57" t="s">
+        <v>126</v>
+      </c>
+      <c r="G57">
+        <v>254000</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J57">
+        <v>254000</v>
+      </c>
+      <c r="L57" t="s">
+        <v>24</v>
+      </c>
+      <c r="M57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>382</v>
+      </c>
+      <c r="B58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58">
+        <v>4210101</v>
+      </c>
+      <c r="D58" t="s">
+        <v>123</v>
+      </c>
+      <c r="E58" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F58" t="s">
+        <v>128</v>
+      </c>
+      <c r="G58">
+        <v>115000</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J58">
+        <v>115000</v>
+      </c>
+      <c r="L58" t="s">
+        <v>24</v>
+      </c>
+      <c r="M58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>396</v>
+      </c>
+      <c r="B59" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59">
+        <v>4210301</v>
+      </c>
+      <c r="D59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F59" t="s">
+        <v>74</v>
+      </c>
+      <c r="G59">
+        <v>98000</v>
+      </c>
+      <c r="I59" t="s">
+        <v>75</v>
+      </c>
+      <c r="J59">
+        <v>98000</v>
+      </c>
+      <c r="L59" t="s">
+        <v>66</v>
+      </c>
+      <c r="M59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>396</v>
+      </c>
+      <c r="B60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60">
+        <v>4210301</v>
+      </c>
+      <c r="D60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F60" t="s">
+        <v>130</v>
+      </c>
+      <c r="G60">
+        <v>50000</v>
+      </c>
+      <c r="I60" t="s">
+        <v>73</v>
+      </c>
+      <c r="J60">
+        <v>50000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>66</v>
+      </c>
+      <c r="M60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="5:5" x14ac:dyDescent="0.25">

--- a/data/comision_chofer.xlsx
+++ b/data/comision_chofer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231B4E9D-C379-4B25-9ABD-A96E71C2D58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B989894-F2B3-48A8-BCF9-DA71ECD85D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="326">
   <si>
     <t>codigo</t>
   </si>
@@ -424,6 +424,594 @@
   </si>
   <si>
     <t>NOX000100011205</t>
+  </si>
+  <si>
+    <t>NOX000100011414</t>
+  </si>
+  <si>
+    <t>ESTACION FERREYRA S.R.L.</t>
+  </si>
+  <si>
+    <t>FCA001600044217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       320 CAM 20 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>FCA001600044249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       210 CAM 10 MARTES</t>
+  </si>
+  <si>
+    <t>FCA001600044266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       419 CAM 19 JUEVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FATIMA SRL </t>
+  </si>
+  <si>
+    <t>NOX000100011276</t>
+  </si>
+  <si>
+    <t>COMBUTIBL SURAN</t>
+  </si>
+  <si>
+    <t>VARIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros </t>
+  </si>
+  <si>
+    <t>NOX000100011272</t>
+  </si>
+  <si>
+    <t>REP APILADORA- MOD TRACCION</t>
+  </si>
+  <si>
+    <t>NOX000100011369</t>
+  </si>
+  <si>
+    <t>caFE 2 KG</t>
+  </si>
+  <si>
+    <t>Costo Administrativo</t>
+  </si>
+  <si>
+    <t>NOX000100011416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATERIA AUTOELEVADOR </t>
+  </si>
+  <si>
+    <t>NOX000100011418</t>
+  </si>
+  <si>
+    <t>ARREGLO MICRONDAS</t>
+  </si>
+  <si>
+    <t>COMISIONES REPARTIDORES</t>
+  </si>
+  <si>
+    <t>NOX000100011335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       211 CAM 11 MARTES</t>
+  </si>
+  <si>
+    <t>211-DIEGO GUZMAN</t>
+  </si>
+  <si>
+    <t>Muni Inspeccion Sanitaria</t>
+  </si>
+  <si>
+    <t>Bromatología, SENASA, ITV, RTO</t>
+  </si>
+  <si>
+    <t>NOX000100011241</t>
+  </si>
+  <si>
+    <t>NOX000100011292</t>
+  </si>
+  <si>
+    <t>NOX000100011293</t>
+  </si>
+  <si>
+    <t>NOX000100011287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       323 CAM 23 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>FCA003700001845</t>
+  </si>
+  <si>
+    <t>SEBA</t>
+  </si>
+  <si>
+    <t>FCA003700001862</t>
+  </si>
+  <si>
+    <t>FCA003700001950</t>
+  </si>
+  <si>
+    <t>NTALIA</t>
+  </si>
+  <si>
+    <t>PLANTA EMBOTELLADORA S.A.S.</t>
+  </si>
+  <si>
+    <t>Agua</t>
+  </si>
+  <si>
+    <t>FCA000400016896</t>
+  </si>
+  <si>
+    <t>BIDONES AGUA JUNIO 2026</t>
+  </si>
+  <si>
+    <t>CAPASITIO S.A.S.</t>
+  </si>
+  <si>
+    <t>FCA000300025916</t>
+  </si>
+  <si>
+    <t>abono naaloo</t>
+  </si>
+  <si>
+    <t>FCA003600064687</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>FCA003600065004</t>
+  </si>
+  <si>
+    <t>FCA000300015113</t>
+  </si>
+  <si>
+    <t>IMPRESORA ALQUILER</t>
+  </si>
+  <si>
+    <t>UNION CONSTRUCTORES DE MAQUINAS S A</t>
+  </si>
+  <si>
+    <t>FCA000200003727</t>
+  </si>
+  <si>
+    <t>ucoma -alquiler julio 26</t>
+  </si>
+  <si>
+    <t>FCA000200006942</t>
+  </si>
+  <si>
+    <t>ucoma expensas junio 26</t>
+  </si>
+  <si>
+    <t>NEA000200006962</t>
+  </si>
+  <si>
+    <t>ucoma - energia junio 26</t>
+  </si>
+  <si>
+    <t>JUAN ESTEBAN DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>Reparación y Mantenimiento de Muebles y Útiles</t>
+  </si>
+  <si>
+    <t>FCA000300000276</t>
+  </si>
+  <si>
+    <t>carteles- vinilos</t>
+  </si>
+  <si>
+    <t>NOX000100011263</t>
+  </si>
+  <si>
+    <t>NOX000100011279</t>
+  </si>
+  <si>
+    <t>NOX000100011333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       221 CAM 21 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011346</t>
+  </si>
+  <si>
+    <t>NOX000100011357</t>
+  </si>
+  <si>
+    <t>NOX000100011269</t>
+  </si>
+  <si>
+    <t>NOX000100011289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       322 CAM 22 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       222 CAM 22 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011344</t>
+  </si>
+  <si>
+    <t>NOX000100011359</t>
+  </si>
+  <si>
+    <t>NOX000100011339</t>
+  </si>
+  <si>
+    <t>NOX000100011236</t>
+  </si>
+  <si>
+    <t>NOX000100011294</t>
+  </si>
+  <si>
+    <t>NOX000100011286</t>
+  </si>
+  <si>
+    <t>NOX000100011340</t>
+  </si>
+  <si>
+    <t>NOX000100011341</t>
+  </si>
+  <si>
+    <t>NOX000100011360</t>
+  </si>
+  <si>
+    <t>NOX000100011237</t>
+  </si>
+  <si>
+    <t>NOX000100011278</t>
+  </si>
+  <si>
+    <t>NOX000100011270</t>
+  </si>
+  <si>
+    <t>NOX000100011280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       324 CAM 24 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       224 CAM 24 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011351</t>
+  </si>
+  <si>
+    <t>NOX000100011362</t>
+  </si>
+  <si>
+    <t>NOX000100011239</t>
+  </si>
+  <si>
+    <t>NOX000100011238</t>
+  </si>
+  <si>
+    <t>NOX000100011329</t>
+  </si>
+  <si>
+    <t>NOX000100011281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       325 CAM 25 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       225 CAM 25 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011350</t>
+  </si>
+  <si>
+    <t>NOX000100011246</t>
+  </si>
+  <si>
+    <t>NOX000100011266</t>
+  </si>
+  <si>
+    <t>NOX000100011282</t>
+  </si>
+  <si>
+    <t>NOX000100011331</t>
+  </si>
+  <si>
+    <t>NOX000100011342</t>
+  </si>
+  <si>
+    <t>NOX000100011361</t>
+  </si>
+  <si>
+    <t>NOX000100011243</t>
+  </si>
+  <si>
+    <t>NOX000100011242</t>
+  </si>
+  <si>
+    <t>NOX000100011267</t>
+  </si>
+  <si>
+    <t>NOX000100011290</t>
+  </si>
+  <si>
+    <t>NOX000100011338</t>
+  </si>
+  <si>
+    <t>NOX000100011366</t>
+  </si>
+  <si>
+    <t>NOX000100011364</t>
+  </si>
+  <si>
+    <t>NOX000100011247</t>
+  </si>
+  <si>
+    <t>NOX000100011304</t>
+  </si>
+  <si>
+    <t>NOX000100011271</t>
+  </si>
+  <si>
+    <t>NOX000100011283</t>
+  </si>
+  <si>
+    <t>NOX000100011348</t>
+  </si>
+  <si>
+    <t>NOX000100011358</t>
+  </si>
+  <si>
+    <t>NOX000100011363</t>
+  </si>
+  <si>
+    <t>NOX000100011240</t>
+  </si>
+  <si>
+    <t>NOX000100011262</t>
+  </si>
+  <si>
+    <t>NOX000100011291</t>
+  </si>
+  <si>
+    <t>NOX000100011300</t>
+  </si>
+  <si>
+    <t>NOX000100011349</t>
+  </si>
+  <si>
+    <t>NOX000100011345</t>
+  </si>
+  <si>
+    <t>NOX000100011356</t>
+  </si>
+  <si>
+    <t>NOX000100011268</t>
+  </si>
+  <si>
+    <t>NOX000100011288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       321 CAM 21 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011330</t>
+  </si>
+  <si>
+    <t>NOX000100011343</t>
+  </si>
+  <si>
+    <t>NOX000100011365</t>
+  </si>
+  <si>
+    <t>NOX000100011245</t>
+  </si>
+  <si>
+    <t>NOX000100011264</t>
+  </si>
+  <si>
+    <t>NOX000100011275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       305 CAM 5 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011336</t>
+  </si>
+  <si>
+    <t>NOX000100011354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       420 CAM 20 JUEVES</t>
+  </si>
+  <si>
+    <t>420-426</t>
+  </si>
+  <si>
+    <t>NOX000100011244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       311 CAM 11 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       212 CAM 12 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       308 CAM 8 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       208 CAM 8 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       206 CAM 6 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       411 CAM 11 JUEVES</t>
+  </si>
+  <si>
+    <t>NEUROSCIEN</t>
+  </si>
+  <si>
+    <t>NOX000100011258</t>
+  </si>
+  <si>
+    <t>abono giroscop</t>
+  </si>
+  <si>
+    <t>PRESSA S.A.</t>
+  </si>
+  <si>
+    <t>FCA000500080895</t>
+  </si>
+  <si>
+    <t>abono julio 26_x000D_
+gps camiones</t>
+  </si>
+  <si>
+    <t>NOX000100011260</t>
+  </si>
+  <si>
+    <t>COMIDA GUS</t>
+  </si>
+  <si>
+    <t>NOX000100011261</t>
+  </si>
+  <si>
+    <t>GASEOSAS PARA PARTIDO</t>
+  </si>
+  <si>
+    <t>NOX000100011273</t>
+  </si>
+  <si>
+    <t>COMIDA VTA INTERIOR</t>
+  </si>
+  <si>
+    <t>NOX000100011305</t>
+  </si>
+  <si>
+    <t>COMIDA NICO</t>
+  </si>
+  <si>
+    <t>NOX000100011306</t>
+  </si>
+  <si>
+    <t>COMIDA GU-NICO</t>
+  </si>
+  <si>
+    <t>NOX000100011390</t>
+  </si>
+  <si>
+    <t>COMIDA VTA- SEBA</t>
+  </si>
+  <si>
+    <t>NOX000100011367</t>
+  </si>
+  <si>
+    <t>comida vta- mensual</t>
+  </si>
+  <si>
+    <t>NOX000100011368</t>
+  </si>
+  <si>
+    <t>comida gus</t>
+  </si>
+  <si>
+    <t>NOX000100011417</t>
+  </si>
+  <si>
+    <t>COMIDA GUS-MAXI</t>
+  </si>
+  <si>
+    <t>NOX000100011445</t>
+  </si>
+  <si>
+    <t>COMIDA MAXI-GUS</t>
+  </si>
+  <si>
+    <t>SANTA ALBINA S A</t>
+  </si>
+  <si>
+    <t>FCA002000081695</t>
+  </si>
+  <si>
+    <t>DEPOSITO</t>
+  </si>
+  <si>
+    <t>FCA002000082066</t>
+  </si>
+  <si>
+    <t>DEPOITO</t>
+  </si>
+  <si>
+    <t>NOX000100011284</t>
+  </si>
+  <si>
+    <t>VARIABLE SERGIO AVENDAÑO</t>
+  </si>
+  <si>
+    <t>NOX000100011285</t>
+  </si>
+  <si>
+    <t>VARIABLE GERMN</t>
+  </si>
+  <si>
+    <t>NOX000100011347</t>
+  </si>
+  <si>
+    <t>NOX000100011259</t>
+  </si>
+  <si>
+    <t>viaaticos julio 26_x000D_
+cba</t>
+  </si>
+  <si>
+    <t>NOX000100011274</t>
+  </si>
+  <si>
+    <t>NOX000100011415</t>
+  </si>
+  <si>
+    <t>SEBATIAN</t>
+  </si>
+  <si>
+    <t>NOX000100011432</t>
+  </si>
+  <si>
+    <t>NOX000100011433</t>
+  </si>
+  <si>
+    <t>VIATICOS JUNIO 26_x000D_
+GIANNINA</t>
   </si>
 </sst>
 </file>
@@ -832,86 +1420,83 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C3">
-        <v>4210701</v>
+        <v>4210304</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2">
-        <v>46204</v>
+        <v>46218</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="G3">
-        <v>767314.05</v>
+        <v>6000</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J3">
-        <v>634143.85</v>
-      </c>
-      <c r="K3">
-        <v>133170.20000000001</v>
+        <v>6000</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>4211201</v>
+        <v>4210701</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>75001.08</v>
+        <v>767314.05</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J4">
-        <v>64086.95</v>
+        <v>634143.85</v>
       </c>
       <c r="K4">
-        <v>10914.13</v>
+        <v>133170.20000000001</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>4211201</v>
@@ -920,22 +1505,22 @@
         <v>25</v>
       </c>
       <c r="E5" s="2">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="G5">
-        <v>84997.96</v>
-      </c>
-      <c r="I5" t="s">
-        <v>31</v>
+        <v>50000.08</v>
+      </c>
+      <c r="H5" t="s">
+        <v>134</v>
       </c>
       <c r="J5">
-        <v>72566.28</v>
+        <v>41322.379999999997</v>
       </c>
       <c r="K5">
-        <v>12431.68</v>
+        <v>8677.7000000000007</v>
       </c>
       <c r="L5" t="s">
         <v>18</v>
@@ -943,48 +1528,57 @@
       <c r="M5">
         <v>5</v>
       </c>
+      <c r="N5">
+        <v>9995</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="C6">
-        <v>4210904</v>
+        <v>4211201</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G6">
-        <v>625500.88</v>
-      </c>
-      <c r="I6" t="s">
-        <v>35</v>
+        <v>50000.1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>136</v>
       </c>
       <c r="J6">
-        <v>625500.88</v>
+        <v>41322.400000000001</v>
+      </c>
+      <c r="K6">
+        <v>8677.7000000000007</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <v>10074</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>224</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>132</v>
       </c>
       <c r="C7">
         <v>4211201</v>
@@ -993,22 +1587,23 @@
         <v>25</v>
       </c>
       <c r="E7" s="2">
-        <v>46206</v>
+        <v>46214</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
       <c r="G7">
-        <v>2825176.63</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>49996.959999999999</v>
+      </c>
+      <c r="H7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I7" s="1"/>
       <c r="J7">
-        <v>2398725.63</v>
+        <v>41319.800000000003</v>
       </c>
       <c r="K7">
-        <v>426451</v>
+        <v>8677.16</v>
       </c>
       <c r="L7" t="s">
         <v>18</v>
@@ -1016,203 +1611,191 @@
       <c r="M7">
         <v>5</v>
       </c>
+      <c r="N7">
+        <v>10109</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>251</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>139</v>
       </c>
       <c r="C8">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="G8">
-        <v>84980</v>
-      </c>
-      <c r="H8">
-        <v>340</v>
+        <v>60000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>141</v>
       </c>
       <c r="J8">
-        <v>84980</v>
+        <v>60000</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M8">
-        <v>4</v>
-      </c>
-      <c r="N8">
-        <v>9906</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C9">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="E9" s="2">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="G9">
-        <v>97560</v>
-      </c>
-      <c r="H9">
-        <v>131</v>
+        <v>390000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>145</v>
       </c>
       <c r="J9">
-        <v>97560</v>
+        <v>390000</v>
       </c>
       <c r="L9" t="s">
         <v>24</v>
       </c>
       <c r="M9">
         <v>4</v>
-      </c>
-      <c r="N9">
-        <v>9922</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C10">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="E10" s="2">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="G10">
-        <v>175030</v>
-      </c>
-      <c r="H10">
-        <v>231</v>
+        <v>88000</v>
+      </c>
+      <c r="I10" t="s">
+        <v>147</v>
       </c>
       <c r="J10">
-        <v>175030</v>
+        <v>88000</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="M10">
-        <v>4</v>
-      </c>
-      <c r="N10">
-        <v>9951</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="C11">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="E11" s="2">
-        <v>46207</v>
+        <v>46218</v>
       </c>
       <c r="F11" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="G11">
-        <v>80441</v>
-      </c>
-      <c r="H11">
-        <v>340</v>
+        <v>135000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>150</v>
       </c>
       <c r="J11">
-        <v>80441</v>
+        <v>135000</v>
       </c>
       <c r="L11" t="s">
         <v>24</v>
       </c>
       <c r="M11">
         <v>4</v>
-      </c>
-      <c r="N11">
-        <v>9977</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>252</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="C12">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="E12" s="2">
-        <v>46204</v>
+        <v>46218</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="G12">
-        <v>100000</v>
-      </c>
-      <c r="H12">
-        <v>332</v>
+        <v>50000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>152</v>
       </c>
       <c r="J12">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="L12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M12">
-        <v>4</v>
-      </c>
-      <c r="N12">
-        <v>9898</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>252</v>
+        <v>134</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>153</v>
       </c>
       <c r="C13">
         <v>4210602</v>
@@ -1221,798 +1804,795 @@
         <v>41</v>
       </c>
       <c r="E13" s="2">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="G13">
-        <v>141500</v>
-      </c>
-      <c r="H13">
-        <v>132</v>
+        <v>75000</v>
+      </c>
+      <c r="H13" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" t="s">
+        <v>156</v>
       </c>
       <c r="J13">
-        <v>141500</v>
+        <v>75000</v>
       </c>
       <c r="L13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N13">
-        <v>9923</v>
+        <v>10075</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="C14">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="E14" s="2">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>159</v>
       </c>
       <c r="G14">
-        <v>153917</v>
+        <v>38900</v>
       </c>
       <c r="H14">
-        <v>232</v>
+        <v>139</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14">
-        <v>153917</v>
+        <v>38900</v>
       </c>
       <c r="L14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>9952</v>
+        <v>10011</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="C15">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="E15" s="2">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="G15">
-        <v>52666</v>
+        <v>8500</v>
       </c>
       <c r="H15">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15">
-        <v>52666</v>
+        <v>8500</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>9969</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="C16">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="E16" s="2">
-        <v>46204</v>
+        <v>46210</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="G16">
-        <v>110000</v>
+        <v>34000</v>
       </c>
       <c r="H16">
-        <v>333</v>
+        <v>239</v>
       </c>
       <c r="J16">
-        <v>110000</v>
+        <v>34000</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>9899</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>253</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="C17">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="E17" s="2">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="G17">
-        <v>40000</v>
-      </c>
-      <c r="H17">
-        <v>333</v>
+        <v>17500</v>
+      </c>
+      <c r="H17" t="s">
+        <v>163</v>
       </c>
       <c r="J17">
-        <v>40000</v>
+        <v>17500</v>
       </c>
       <c r="L17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>9899</v>
+        <v>10054</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>253</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C18">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="G18">
-        <v>131000</v>
-      </c>
-      <c r="H18">
-        <v>133</v>
+        <v>75001.08</v>
+      </c>
+      <c r="I18" t="s">
+        <v>27</v>
       </c>
       <c r="J18">
-        <v>131000</v>
+        <v>64086.95</v>
+      </c>
+      <c r="K18">
+        <v>10914.13</v>
       </c>
       <c r="L18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M18">
-        <v>4</v>
-      </c>
-      <c r="N18">
-        <v>9924</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>253</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="G19">
-        <v>149000</v>
-      </c>
-      <c r="H19">
-        <v>233</v>
+        <v>30000.07</v>
+      </c>
+      <c r="I19" t="s">
+        <v>165</v>
       </c>
       <c r="J19">
-        <v>149000</v>
+        <v>25634.47</v>
+      </c>
+      <c r="K19">
+        <v>4365.6000000000004</v>
       </c>
       <c r="L19" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M19">
-        <v>4</v>
-      </c>
-      <c r="N19">
-        <v>9953</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>253</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E20" s="2">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="G20">
-        <v>17500</v>
-      </c>
-      <c r="H20">
-        <v>233</v>
+        <v>49999.99</v>
+      </c>
+      <c r="I20" t="s">
+        <v>165</v>
       </c>
       <c r="J20">
-        <v>17500</v>
+        <v>42724.01</v>
+      </c>
+      <c r="K20">
+        <v>7275.98</v>
       </c>
       <c r="L20" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M20">
-        <v>4</v>
-      </c>
-      <c r="N20">
-        <v>9953</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>254</v>
+        <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E21" s="2">
-        <v>46204</v>
+        <v>46217</v>
       </c>
       <c r="F21" t="s">
-        <v>49</v>
+        <v>167</v>
       </c>
       <c r="G21">
-        <v>102615</v>
-      </c>
-      <c r="H21">
-        <v>334</v>
+        <v>49999.99</v>
+      </c>
+      <c r="I21" t="s">
+        <v>168</v>
       </c>
       <c r="J21">
-        <v>102615</v>
+        <v>42724.01</v>
+      </c>
+      <c r="K21">
+        <v>7275.98</v>
       </c>
       <c r="L21" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M21">
-        <v>4</v>
-      </c>
-      <c r="N21">
-        <v>9900</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>254</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="C22">
-        <v>4210602</v>
+        <v>4210805</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2">
-        <v>46205</v>
+        <v>46217</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="G22">
-        <v>162500</v>
-      </c>
-      <c r="H22" t="s">
-        <v>86</v>
+        <v>259999.99</v>
+      </c>
+      <c r="I22" t="s">
+        <v>172</v>
       </c>
       <c r="J22">
-        <v>162500</v>
+        <v>214876.03</v>
+      </c>
+      <c r="K22">
+        <v>45123.96</v>
       </c>
       <c r="L22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M22">
-        <v>4</v>
-      </c>
-      <c r="N22">
-        <v>9916</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>173</v>
       </c>
       <c r="C23">
-        <v>4210602</v>
+        <v>4210701</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="G23">
-        <v>118952</v>
-      </c>
-      <c r="H23">
-        <v>234</v>
+        <v>331434.96999999997</v>
+      </c>
+      <c r="I23" t="s">
+        <v>175</v>
       </c>
       <c r="J23">
-        <v>118952</v>
+        <v>273913.2</v>
+      </c>
+      <c r="K23">
+        <v>57521.77</v>
       </c>
       <c r="L23" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="M23">
-        <v>4</v>
-      </c>
-      <c r="N23">
-        <v>9954</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>255</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C24">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E24" s="2">
         <v>46204</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G24">
-        <v>86962</v>
-      </c>
-      <c r="H24">
-        <v>335</v>
+        <v>84997.96</v>
+      </c>
+      <c r="I24" t="s">
+        <v>31</v>
       </c>
       <c r="J24">
-        <v>86962</v>
+        <v>72566.28</v>
+      </c>
+      <c r="K24">
+        <v>12431.68</v>
       </c>
       <c r="L24" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M24">
-        <v>4</v>
-      </c>
-      <c r="N24">
-        <v>9901</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>255</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E25" s="2">
-        <v>46205</v>
+        <v>46217</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="G25">
-        <v>92879.86</v>
-      </c>
-      <c r="H25">
-        <v>135</v>
+        <v>65010.38</v>
+      </c>
+      <c r="I25" t="s">
+        <v>177</v>
       </c>
       <c r="J25">
-        <v>92879.86</v>
+        <v>55508.87</v>
+      </c>
+      <c r="K25">
+        <v>9501.51</v>
       </c>
       <c r="L25" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M25">
-        <v>4</v>
-      </c>
-      <c r="N25">
-        <v>9925</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>255</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C26">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E26" s="2">
-        <v>46206</v>
+        <v>46218</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="G26">
-        <v>122626</v>
-      </c>
-      <c r="H26">
-        <v>235</v>
+        <v>76037.919999999998</v>
+      </c>
+      <c r="I26" t="s">
+        <v>177</v>
       </c>
       <c r="J26">
-        <v>122626</v>
+        <v>64916.72</v>
+      </c>
+      <c r="K26">
+        <v>11121.2</v>
       </c>
       <c r="L26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M26">
-        <v>4</v>
-      </c>
-      <c r="N26">
-        <v>9955</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>256</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C27">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>34</v>
       </c>
       <c r="G27">
-        <v>77471.83</v>
-      </c>
-      <c r="H27">
-        <v>336</v>
+        <v>625500.88</v>
+      </c>
+      <c r="I27" t="s">
+        <v>35</v>
       </c>
       <c r="J27">
-        <v>77471.83</v>
+        <v>625500.88</v>
       </c>
       <c r="L27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M27">
-        <v>4</v>
-      </c>
-      <c r="N27">
-        <v>9902</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>256</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E28" s="2">
-        <v>46205</v>
+        <v>46217</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="G28">
-        <v>186377</v>
-      </c>
-      <c r="H28">
-        <v>136</v>
+        <v>521413.2</v>
+      </c>
+      <c r="I28" t="s">
+        <v>180</v>
       </c>
       <c r="J28">
-        <v>186377</v>
+        <v>430920</v>
+      </c>
+      <c r="K28">
+        <v>90493.2</v>
       </c>
       <c r="L28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M28">
-        <v>4</v>
-      </c>
-      <c r="N28">
-        <v>9926</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="C29">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E29" s="2">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="G29">
-        <v>118885</v>
-      </c>
-      <c r="H29">
-        <v>236</v>
+        <v>25876614.219999999</v>
+      </c>
+      <c r="I29" t="s">
+        <v>183</v>
       </c>
       <c r="J29">
-        <v>118885</v>
+        <v>21385631.719999999</v>
+      </c>
+      <c r="K29">
+        <v>4490982.5</v>
       </c>
       <c r="L29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M29">
-        <v>4</v>
-      </c>
-      <c r="N29">
-        <v>9956</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>181</v>
       </c>
       <c r="C30">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E30" s="2">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="F30" t="s">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="G30">
-        <v>99674.94</v>
-      </c>
-      <c r="H30">
-        <v>336</v>
+        <v>6146969.79</v>
+      </c>
+      <c r="I30" t="s">
+        <v>185</v>
       </c>
       <c r="J30">
-        <v>99674.94</v>
+        <v>5235842.66</v>
+      </c>
+      <c r="K30">
+        <v>911127.13</v>
       </c>
       <c r="L30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M30">
-        <v>4</v>
-      </c>
-      <c r="N30">
-        <v>9973</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="C31">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E31" s="2">
-        <v>46204</v>
+        <v>46210</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="G31">
-        <v>132990</v>
-      </c>
-      <c r="H31">
-        <v>337</v>
+        <v>1210871.3400000001</v>
+      </c>
+      <c r="I31" t="s">
+        <v>187</v>
       </c>
       <c r="J31">
-        <v>132990</v>
+        <v>1210871.3400000001</v>
       </c>
       <c r="L31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M31">
-        <v>4</v>
-      </c>
-      <c r="N31">
-        <v>9903</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="C32">
-        <v>4210602</v>
+        <v>4211104</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="E32" s="2">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="F32" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="G32">
-        <v>80018</v>
-      </c>
-      <c r="H32">
-        <v>137</v>
+        <v>393250</v>
+      </c>
+      <c r="I32" t="s">
+        <v>191</v>
       </c>
       <c r="J32">
-        <v>80018</v>
+        <v>325000</v>
+      </c>
+      <c r="K32">
+        <v>68250</v>
       </c>
       <c r="L32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M32">
-        <v>4</v>
-      </c>
-      <c r="N32">
-        <v>9927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E33" s="2">
         <v>46206</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="G33">
-        <v>158158</v>
-      </c>
-      <c r="H33">
-        <v>237</v>
+        <v>2825176.63</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="J33">
-        <v>158158</v>
+        <v>2398725.63</v>
+      </c>
+      <c r="K33">
+        <v>426451</v>
       </c>
       <c r="L33" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M33">
-        <v>4</v>
-      </c>
-      <c r="N33">
-        <v>9957</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C34">
         <v>4210602</v>
@@ -2024,16 +2604,16 @@
         <v>46204</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="G34">
-        <v>89861.83</v>
+        <v>84980</v>
       </c>
       <c r="H34">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J34">
-        <v>89861.83</v>
+        <v>84980</v>
       </c>
       <c r="L34" t="s">
         <v>24</v>
@@ -2042,15 +2622,15 @@
         <v>4</v>
       </c>
       <c r="N34">
-        <v>9904</v>
+        <v>9906</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C35">
         <v>4210602</v>
@@ -2062,16 +2642,16 @@
         <v>46205</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="G35">
-        <v>108359.99</v>
+        <v>97560</v>
       </c>
       <c r="H35">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="J35">
-        <v>108359.99</v>
+        <v>97560</v>
       </c>
       <c r="L35" t="s">
         <v>24</v>
@@ -2080,15 +2660,15 @@
         <v>4</v>
       </c>
       <c r="N35">
-        <v>9928</v>
+        <v>9922</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C36">
         <v>4210602</v>
@@ -2097,19 +2677,19 @@
         <v>41</v>
       </c>
       <c r="E36" s="2">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="G36">
-        <v>105720.54</v>
+        <v>175030</v>
       </c>
       <c r="H36">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="J36">
-        <v>105720.54</v>
+        <v>175030</v>
       </c>
       <c r="L36" t="s">
         <v>24</v>
@@ -2118,15 +2698,15 @@
         <v>4</v>
       </c>
       <c r="N36">
-        <v>9958</v>
+        <v>9951</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C37">
         <v>4210602</v>
@@ -2135,19 +2715,19 @@
         <v>41</v>
       </c>
       <c r="E37" s="2">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="G37">
-        <v>114052</v>
+        <v>80441</v>
       </c>
       <c r="H37">
-        <v>139</v>
+        <v>340</v>
       </c>
       <c r="J37">
-        <v>114052</v>
+        <v>80441</v>
       </c>
       <c r="L37" t="s">
         <v>24</v>
@@ -2156,15 +2736,15 @@
         <v>4</v>
       </c>
       <c r="N37">
-        <v>9929</v>
+        <v>9977</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C38">
         <v>4210602</v>
@@ -2173,19 +2753,19 @@
         <v>41</v>
       </c>
       <c r="E38" s="2">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="G38">
-        <v>90086</v>
+        <v>137882</v>
       </c>
       <c r="H38">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="J38">
-        <v>90086</v>
+        <v>137882</v>
       </c>
       <c r="L38" t="s">
         <v>24</v>
@@ -2194,15 +2774,15 @@
         <v>4</v>
       </c>
       <c r="N38">
-        <v>9959</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C39">
         <v>4210602</v>
@@ -2211,19 +2791,19 @@
         <v>41</v>
       </c>
       <c r="E39" s="2">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="G39">
-        <v>156498</v>
+        <v>143252</v>
       </c>
       <c r="H39">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="J39">
-        <v>156498</v>
+        <v>143252</v>
       </c>
       <c r="L39" t="s">
         <v>24</v>
@@ -2232,15 +2812,15 @@
         <v>4</v>
       </c>
       <c r="N39">
-        <v>9976</v>
+        <v>10061</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C40">
         <v>4210602</v>
@@ -2249,19 +2829,19 @@
         <v>41</v>
       </c>
       <c r="E40" s="2">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>194</v>
       </c>
       <c r="G40">
-        <v>158000</v>
-      </c>
-      <c r="H40">
-        <v>331</v>
+        <v>280611</v>
+      </c>
+      <c r="H40" t="s">
+        <v>195</v>
       </c>
       <c r="J40">
-        <v>158000</v>
+        <v>280611</v>
       </c>
       <c r="L40" t="s">
         <v>24</v>
@@ -2270,15 +2850,15 @@
         <v>4</v>
       </c>
       <c r="N40">
-        <v>9897</v>
+        <v>10080</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C41">
         <v>4210602</v>
@@ -2287,19 +2867,19 @@
         <v>41</v>
       </c>
       <c r="E41" s="2">
-        <v>46205</v>
+        <v>46214</v>
       </c>
       <c r="F41" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="G41">
-        <v>11400</v>
-      </c>
-      <c r="H41" t="s">
-        <v>103</v>
+        <v>116073.67</v>
+      </c>
+      <c r="H41">
+        <v>330</v>
       </c>
       <c r="J41">
-        <v>11400</v>
+        <v>116073.67</v>
       </c>
       <c r="L41" t="s">
         <v>24</v>
@@ -2308,15 +2888,15 @@
         <v>4</v>
       </c>
       <c r="N41">
-        <v>9934</v>
+        <v>10130</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C42">
         <v>4210602</v>
@@ -2325,19 +2905,19 @@
         <v>41</v>
       </c>
       <c r="E42" s="2">
-        <v>46205</v>
+        <v>46216</v>
       </c>
       <c r="F42" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="G42">
-        <v>95300</v>
+        <v>72463</v>
       </c>
       <c r="H42">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="J42">
-        <v>95300</v>
+        <v>72463</v>
       </c>
       <c r="L42" t="s">
         <v>24</v>
@@ -2346,15 +2926,15 @@
         <v>4</v>
       </c>
       <c r="N42">
-        <v>9930</v>
+        <v>10136</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C43">
         <v>4210602</v>
@@ -2363,22 +2943,19 @@
         <v>41</v>
       </c>
       <c r="E43" s="2">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="G43">
-        <v>750000</v>
+        <v>100000</v>
       </c>
       <c r="H43">
-        <v>140</v>
-      </c>
-      <c r="I43" t="s">
-        <v>106</v>
+        <v>332</v>
       </c>
       <c r="J43">
-        <v>750000</v>
+        <v>100000</v>
       </c>
       <c r="L43" t="s">
         <v>24</v>
@@ -2387,15 +2964,15 @@
         <v>4</v>
       </c>
       <c r="N43">
-        <v>9930</v>
+        <v>9898</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C44">
         <v>4210602</v>
@@ -2404,19 +2981,19 @@
         <v>41</v>
       </c>
       <c r="E44" s="2">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F44" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="G44">
-        <v>89800</v>
+        <v>141500</v>
       </c>
       <c r="H44">
-        <v>240</v>
+        <v>132</v>
       </c>
       <c r="J44">
-        <v>89800</v>
+        <v>141500</v>
       </c>
       <c r="L44" t="s">
         <v>24</v>
@@ -2425,15 +3002,15 @@
         <v>4</v>
       </c>
       <c r="N44">
-        <v>9960</v>
+        <v>9923</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C45">
         <v>4210602</v>
@@ -2442,19 +3019,19 @@
         <v>41</v>
       </c>
       <c r="E45" s="2">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="F45" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="G45">
-        <v>74500</v>
+        <v>153917</v>
       </c>
       <c r="H45">
-        <v>331</v>
+        <v>232</v>
       </c>
       <c r="J45">
-        <v>74500</v>
+        <v>153917</v>
       </c>
       <c r="L45" t="s">
         <v>24</v>
@@ -2463,15 +3040,15 @@
         <v>4</v>
       </c>
       <c r="N45">
-        <v>9968</v>
+        <v>9952</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C46">
         <v>4210602</v>
@@ -2480,19 +3057,19 @@
         <v>41</v>
       </c>
       <c r="E46" s="2">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G46">
-        <v>75000</v>
-      </c>
-      <c r="H46" t="s">
-        <v>62</v>
+        <v>52666</v>
+      </c>
+      <c r="H46">
+        <v>332</v>
       </c>
       <c r="J46">
-        <v>75000</v>
+        <v>52666</v>
       </c>
       <c r="L46" t="s">
         <v>24</v>
@@ -2501,15 +3078,15 @@
         <v>4</v>
       </c>
       <c r="N46">
-        <v>9895</v>
+        <v>9969</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C47">
         <v>4210602</v>
@@ -2518,19 +3095,19 @@
         <v>41</v>
       </c>
       <c r="E47" s="2">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="F47" t="s">
-        <v>109</v>
+        <v>198</v>
       </c>
       <c r="G47">
-        <v>75000</v>
-      </c>
-      <c r="H47" t="s">
-        <v>110</v>
+        <v>96534</v>
+      </c>
+      <c r="H47">
+        <v>232</v>
       </c>
       <c r="J47">
-        <v>75000</v>
+        <v>96534</v>
       </c>
       <c r="L47" t="s">
         <v>24</v>
@@ -2539,15 +3116,15 @@
         <v>4</v>
       </c>
       <c r="N47">
-        <v>9917</v>
+        <v>10029</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C48">
         <v>4210602</v>
@@ -2556,19 +3133,19 @@
         <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>199</v>
       </c>
       <c r="G48">
-        <v>75000</v>
+        <v>248200</v>
       </c>
       <c r="H48" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="J48">
-        <v>75000</v>
+        <v>248200</v>
       </c>
       <c r="L48" t="s">
         <v>24</v>
@@ -2577,15 +3154,15 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>9947</v>
+        <v>10053</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C49">
         <v>4210602</v>
@@ -2594,19 +3171,19 @@
         <v>41</v>
       </c>
       <c r="E49" s="2">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="F49" t="s">
-        <v>112</v>
+        <v>201</v>
       </c>
       <c r="G49">
-        <v>75000</v>
+        <v>216300</v>
       </c>
       <c r="H49" t="s">
-        <v>113</v>
+        <v>202</v>
       </c>
       <c r="J49">
-        <v>75000</v>
+        <v>216300</v>
       </c>
       <c r="L49" t="s">
         <v>24</v>
@@ -2615,15 +3192,15 @@
         <v>4</v>
       </c>
       <c r="N49">
-        <v>9991</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C50">
         <v>4210602</v>
@@ -2632,19 +3209,19 @@
         <v>41</v>
       </c>
       <c r="E50" s="2">
-        <v>46205</v>
+        <v>46214</v>
       </c>
       <c r="F50" t="s">
-        <v>114</v>
+        <v>203</v>
       </c>
       <c r="G50">
-        <v>262767</v>
+        <v>120808</v>
       </c>
       <c r="H50" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="J50">
-        <v>262767</v>
+        <v>120808</v>
       </c>
       <c r="L50" t="s">
         <v>24</v>
@@ -2653,15 +3230,15 @@
         <v>4</v>
       </c>
       <c r="N50">
-        <v>9915</v>
+        <v>10122</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C51">
         <v>4210602</v>
@@ -2670,19 +3247,19 @@
         <v>41</v>
       </c>
       <c r="E51" s="2">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="F51" t="s">
-        <v>116</v>
+        <v>204</v>
       </c>
       <c r="G51">
-        <v>179809</v>
-      </c>
-      <c r="H51" t="s">
-        <v>36</v>
+        <v>203800</v>
+      </c>
+      <c r="H51">
+        <v>132</v>
       </c>
       <c r="J51">
-        <v>179809</v>
+        <v>203800</v>
       </c>
       <c r="L51" t="s">
         <v>24</v>
@@ -2691,220 +3268,227 @@
         <v>4</v>
       </c>
       <c r="N51">
-        <v>9939</v>
+        <v>10137</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>321</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="C52">
-        <v>4210803</v>
+        <v>4210602</v>
       </c>
       <c r="D52" t="s">
-        <v>118</v>
+        <v>41</v>
       </c>
       <c r="E52" s="2">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F52" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="G52">
-        <v>270253.5</v>
-      </c>
-      <c r="I52" t="s">
-        <v>120</v>
+        <v>110000</v>
+      </c>
+      <c r="H52">
+        <v>333</v>
       </c>
       <c r="J52">
-        <v>223350</v>
-      </c>
-      <c r="K52">
-        <v>46903.5</v>
+        <v>110000</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="N52">
+        <v>9899</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>355</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C53">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E53" s="2">
         <v>46204</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="G53">
-        <v>18000</v>
-      </c>
-      <c r="I53" t="s">
-        <v>68</v>
+        <v>40000</v>
+      </c>
+      <c r="H53">
+        <v>333</v>
       </c>
       <c r="J53">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="L53" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N53">
+        <v>9899</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>355</v>
+        <v>253</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C54">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E54" s="2">
         <v>46205</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G54">
-        <v>22500</v>
-      </c>
-      <c r="I54" t="s">
-        <v>70</v>
+        <v>131000</v>
+      </c>
+      <c r="H54">
+        <v>133</v>
       </c>
       <c r="J54">
-        <v>22500</v>
+        <v>131000</v>
       </c>
       <c r="L54" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N54">
+        <v>9924</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>355</v>
+        <v>253</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C55">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E55" s="2">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="F55" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="G55">
-        <v>21500</v>
-      </c>
-      <c r="I55" t="s">
-        <v>70</v>
+        <v>149000</v>
+      </c>
+      <c r="H55">
+        <v>233</v>
       </c>
       <c r="J55">
-        <v>21500</v>
+        <v>149000</v>
       </c>
       <c r="L55" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N55">
+        <v>9953</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>382</v>
+        <v>253</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="C56">
-        <v>4210101</v>
+        <v>4210602</v>
       </c>
       <c r="D56" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="E56" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F56" t="s">
+        <v>84</v>
+      </c>
+      <c r="G56">
+        <v>17500</v>
+      </c>
+      <c r="H56">
+        <v>233</v>
+      </c>
+      <c r="J56">
+        <v>17500</v>
+      </c>
+      <c r="L56" t="s">
+        <v>24</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>9953</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>253</v>
+      </c>
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57">
+        <v>4210602</v>
+      </c>
+      <c r="D57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" s="2">
         <v>46207</v>
       </c>
-      <c r="F56" t="s">
-        <v>124</v>
-      </c>
-      <c r="G56">
-        <v>150000</v>
-      </c>
-      <c r="H56">
-        <v>340</v>
-      </c>
-      <c r="I56" t="s">
-        <v>125</v>
-      </c>
-      <c r="J56">
-        <v>150000</v>
-      </c>
-      <c r="L56" t="s">
-        <v>24</v>
-      </c>
-      <c r="M56">
-        <v>4</v>
-      </c>
-      <c r="N56">
-        <v>9977</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>382</v>
-      </c>
-      <c r="B57" t="s">
-        <v>122</v>
-      </c>
-      <c r="C57">
-        <v>4210101</v>
-      </c>
-      <c r="D57" t="s">
-        <v>123</v>
-      </c>
-      <c r="E57" s="2">
-        <v>46209</v>
-      </c>
       <c r="F57" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="G57">
-        <v>254000</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>127</v>
-      </c>
+        <v>52000</v>
+      </c>
+      <c r="H57">
+        <v>333</v>
+      </c>
+      <c r="I57" s="1"/>
       <c r="J57">
-        <v>254000</v>
+        <v>52000</v>
       </c>
       <c r="L57" t="s">
         <v>24</v>
@@ -2912,506 +3496,4685 @@
       <c r="M57">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="N57">
+        <v>9970</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>382</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="C58">
-        <v>4210101</v>
+        <v>4210602</v>
       </c>
       <c r="D58" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="E58" s="2">
         <v>46209</v>
       </c>
       <c r="F58" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="G58">
-        <v>115000</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>129</v>
-      </c>
+        <v>102000</v>
+      </c>
+      <c r="H58">
+        <v>133</v>
+      </c>
+      <c r="I58" s="1"/>
       <c r="J58">
-        <v>115000</v>
+        <v>102000</v>
       </c>
       <c r="L58" t="s">
         <v>24</v>
       </c>
       <c r="M58">
         <v>4</v>
+      </c>
+      <c r="N58">
+        <v>10005</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>396</v>
+        <v>253</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C59">
-        <v>4210301</v>
+        <v>4210602</v>
       </c>
       <c r="D59" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E59" s="2">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="F59" t="s">
-        <v>74</v>
+        <v>207</v>
       </c>
       <c r="G59">
-        <v>98000</v>
-      </c>
-      <c r="I59" t="s">
-        <v>75</v>
+        <v>192500</v>
+      </c>
+      <c r="H59">
+        <v>233</v>
       </c>
       <c r="J59">
-        <v>98000</v>
+        <v>192500</v>
       </c>
       <c r="L59" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N59">
+        <v>10030</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
+        <v>253</v>
+      </c>
+      <c r="B60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60">
+        <v>4210602</v>
+      </c>
+      <c r="D60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F60" t="s">
+        <v>208</v>
+      </c>
+      <c r="G60">
+        <v>230000</v>
+      </c>
+      <c r="H60" t="s">
+        <v>163</v>
+      </c>
+      <c r="J60">
+        <v>230000</v>
+      </c>
+      <c r="L60" t="s">
+        <v>24</v>
+      </c>
+      <c r="M60">
+        <v>4</v>
+      </c>
+      <c r="N60">
+        <v>10054</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>253</v>
+      </c>
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61">
+        <v>4210602</v>
+      </c>
+      <c r="D61" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F61" t="s">
+        <v>209</v>
+      </c>
+      <c r="G61">
+        <v>120000</v>
+      </c>
+      <c r="H61" t="s">
+        <v>163</v>
+      </c>
+      <c r="J61">
+        <v>120000</v>
+      </c>
+      <c r="L61" t="s">
+        <v>24</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61">
+        <v>10123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>253</v>
+      </c>
+      <c r="B62" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62">
+        <v>4210602</v>
+      </c>
+      <c r="D62" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F62" t="s">
+        <v>210</v>
+      </c>
+      <c r="G62">
+        <v>60000</v>
+      </c>
+      <c r="H62" t="s">
+        <v>163</v>
+      </c>
+      <c r="J62">
+        <v>60000</v>
+      </c>
+      <c r="L62" t="s">
+        <v>24</v>
+      </c>
+      <c r="M62">
+        <v>4</v>
+      </c>
+      <c r="N62">
+        <v>10123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>253</v>
+      </c>
+      <c r="B63" t="s">
+        <v>45</v>
+      </c>
+      <c r="C63">
+        <v>4210602</v>
+      </c>
+      <c r="D63" t="s">
+        <v>41</v>
+      </c>
+      <c r="E63" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F63" t="s">
+        <v>211</v>
+      </c>
+      <c r="G63">
+        <v>120000</v>
+      </c>
+      <c r="H63">
+        <v>133</v>
+      </c>
+      <c r="J63">
+        <v>120000</v>
+      </c>
+      <c r="L63" t="s">
+        <v>24</v>
+      </c>
+      <c r="M63">
+        <v>4</v>
+      </c>
+      <c r="N63">
+        <v>10138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>254</v>
+      </c>
+      <c r="B64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64">
+        <v>4210602</v>
+      </c>
+      <c r="D64" t="s">
+        <v>41</v>
+      </c>
+      <c r="E64" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F64" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64">
+        <v>102615</v>
+      </c>
+      <c r="H64">
+        <v>334</v>
+      </c>
+      <c r="J64">
+        <v>102615</v>
+      </c>
+      <c r="L64" t="s">
+        <v>24</v>
+      </c>
+      <c r="M64">
+        <v>4</v>
+      </c>
+      <c r="N64">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>254</v>
+      </c>
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65">
+        <v>4210602</v>
+      </c>
+      <c r="D65" t="s">
+        <v>41</v>
+      </c>
+      <c r="E65" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F65" t="s">
+        <v>85</v>
+      </c>
+      <c r="G65">
+        <v>162500</v>
+      </c>
+      <c r="H65" t="s">
+        <v>86</v>
+      </c>
+      <c r="J65">
+        <v>162500</v>
+      </c>
+      <c r="L65" t="s">
+        <v>24</v>
+      </c>
+      <c r="M65">
+        <v>4</v>
+      </c>
+      <c r="N65">
+        <v>9916</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>254</v>
+      </c>
+      <c r="B66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66">
+        <v>4210602</v>
+      </c>
+      <c r="D66" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F66" t="s">
+        <v>87</v>
+      </c>
+      <c r="G66">
+        <v>118952</v>
+      </c>
+      <c r="H66">
+        <v>234</v>
+      </c>
+      <c r="J66">
+        <v>118952</v>
+      </c>
+      <c r="L66" t="s">
+        <v>24</v>
+      </c>
+      <c r="M66">
+        <v>4</v>
+      </c>
+      <c r="N66">
+        <v>9954</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>254</v>
+      </c>
+      <c r="B67" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67">
+        <v>4210602</v>
+      </c>
+      <c r="D67" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F67" t="s">
+        <v>212</v>
+      </c>
+      <c r="G67">
+        <v>97721</v>
+      </c>
+      <c r="H67">
+        <v>338</v>
+      </c>
+      <c r="J67">
+        <v>97721</v>
+      </c>
+      <c r="L67" t="s">
+        <v>24</v>
+      </c>
+      <c r="M67">
+        <v>4</v>
+      </c>
+      <c r="N67">
+        <v>9975</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>254</v>
+      </c>
+      <c r="B68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68">
+        <v>4210602</v>
+      </c>
+      <c r="D68" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F68" t="s">
+        <v>213</v>
+      </c>
+      <c r="G68">
+        <v>40562</v>
+      </c>
+      <c r="H68">
+        <v>134</v>
+      </c>
+      <c r="J68">
+        <v>40562</v>
+      </c>
+      <c r="L68" t="s">
+        <v>24</v>
+      </c>
+      <c r="M68">
+        <v>4</v>
+      </c>
+      <c r="N68">
+        <v>10006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>254</v>
+      </c>
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69">
+        <v>4210602</v>
+      </c>
+      <c r="D69" t="s">
+        <v>41</v>
+      </c>
+      <c r="E69" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F69" t="s">
+        <v>214</v>
+      </c>
+      <c r="G69">
+        <v>55516</v>
+      </c>
+      <c r="H69">
+        <v>234</v>
+      </c>
+      <c r="J69">
+        <v>55516</v>
+      </c>
+      <c r="L69" t="s">
+        <v>24</v>
+      </c>
+      <c r="M69">
+        <v>4</v>
+      </c>
+      <c r="N69">
+        <v>10031</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>254</v>
+      </c>
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70">
+        <v>4210602</v>
+      </c>
+      <c r="D70" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F70" t="s">
+        <v>215</v>
+      </c>
+      <c r="G70">
+        <v>86777</v>
+      </c>
+      <c r="H70" t="s">
+        <v>216</v>
+      </c>
+      <c r="J70">
+        <v>86777</v>
+      </c>
+      <c r="L70" t="s">
+        <v>24</v>
+      </c>
+      <c r="M70">
+        <v>4</v>
+      </c>
+      <c r="N70">
+        <v>10055</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>254</v>
+      </c>
+      <c r="B71" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71">
+        <v>4210602</v>
+      </c>
+      <c r="D71" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F71" t="s">
+        <v>217</v>
+      </c>
+      <c r="G71">
+        <v>69310</v>
+      </c>
+      <c r="H71" t="s">
+        <v>218</v>
+      </c>
+      <c r="J71">
+        <v>69310</v>
+      </c>
+      <c r="L71" t="s">
+        <v>24</v>
+      </c>
+      <c r="M71">
+        <v>4</v>
+      </c>
+      <c r="N71">
+        <v>10083</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>254</v>
+      </c>
+      <c r="B72" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72">
+        <v>4210602</v>
+      </c>
+      <c r="D72" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F72" t="s">
+        <v>219</v>
+      </c>
+      <c r="G72">
+        <v>134461</v>
+      </c>
+      <c r="H72">
+        <v>328</v>
+      </c>
+      <c r="J72">
+        <v>134461</v>
+      </c>
+      <c r="L72" t="s">
+        <v>24</v>
+      </c>
+      <c r="M72">
+        <v>4</v>
+      </c>
+      <c r="N72">
+        <v>10128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>254</v>
+      </c>
+      <c r="B73" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73">
+        <v>4210602</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F73" t="s">
+        <v>220</v>
+      </c>
+      <c r="G73">
+        <v>98450</v>
+      </c>
+      <c r="H73">
+        <v>134</v>
+      </c>
+      <c r="J73">
+        <v>98450</v>
+      </c>
+      <c r="L73" t="s">
+        <v>24</v>
+      </c>
+      <c r="M73">
+        <v>4</v>
+      </c>
+      <c r="N73">
+        <v>10139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>255</v>
+      </c>
+      <c r="B74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C74">
+        <v>4210602</v>
+      </c>
+      <c r="D74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F74" t="s">
+        <v>51</v>
+      </c>
+      <c r="G74">
+        <v>86962</v>
+      </c>
+      <c r="H74">
+        <v>335</v>
+      </c>
+      <c r="J74">
+        <v>86962</v>
+      </c>
+      <c r="L74" t="s">
+        <v>24</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>9901</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>255</v>
+      </c>
+      <c r="B75" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75">
+        <v>4210602</v>
+      </c>
+      <c r="D75" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F75" t="s">
+        <v>88</v>
+      </c>
+      <c r="G75">
+        <v>92879.86</v>
+      </c>
+      <c r="H75">
+        <v>135</v>
+      </c>
+      <c r="J75">
+        <v>92879.86</v>
+      </c>
+      <c r="L75" t="s">
+        <v>24</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <v>9925</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>255</v>
+      </c>
+      <c r="B76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76">
+        <v>4210602</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F76" t="s">
+        <v>89</v>
+      </c>
+      <c r="G76">
+        <v>122626</v>
+      </c>
+      <c r="H76">
+        <v>235</v>
+      </c>
+      <c r="J76">
+        <v>122626</v>
+      </c>
+      <c r="L76" t="s">
+        <v>24</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>9955</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>255</v>
+      </c>
+      <c r="B77" t="s">
+        <v>50</v>
+      </c>
+      <c r="C77">
+        <v>4210602</v>
+      </c>
+      <c r="D77" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F77" t="s">
+        <v>221</v>
+      </c>
+      <c r="G77">
+        <v>95914.57</v>
+      </c>
+      <c r="H77">
+        <v>335</v>
+      </c>
+      <c r="J77">
+        <v>95914.57</v>
+      </c>
+      <c r="L77" t="s">
+        <v>24</v>
+      </c>
+      <c r="M77">
+        <v>4</v>
+      </c>
+      <c r="N77">
+        <v>9972</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>255</v>
+      </c>
+      <c r="B78" t="s">
+        <v>50</v>
+      </c>
+      <c r="C78">
+        <v>4210602</v>
+      </c>
+      <c r="D78" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F78" t="s">
+        <v>222</v>
+      </c>
+      <c r="G78">
+        <v>129860.52</v>
+      </c>
+      <c r="H78">
+        <v>135</v>
+      </c>
+      <c r="J78">
+        <v>129860.52</v>
+      </c>
+      <c r="L78" t="s">
+        <v>24</v>
+      </c>
+      <c r="M78">
+        <v>4</v>
+      </c>
+      <c r="N78">
+        <v>10007</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>255</v>
+      </c>
+      <c r="B79" t="s">
+        <v>50</v>
+      </c>
+      <c r="C79">
+        <v>4210602</v>
+      </c>
+      <c r="D79" t="s">
+        <v>41</v>
+      </c>
+      <c r="E79" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F79" t="s">
+        <v>223</v>
+      </c>
+      <c r="G79">
+        <v>113935</v>
+      </c>
+      <c r="H79">
+        <v>235</v>
+      </c>
+      <c r="J79">
+        <v>113935</v>
+      </c>
+      <c r="L79" t="s">
+        <v>24</v>
+      </c>
+      <c r="M79">
+        <v>4</v>
+      </c>
+      <c r="N79">
+        <v>10032</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>255</v>
+      </c>
+      <c r="B80" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80">
+        <v>4210602</v>
+      </c>
+      <c r="D80" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F80" t="s">
+        <v>224</v>
+      </c>
+      <c r="G80">
+        <v>70877</v>
+      </c>
+      <c r="H80" t="s">
+        <v>225</v>
+      </c>
+      <c r="J80">
+        <v>70877</v>
+      </c>
+      <c r="L80" t="s">
+        <v>24</v>
+      </c>
+      <c r="M80">
+        <v>4</v>
+      </c>
+      <c r="N80">
+        <v>10056</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>255</v>
+      </c>
+      <c r="B81" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81">
+        <v>4210602</v>
+      </c>
+      <c r="D81" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F81" t="s">
+        <v>226</v>
+      </c>
+      <c r="G81">
+        <v>132299.85999999999</v>
+      </c>
+      <c r="H81" t="s">
+        <v>227</v>
+      </c>
+      <c r="J81">
+        <v>132299.85999999999</v>
+      </c>
+      <c r="L81" t="s">
+        <v>24</v>
+      </c>
+      <c r="M81">
+        <v>4</v>
+      </c>
+      <c r="N81">
+        <v>10084</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>255</v>
+      </c>
+      <c r="B82" t="s">
+        <v>50</v>
+      </c>
+      <c r="C82">
+        <v>4210602</v>
+      </c>
+      <c r="D82" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F82" t="s">
+        <v>228</v>
+      </c>
+      <c r="G82">
+        <v>209579</v>
+      </c>
+      <c r="H82" t="s">
+        <v>225</v>
+      </c>
+      <c r="J82">
+        <v>209579</v>
+      </c>
+      <c r="L82" t="s">
+        <v>24</v>
+      </c>
+      <c r="M82">
+        <v>4</v>
+      </c>
+      <c r="N82">
+        <v>10125</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>256</v>
+      </c>
+      <c r="B83" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83">
+        <v>4210602</v>
+      </c>
+      <c r="D83" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F83" t="s">
+        <v>90</v>
+      </c>
+      <c r="G83">
+        <v>77471.83</v>
+      </c>
+      <c r="H83">
+        <v>336</v>
+      </c>
+      <c r="J83">
+        <v>77471.83</v>
+      </c>
+      <c r="L83" t="s">
+        <v>24</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83">
+        <v>9902</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>256</v>
+      </c>
+      <c r="B84" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84">
+        <v>4210602</v>
+      </c>
+      <c r="D84" t="s">
+        <v>41</v>
+      </c>
+      <c r="E84" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F84" t="s">
+        <v>91</v>
+      </c>
+      <c r="G84">
+        <v>186377</v>
+      </c>
+      <c r="H84">
+        <v>136</v>
+      </c>
+      <c r="J84">
+        <v>186377</v>
+      </c>
+      <c r="L84" t="s">
+        <v>24</v>
+      </c>
+      <c r="M84">
+        <v>4</v>
+      </c>
+      <c r="N84">
+        <v>9926</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>256</v>
+      </c>
+      <c r="B85" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85">
+        <v>4210602</v>
+      </c>
+      <c r="D85" t="s">
+        <v>41</v>
+      </c>
+      <c r="E85" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F85" t="s">
+        <v>92</v>
+      </c>
+      <c r="G85">
+        <v>118885</v>
+      </c>
+      <c r="H85">
+        <v>236</v>
+      </c>
+      <c r="J85">
+        <v>118885</v>
+      </c>
+      <c r="L85" t="s">
+        <v>24</v>
+      </c>
+      <c r="M85">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <v>9956</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>256</v>
+      </c>
+      <c r="B86" t="s">
+        <v>52</v>
+      </c>
+      <c r="C86">
+        <v>4210602</v>
+      </c>
+      <c r="D86" t="s">
+        <v>41</v>
+      </c>
+      <c r="E86" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F86" t="s">
+        <v>93</v>
+      </c>
+      <c r="G86">
+        <v>99674.94</v>
+      </c>
+      <c r="H86">
+        <v>336</v>
+      </c>
+      <c r="J86">
+        <v>99674.94</v>
+      </c>
+      <c r="L86" t="s">
+        <v>24</v>
+      </c>
+      <c r="M86">
+        <v>4</v>
+      </c>
+      <c r="N86">
+        <v>9973</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>256</v>
+      </c>
+      <c r="B87" t="s">
+        <v>52</v>
+      </c>
+      <c r="C87">
+        <v>4210602</v>
+      </c>
+      <c r="D87" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F87" t="s">
+        <v>229</v>
+      </c>
+      <c r="G87">
+        <v>109011</v>
+      </c>
+      <c r="H87">
+        <v>136</v>
+      </c>
+      <c r="J87">
+        <v>109011</v>
+      </c>
+      <c r="L87" t="s">
+        <v>24</v>
+      </c>
+      <c r="M87">
+        <v>4</v>
+      </c>
+      <c r="N87">
+        <v>10008</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>256</v>
+      </c>
+      <c r="B88" t="s">
+        <v>52</v>
+      </c>
+      <c r="C88">
+        <v>4210602</v>
+      </c>
+      <c r="D88" t="s">
+        <v>41</v>
+      </c>
+      <c r="E88" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F88" t="s">
+        <v>230</v>
+      </c>
+      <c r="G88">
+        <v>101543</v>
+      </c>
+      <c r="H88">
+        <v>236</v>
+      </c>
+      <c r="J88">
+        <v>101543</v>
+      </c>
+      <c r="L88" t="s">
+        <v>24</v>
+      </c>
+      <c r="M88">
+        <v>4</v>
+      </c>
+      <c r="N88">
+        <v>10033</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>256</v>
+      </c>
+      <c r="B89" t="s">
+        <v>52</v>
+      </c>
+      <c r="C89">
+        <v>4210602</v>
+      </c>
+      <c r="D89" t="s">
+        <v>41</v>
+      </c>
+      <c r="E89" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F89" t="s">
+        <v>231</v>
+      </c>
+      <c r="G89">
+        <v>112447</v>
+      </c>
+      <c r="H89">
+        <v>326</v>
+      </c>
+      <c r="J89">
+        <v>112447</v>
+      </c>
+      <c r="L89" t="s">
+        <v>24</v>
+      </c>
+      <c r="M89">
+        <v>4</v>
+      </c>
+      <c r="N89">
+        <v>10057</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>256</v>
+      </c>
+      <c r="B90" t="s">
+        <v>52</v>
+      </c>
+      <c r="C90">
+        <v>4210602</v>
+      </c>
+      <c r="D90" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F90" t="s">
+        <v>232</v>
+      </c>
+      <c r="G90">
+        <v>125948</v>
+      </c>
+      <c r="H90">
+        <v>226</v>
+      </c>
+      <c r="J90">
+        <v>125948</v>
+      </c>
+      <c r="L90" t="s">
+        <v>24</v>
+      </c>
+      <c r="M90">
+        <v>4</v>
+      </c>
+      <c r="N90">
+        <v>10085</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>256</v>
+      </c>
+      <c r="B91" t="s">
+        <v>52</v>
+      </c>
+      <c r="C91">
+        <v>4210602</v>
+      </c>
+      <c r="D91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F91" t="s">
+        <v>233</v>
+      </c>
+      <c r="G91">
+        <v>193390.47</v>
+      </c>
+      <c r="H91">
+        <v>326</v>
+      </c>
+      <c r="J91">
+        <v>193390.47</v>
+      </c>
+      <c r="L91" t="s">
+        <v>24</v>
+      </c>
+      <c r="M91">
+        <v>4</v>
+      </c>
+      <c r="N91">
+        <v>10126</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>256</v>
+      </c>
+      <c r="B92" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92">
+        <v>4210602</v>
+      </c>
+      <c r="D92" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F92" t="s">
+        <v>234</v>
+      </c>
+      <c r="G92">
+        <v>143423.23000000001</v>
+      </c>
+      <c r="H92">
+        <v>136</v>
+      </c>
+      <c r="J92">
+        <v>143423.23000000001</v>
+      </c>
+      <c r="L92" t="s">
+        <v>24</v>
+      </c>
+      <c r="M92">
+        <v>4</v>
+      </c>
+      <c r="N92">
+        <v>10141</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>257</v>
+      </c>
+      <c r="B93" t="s">
+        <v>53</v>
+      </c>
+      <c r="C93">
+        <v>4210602</v>
+      </c>
+      <c r="D93" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F93" t="s">
+        <v>54</v>
+      </c>
+      <c r="G93">
+        <v>132990</v>
+      </c>
+      <c r="H93">
+        <v>337</v>
+      </c>
+      <c r="J93">
+        <v>132990</v>
+      </c>
+      <c r="L93" t="s">
+        <v>24</v>
+      </c>
+      <c r="M93">
+        <v>4</v>
+      </c>
+      <c r="N93">
+        <v>9903</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>257</v>
+      </c>
+      <c r="B94" t="s">
+        <v>53</v>
+      </c>
+      <c r="C94">
+        <v>4210602</v>
+      </c>
+      <c r="D94" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F94" t="s">
+        <v>94</v>
+      </c>
+      <c r="G94">
+        <v>80018</v>
+      </c>
+      <c r="H94">
+        <v>137</v>
+      </c>
+      <c r="J94">
+        <v>80018</v>
+      </c>
+      <c r="L94" t="s">
+        <v>24</v>
+      </c>
+      <c r="M94">
+        <v>4</v>
+      </c>
+      <c r="N94">
+        <v>9927</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>257</v>
+      </c>
+      <c r="B95" t="s">
+        <v>53</v>
+      </c>
+      <c r="C95">
+        <v>4210602</v>
+      </c>
+      <c r="D95" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F95" t="s">
+        <v>95</v>
+      </c>
+      <c r="G95">
+        <v>158158</v>
+      </c>
+      <c r="H95">
+        <v>237</v>
+      </c>
+      <c r="J95">
+        <v>158158</v>
+      </c>
+      <c r="L95" t="s">
+        <v>24</v>
+      </c>
+      <c r="M95">
+        <v>4</v>
+      </c>
+      <c r="N95">
+        <v>9957</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>257</v>
+      </c>
+      <c r="B96" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96">
+        <v>4210602</v>
+      </c>
+      <c r="D96" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F96" t="s">
+        <v>235</v>
+      </c>
+      <c r="G96">
+        <v>56540</v>
+      </c>
+      <c r="J96">
+        <v>56540</v>
+      </c>
+      <c r="L96" t="s">
+        <v>24</v>
+      </c>
+      <c r="M96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>257</v>
+      </c>
+      <c r="B97" t="s">
+        <v>53</v>
+      </c>
+      <c r="C97">
+        <v>4210602</v>
+      </c>
+      <c r="D97" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F97" t="s">
+        <v>236</v>
+      </c>
+      <c r="G97">
+        <v>49202</v>
+      </c>
+      <c r="H97">
+        <v>137</v>
+      </c>
+      <c r="J97">
+        <v>49202</v>
+      </c>
+      <c r="L97" t="s">
+        <v>24</v>
+      </c>
+      <c r="M97">
+        <v>4</v>
+      </c>
+      <c r="N97">
+        <v>10009</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>257</v>
+      </c>
+      <c r="B98" t="s">
+        <v>53</v>
+      </c>
+      <c r="C98">
+        <v>4210602</v>
+      </c>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F98" t="s">
+        <v>237</v>
+      </c>
+      <c r="G98">
+        <v>86214</v>
+      </c>
+      <c r="H98">
+        <v>237</v>
+      </c>
+      <c r="J98">
+        <v>86214</v>
+      </c>
+      <c r="L98" t="s">
+        <v>24</v>
+      </c>
+      <c r="M98">
+        <v>4</v>
+      </c>
+      <c r="N98">
+        <v>10034</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>257</v>
+      </c>
+      <c r="B99" t="s">
+        <v>53</v>
+      </c>
+      <c r="C99">
+        <v>4210602</v>
+      </c>
+      <c r="D99" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F99" t="s">
+        <v>238</v>
+      </c>
+      <c r="G99">
+        <v>137613</v>
+      </c>
+      <c r="H99">
+        <v>327</v>
+      </c>
+      <c r="J99">
+        <v>137613</v>
+      </c>
+      <c r="L99" t="s">
+        <v>24</v>
+      </c>
+      <c r="M99">
+        <v>4</v>
+      </c>
+      <c r="N99">
+        <v>10058</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>257</v>
+      </c>
+      <c r="B100" t="s">
+        <v>53</v>
+      </c>
+      <c r="C100">
+        <v>4210602</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F100" t="s">
+        <v>239</v>
+      </c>
+      <c r="G100">
+        <v>131430</v>
+      </c>
+      <c r="H100">
+        <v>227</v>
+      </c>
+      <c r="J100">
+        <v>131430</v>
+      </c>
+      <c r="L100" t="s">
+        <v>24</v>
+      </c>
+      <c r="M100">
+        <v>4</v>
+      </c>
+      <c r="N100">
+        <v>10086</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>257</v>
+      </c>
+      <c r="B101" t="s">
+        <v>53</v>
+      </c>
+      <c r="C101">
+        <v>4210602</v>
+      </c>
+      <c r="D101" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F101" t="s">
+        <v>240</v>
+      </c>
+      <c r="G101">
+        <v>263679.33</v>
+      </c>
+      <c r="H101">
+        <v>327</v>
+      </c>
+      <c r="J101">
+        <v>263679.33</v>
+      </c>
+      <c r="L101" t="s">
+        <v>24</v>
+      </c>
+      <c r="M101">
+        <v>4</v>
+      </c>
+      <c r="N101">
+        <v>10127</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>257</v>
+      </c>
+      <c r="B102" t="s">
+        <v>53</v>
+      </c>
+      <c r="C102">
+        <v>4210602</v>
+      </c>
+      <c r="D102" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F102" t="s">
+        <v>241</v>
+      </c>
+      <c r="G102">
+        <v>38905</v>
+      </c>
+      <c r="H102">
+        <v>137</v>
+      </c>
+      <c r="J102">
+        <v>38905</v>
+      </c>
+      <c r="L102" t="s">
+        <v>24</v>
+      </c>
+      <c r="M102">
+        <v>4</v>
+      </c>
+      <c r="N102">
+        <v>10142</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>258</v>
+      </c>
+      <c r="B103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C103">
+        <v>4210602</v>
+      </c>
+      <c r="D103" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F103" t="s">
+        <v>96</v>
+      </c>
+      <c r="G103">
+        <v>89861.83</v>
+      </c>
+      <c r="H103">
+        <v>338</v>
+      </c>
+      <c r="J103">
+        <v>89861.83</v>
+      </c>
+      <c r="L103" t="s">
+        <v>24</v>
+      </c>
+      <c r="M103">
+        <v>4</v>
+      </c>
+      <c r="N103">
+        <v>9904</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>258</v>
+      </c>
+      <c r="B104" t="s">
+        <v>55</v>
+      </c>
+      <c r="C104">
+        <v>4210602</v>
+      </c>
+      <c r="D104" t="s">
+        <v>41</v>
+      </c>
+      <c r="E104" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F104" t="s">
+        <v>97</v>
+      </c>
+      <c r="G104">
+        <v>108359.99</v>
+      </c>
+      <c r="H104">
+        <v>138</v>
+      </c>
+      <c r="J104">
+        <v>108359.99</v>
+      </c>
+      <c r="L104" t="s">
+        <v>24</v>
+      </c>
+      <c r="M104">
+        <v>4</v>
+      </c>
+      <c r="N104">
+        <v>9928</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>258</v>
+      </c>
+      <c r="B105" t="s">
+        <v>55</v>
+      </c>
+      <c r="C105">
+        <v>4210602</v>
+      </c>
+      <c r="D105" t="s">
+        <v>41</v>
+      </c>
+      <c r="E105" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F105" t="s">
+        <v>98</v>
+      </c>
+      <c r="G105">
+        <v>105720.54</v>
+      </c>
+      <c r="H105">
+        <v>238</v>
+      </c>
+      <c r="J105">
+        <v>105720.54</v>
+      </c>
+      <c r="L105" t="s">
+        <v>24</v>
+      </c>
+      <c r="M105">
+        <v>4</v>
+      </c>
+      <c r="N105">
+        <v>9958</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>258</v>
+      </c>
+      <c r="B106" t="s">
+        <v>55</v>
+      </c>
+      <c r="C106">
+        <v>4210602</v>
+      </c>
+      <c r="D106" t="s">
+        <v>41</v>
+      </c>
+      <c r="E106" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F106" t="s">
+        <v>242</v>
+      </c>
+      <c r="G106">
+        <v>124926</v>
+      </c>
+      <c r="H106">
+        <v>138</v>
+      </c>
+      <c r="J106">
+        <v>124926</v>
+      </c>
+      <c r="L106" t="s">
+        <v>24</v>
+      </c>
+      <c r="M106">
+        <v>4</v>
+      </c>
+      <c r="N106">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>258</v>
+      </c>
+      <c r="B107" t="s">
+        <v>55</v>
+      </c>
+      <c r="C107">
+        <v>4210602</v>
+      </c>
+      <c r="D107" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F107" t="s">
+        <v>243</v>
+      </c>
+      <c r="G107">
+        <v>50693</v>
+      </c>
+      <c r="H107">
+        <v>334</v>
+      </c>
+      <c r="J107">
+        <v>50693</v>
+      </c>
+      <c r="L107" t="s">
+        <v>24</v>
+      </c>
+      <c r="M107">
+        <v>4</v>
+      </c>
+      <c r="N107">
+        <v>9971</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>258</v>
+      </c>
+      <c r="B108" t="s">
+        <v>55</v>
+      </c>
+      <c r="C108">
+        <v>4210602</v>
+      </c>
+      <c r="D108" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F108" t="s">
+        <v>244</v>
+      </c>
+      <c r="G108">
+        <v>131777.14000000001</v>
+      </c>
+      <c r="H108">
+        <v>238</v>
+      </c>
+      <c r="J108">
+        <v>131777.14000000001</v>
+      </c>
+      <c r="L108" t="s">
+        <v>24</v>
+      </c>
+      <c r="M108">
+        <v>4</v>
+      </c>
+      <c r="N108">
+        <v>10035</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>258</v>
+      </c>
+      <c r="B109" t="s">
+        <v>55</v>
+      </c>
+      <c r="C109">
+        <v>4210602</v>
+      </c>
+      <c r="D109" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F109" t="s">
+        <v>245</v>
+      </c>
+      <c r="G109">
+        <v>98948</v>
+      </c>
+      <c r="H109">
+        <v>328</v>
+      </c>
+      <c r="J109">
+        <v>98948</v>
+      </c>
+      <c r="L109" t="s">
+        <v>24</v>
+      </c>
+      <c r="M109">
+        <v>4</v>
+      </c>
+      <c r="N109">
+        <v>10059</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>258</v>
+      </c>
+      <c r="B110" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110">
+        <v>4210602</v>
+      </c>
+      <c r="D110" t="s">
+        <v>41</v>
+      </c>
+      <c r="E110" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F110" t="s">
+        <v>246</v>
+      </c>
+      <c r="G110">
+        <v>92160</v>
+      </c>
+      <c r="H110">
+        <v>228</v>
+      </c>
+      <c r="J110">
+        <v>92160</v>
+      </c>
+      <c r="L110" t="s">
+        <v>24</v>
+      </c>
+      <c r="M110">
+        <v>4</v>
+      </c>
+      <c r="N110">
+        <v>10087</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>258</v>
+      </c>
+      <c r="B111" t="s">
+        <v>55</v>
+      </c>
+      <c r="C111">
+        <v>4210602</v>
+      </c>
+      <c r="D111" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F111" t="s">
+        <v>247</v>
+      </c>
+      <c r="G111">
+        <v>46101.58</v>
+      </c>
+      <c r="H111" t="s">
+        <v>216</v>
+      </c>
+      <c r="J111">
+        <v>46101.58</v>
+      </c>
+      <c r="L111" t="s">
+        <v>24</v>
+      </c>
+      <c r="M111">
+        <v>4</v>
+      </c>
+      <c r="N111">
+        <v>10124</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>258</v>
+      </c>
+      <c r="B112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112">
+        <v>4210602</v>
+      </c>
+      <c r="D112" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F112" t="s">
+        <v>248</v>
+      </c>
+      <c r="G112">
+        <v>156890.20000000001</v>
+      </c>
+      <c r="H112">
+        <v>138</v>
+      </c>
+      <c r="J112">
+        <v>156890.20000000001</v>
+      </c>
+      <c r="L112" t="s">
+        <v>24</v>
+      </c>
+      <c r="M112">
+        <v>4</v>
+      </c>
+      <c r="N112">
+        <v>10143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>259</v>
+      </c>
+      <c r="B113" t="s">
+        <v>56</v>
+      </c>
+      <c r="C113">
+        <v>4210602</v>
+      </c>
+      <c r="D113" t="s">
+        <v>41</v>
+      </c>
+      <c r="E113" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F113" t="s">
+        <v>99</v>
+      </c>
+      <c r="G113">
+        <v>114052</v>
+      </c>
+      <c r="H113">
+        <v>139</v>
+      </c>
+      <c r="J113">
+        <v>114052</v>
+      </c>
+      <c r="L113" t="s">
+        <v>24</v>
+      </c>
+      <c r="M113">
+        <v>4</v>
+      </c>
+      <c r="N113">
+        <v>9929</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>259</v>
+      </c>
+      <c r="B114" t="s">
+        <v>56</v>
+      </c>
+      <c r="C114">
+        <v>4210602</v>
+      </c>
+      <c r="D114" t="s">
+        <v>41</v>
+      </c>
+      <c r="E114" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F114" t="s">
+        <v>100</v>
+      </c>
+      <c r="G114">
+        <v>90086</v>
+      </c>
+      <c r="H114">
+        <v>239</v>
+      </c>
+      <c r="J114">
+        <v>90086</v>
+      </c>
+      <c r="L114" t="s">
+        <v>24</v>
+      </c>
+      <c r="M114">
+        <v>4</v>
+      </c>
+      <c r="N114">
+        <v>9959</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>259</v>
+      </c>
+      <c r="B115" t="s">
+        <v>56</v>
+      </c>
+      <c r="C115">
+        <v>4210602</v>
+      </c>
+      <c r="D115" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F115" t="s">
+        <v>101</v>
+      </c>
+      <c r="G115">
+        <v>156498</v>
+      </c>
+      <c r="H115">
+        <v>339</v>
+      </c>
+      <c r="J115">
+        <v>156498</v>
+      </c>
+      <c r="L115" t="s">
+        <v>24</v>
+      </c>
+      <c r="M115">
+        <v>4</v>
+      </c>
+      <c r="N115">
+        <v>9976</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>259</v>
+      </c>
+      <c r="B116" t="s">
+        <v>56</v>
+      </c>
+      <c r="C116">
+        <v>4210602</v>
+      </c>
+      <c r="D116" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F116" t="s">
+        <v>249</v>
+      </c>
+      <c r="G116">
+        <v>96232</v>
+      </c>
+      <c r="H116">
+        <v>139</v>
+      </c>
+      <c r="J116">
+        <v>96232</v>
+      </c>
+      <c r="L116" t="s">
+        <v>24</v>
+      </c>
+      <c r="M116">
+        <v>4</v>
+      </c>
+      <c r="N116">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>259</v>
+      </c>
+      <c r="B117" t="s">
+        <v>56</v>
+      </c>
+      <c r="C117">
+        <v>4210602</v>
+      </c>
+      <c r="D117" t="s">
+        <v>41</v>
+      </c>
+      <c r="E117" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F117" t="s">
+        <v>250</v>
+      </c>
+      <c r="G117">
+        <v>67621</v>
+      </c>
+      <c r="H117">
+        <v>131</v>
+      </c>
+      <c r="J117">
+        <v>67621</v>
+      </c>
+      <c r="L117" t="s">
+        <v>24</v>
+      </c>
+      <c r="M117">
+        <v>4</v>
+      </c>
+      <c r="N117">
+        <v>10004</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>259</v>
+      </c>
+      <c r="B118" t="s">
+        <v>56</v>
+      </c>
+      <c r="C118">
+        <v>4210602</v>
+      </c>
+      <c r="D118" t="s">
+        <v>41</v>
+      </c>
+      <c r="E118" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F118" t="s">
+        <v>251</v>
+      </c>
+      <c r="G118">
+        <v>212726</v>
+      </c>
+      <c r="H118">
+        <v>239</v>
+      </c>
+      <c r="J118">
+        <v>212726</v>
+      </c>
+      <c r="L118" t="s">
+        <v>24</v>
+      </c>
+      <c r="M118">
+        <v>4</v>
+      </c>
+      <c r="N118">
+        <v>10036</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>259</v>
+      </c>
+      <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119">
+        <v>4210602</v>
+      </c>
+      <c r="D119" t="s">
+        <v>41</v>
+      </c>
+      <c r="E119" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F119" t="s">
+        <v>252</v>
+      </c>
+      <c r="G119">
+        <v>144444</v>
+      </c>
+      <c r="H119">
+        <v>329</v>
+      </c>
+      <c r="J119">
+        <v>144444</v>
+      </c>
+      <c r="L119" t="s">
+        <v>24</v>
+      </c>
+      <c r="M119">
+        <v>4</v>
+      </c>
+      <c r="N119">
+        <v>10060</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>259</v>
+      </c>
+      <c r="B120" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120">
+        <v>4210602</v>
+      </c>
+      <c r="D120" t="s">
+        <v>41</v>
+      </c>
+      <c r="E120" s="2">
+        <v>46212</v>
+      </c>
+      <c r="F120" t="s">
+        <v>253</v>
+      </c>
+      <c r="G120">
+        <v>129228</v>
+      </c>
+      <c r="H120">
+        <v>229</v>
+      </c>
+      <c r="J120">
+        <v>129228</v>
+      </c>
+      <c r="L120" t="s">
+        <v>24</v>
+      </c>
+      <c r="M120">
+        <v>4</v>
+      </c>
+      <c r="N120">
+        <v>10088</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>259</v>
+      </c>
+      <c r="B121" t="s">
+        <v>56</v>
+      </c>
+      <c r="C121">
+        <v>4210602</v>
+      </c>
+      <c r="D121" t="s">
+        <v>41</v>
+      </c>
+      <c r="E121" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F121" t="s">
+        <v>254</v>
+      </c>
+      <c r="G121">
+        <v>329844</v>
+      </c>
+      <c r="H121">
+        <v>329</v>
+      </c>
+      <c r="J121">
+        <v>329844</v>
+      </c>
+      <c r="L121" t="s">
+        <v>24</v>
+      </c>
+      <c r="M121">
+        <v>4</v>
+      </c>
+      <c r="N121">
+        <v>10129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>259</v>
+      </c>
+      <c r="B122" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122">
+        <v>4210602</v>
+      </c>
+      <c r="D122" t="s">
+        <v>41</v>
+      </c>
+      <c r="E122" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F122" t="s">
+        <v>255</v>
+      </c>
+      <c r="G122">
+        <v>134220</v>
+      </c>
+      <c r="H122">
+        <v>139</v>
+      </c>
+      <c r="J122">
+        <v>134220</v>
+      </c>
+      <c r="L122" t="s">
+        <v>24</v>
+      </c>
+      <c r="M122">
+        <v>4</v>
+      </c>
+      <c r="N122">
+        <v>10144</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>260</v>
+      </c>
+      <c r="B123" t="s">
+        <v>57</v>
+      </c>
+      <c r="C123">
+        <v>4210602</v>
+      </c>
+      <c r="D123" t="s">
+        <v>41</v>
+      </c>
+      <c r="E123" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F123" t="s">
+        <v>58</v>
+      </c>
+      <c r="G123">
+        <v>158000</v>
+      </c>
+      <c r="H123">
+        <v>331</v>
+      </c>
+      <c r="J123">
+        <v>158000</v>
+      </c>
+      <c r="L123" t="s">
+        <v>24</v>
+      </c>
+      <c r="M123">
+        <v>4</v>
+      </c>
+      <c r="N123">
+        <v>9897</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>260</v>
+      </c>
+      <c r="B124" t="s">
+        <v>57</v>
+      </c>
+      <c r="C124">
+        <v>4210602</v>
+      </c>
+      <c r="D124" t="s">
+        <v>41</v>
+      </c>
+      <c r="E124" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F124" t="s">
+        <v>102</v>
+      </c>
+      <c r="G124">
+        <v>11400</v>
+      </c>
+      <c r="H124" t="s">
+        <v>103</v>
+      </c>
+      <c r="J124">
+        <v>11400</v>
+      </c>
+      <c r="L124" t="s">
+        <v>24</v>
+      </c>
+      <c r="M124">
+        <v>4</v>
+      </c>
+      <c r="N124">
+        <v>9934</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>260</v>
+      </c>
+      <c r="B125" t="s">
+        <v>57</v>
+      </c>
+      <c r="C125">
+        <v>4210602</v>
+      </c>
+      <c r="D125" t="s">
+        <v>41</v>
+      </c>
+      <c r="E125" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F125" t="s">
+        <v>104</v>
+      </c>
+      <c r="G125">
+        <v>95300</v>
+      </c>
+      <c r="H125">
+        <v>140</v>
+      </c>
+      <c r="J125">
+        <v>95300</v>
+      </c>
+      <c r="L125" t="s">
+        <v>24</v>
+      </c>
+      <c r="M125">
+        <v>4</v>
+      </c>
+      <c r="N125">
+        <v>9930</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>260</v>
+      </c>
+      <c r="B126" t="s">
+        <v>57</v>
+      </c>
+      <c r="C126">
+        <v>4210602</v>
+      </c>
+      <c r="D126" t="s">
+        <v>41</v>
+      </c>
+      <c r="E126" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F126" t="s">
+        <v>105</v>
+      </c>
+      <c r="G126">
+        <v>750000</v>
+      </c>
+      <c r="H126">
+        <v>140</v>
+      </c>
+      <c r="I126" t="s">
+        <v>106</v>
+      </c>
+      <c r="J126">
+        <v>750000</v>
+      </c>
+      <c r="L126" t="s">
+        <v>24</v>
+      </c>
+      <c r="M126">
+        <v>4</v>
+      </c>
+      <c r="N126">
+        <v>9930</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>260</v>
+      </c>
+      <c r="B127" t="s">
+        <v>57</v>
+      </c>
+      <c r="C127">
+        <v>4210602</v>
+      </c>
+      <c r="D127" t="s">
+        <v>41</v>
+      </c>
+      <c r="E127" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F127" t="s">
+        <v>107</v>
+      </c>
+      <c r="G127">
+        <v>89800</v>
+      </c>
+      <c r="H127">
+        <v>240</v>
+      </c>
+      <c r="J127">
+        <v>89800</v>
+      </c>
+      <c r="L127" t="s">
+        <v>24</v>
+      </c>
+      <c r="M127">
+        <v>4</v>
+      </c>
+      <c r="N127">
+        <v>9960</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>260</v>
+      </c>
+      <c r="B128" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128">
+        <v>4210602</v>
+      </c>
+      <c r="D128" t="s">
+        <v>41</v>
+      </c>
+      <c r="E128" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F128" t="s">
+        <v>108</v>
+      </c>
+      <c r="G128">
+        <v>74500</v>
+      </c>
+      <c r="H128">
+        <v>331</v>
+      </c>
+      <c r="J128">
+        <v>74500</v>
+      </c>
+      <c r="L128" t="s">
+        <v>24</v>
+      </c>
+      <c r="M128">
+        <v>4</v>
+      </c>
+      <c r="N128">
+        <v>9968</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>260</v>
+      </c>
+      <c r="B129" t="s">
+        <v>57</v>
+      </c>
+      <c r="C129">
+        <v>4210602</v>
+      </c>
+      <c r="D129" t="s">
+        <v>41</v>
+      </c>
+      <c r="E129" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F129" t="s">
+        <v>256</v>
+      </c>
+      <c r="G129">
+        <v>161200</v>
+      </c>
+      <c r="H129">
+        <v>240</v>
+      </c>
+      <c r="J129">
+        <v>161200</v>
+      </c>
+      <c r="L129" t="s">
+        <v>24</v>
+      </c>
+      <c r="M129">
+        <v>4</v>
+      </c>
+      <c r="N129">
+        <v>10037</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>260</v>
+      </c>
+      <c r="B130" t="s">
+        <v>57</v>
+      </c>
+      <c r="C130">
+        <v>4210602</v>
+      </c>
+      <c r="D130" t="s">
+        <v>41</v>
+      </c>
+      <c r="E130" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F130" t="s">
+        <v>257</v>
+      </c>
+      <c r="G130">
+        <v>159200</v>
+      </c>
+      <c r="H130" t="s">
+        <v>258</v>
+      </c>
+      <c r="J130">
+        <v>159200</v>
+      </c>
+      <c r="L130" t="s">
+        <v>24</v>
+      </c>
+      <c r="M130">
+        <v>4</v>
+      </c>
+      <c r="N130">
+        <v>10052</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>260</v>
+      </c>
+      <c r="B131" t="s">
+        <v>57</v>
+      </c>
+      <c r="C131">
+        <v>4210602</v>
+      </c>
+      <c r="D131" t="s">
+        <v>41</v>
+      </c>
+      <c r="E131" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F131" t="s">
+        <v>259</v>
+      </c>
+      <c r="G131">
+        <v>97700</v>
+      </c>
+      <c r="H131">
+        <v>230</v>
+      </c>
+      <c r="J131">
+        <v>97700</v>
+      </c>
+      <c r="L131" t="s">
+        <v>24</v>
+      </c>
+      <c r="M131">
+        <v>4</v>
+      </c>
+      <c r="N131">
+        <v>10089</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>260</v>
+      </c>
+      <c r="B132" t="s">
+        <v>57</v>
+      </c>
+      <c r="C132">
+        <v>4210602</v>
+      </c>
+      <c r="D132" t="s">
+        <v>41</v>
+      </c>
+      <c r="E132" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F132" t="s">
+        <v>260</v>
+      </c>
+      <c r="G132">
+        <v>69800</v>
+      </c>
+      <c r="H132" t="s">
+        <v>258</v>
+      </c>
+      <c r="J132">
+        <v>69800</v>
+      </c>
+      <c r="L132" t="s">
+        <v>24</v>
+      </c>
+      <c r="M132">
+        <v>4</v>
+      </c>
+      <c r="N132">
+        <v>10121</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>260</v>
+      </c>
+      <c r="B133" t="s">
+        <v>57</v>
+      </c>
+      <c r="C133">
+        <v>4210602</v>
+      </c>
+      <c r="D133" t="s">
+        <v>41</v>
+      </c>
+      <c r="E133" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F133" t="s">
+        <v>261</v>
+      </c>
+      <c r="G133">
+        <v>149000</v>
+      </c>
+      <c r="H133">
+        <v>140</v>
+      </c>
+      <c r="J133">
+        <v>149000</v>
+      </c>
+      <c r="L133" t="s">
+        <v>24</v>
+      </c>
+      <c r="M133">
+        <v>4</v>
+      </c>
+      <c r="N133">
+        <v>10145</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>261</v>
+      </c>
+      <c r="B134" t="s">
+        <v>59</v>
+      </c>
+      <c r="C134">
+        <v>4210602</v>
+      </c>
+      <c r="D134" t="s">
+        <v>41</v>
+      </c>
+      <c r="E134" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F134" t="s">
+        <v>61</v>
+      </c>
+      <c r="G134">
+        <v>75000</v>
+      </c>
+      <c r="H134" t="s">
+        <v>62</v>
+      </c>
+      <c r="J134">
+        <v>75000</v>
+      </c>
+      <c r="L134" t="s">
+        <v>24</v>
+      </c>
+      <c r="M134">
+        <v>4</v>
+      </c>
+      <c r="N134">
+        <v>9895</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>261</v>
+      </c>
+      <c r="B135" t="s">
+        <v>59</v>
+      </c>
+      <c r="C135">
+        <v>4210602</v>
+      </c>
+      <c r="D135" t="s">
+        <v>41</v>
+      </c>
+      <c r="E135" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F135" t="s">
+        <v>109</v>
+      </c>
+      <c r="G135">
+        <v>75000</v>
+      </c>
+      <c r="H135" t="s">
+        <v>110</v>
+      </c>
+      <c r="J135">
+        <v>75000</v>
+      </c>
+      <c r="L135" t="s">
+        <v>24</v>
+      </c>
+      <c r="M135">
+        <v>4</v>
+      </c>
+      <c r="N135">
+        <v>9917</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>261</v>
+      </c>
+      <c r="B136" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136">
+        <v>4210602</v>
+      </c>
+      <c r="D136" t="s">
+        <v>41</v>
+      </c>
+      <c r="E136" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F136" t="s">
+        <v>111</v>
+      </c>
+      <c r="G136">
+        <v>75000</v>
+      </c>
+      <c r="H136" t="s">
+        <v>60</v>
+      </c>
+      <c r="J136">
+        <v>75000</v>
+      </c>
+      <c r="L136" t="s">
+        <v>24</v>
+      </c>
+      <c r="M136">
+        <v>4</v>
+      </c>
+      <c r="N136">
+        <v>9947</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>261</v>
+      </c>
+      <c r="B137" t="s">
+        <v>59</v>
+      </c>
+      <c r="C137">
+        <v>4210602</v>
+      </c>
+      <c r="D137" t="s">
+        <v>41</v>
+      </c>
+      <c r="E137" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F137" t="s">
+        <v>112</v>
+      </c>
+      <c r="G137">
+        <v>75000</v>
+      </c>
+      <c r="H137" t="s">
+        <v>113</v>
+      </c>
+      <c r="J137">
+        <v>75000</v>
+      </c>
+      <c r="L137" t="s">
+        <v>24</v>
+      </c>
+      <c r="M137">
+        <v>4</v>
+      </c>
+      <c r="N137">
+        <v>9991</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>261</v>
+      </c>
+      <c r="B138" t="s">
+        <v>59</v>
+      </c>
+      <c r="C138">
+        <v>4210602</v>
+      </c>
+      <c r="D138" t="s">
+        <v>41</v>
+      </c>
+      <c r="E138" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F138" t="s">
+        <v>262</v>
+      </c>
+      <c r="G138">
+        <v>75000</v>
+      </c>
+      <c r="H138" t="s">
+        <v>134</v>
+      </c>
+      <c r="J138">
+        <v>75000</v>
+      </c>
+      <c r="L138" t="s">
+        <v>24</v>
+      </c>
+      <c r="M138">
+        <v>4</v>
+      </c>
+      <c r="N138">
+        <v>9995</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>261</v>
+      </c>
+      <c r="B139" t="s">
+        <v>59</v>
+      </c>
+      <c r="C139">
+        <v>4210602</v>
+      </c>
+      <c r="D139" t="s">
+        <v>41</v>
+      </c>
+      <c r="E139" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F139" t="s">
+        <v>263</v>
+      </c>
+      <c r="G139">
+        <v>75000</v>
+      </c>
+      <c r="H139" t="s">
+        <v>136</v>
+      </c>
+      <c r="J139">
+        <v>75000</v>
+      </c>
+      <c r="L139" t="s">
+        <v>24</v>
+      </c>
+      <c r="M139">
+        <v>4</v>
+      </c>
+      <c r="N139">
+        <v>10025</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>261</v>
+      </c>
+      <c r="B140" t="s">
+        <v>59</v>
+      </c>
+      <c r="C140">
+        <v>4210602</v>
+      </c>
+      <c r="D140" t="s">
+        <v>41</v>
+      </c>
+      <c r="E140" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F140" t="s">
+        <v>264</v>
+      </c>
+      <c r="G140">
+        <v>75000</v>
+      </c>
+      <c r="H140" t="s">
+        <v>265</v>
+      </c>
+      <c r="J140">
+        <v>75000</v>
+      </c>
+      <c r="L140" t="s">
+        <v>24</v>
+      </c>
+      <c r="M140">
+        <v>4</v>
+      </c>
+      <c r="N140">
+        <v>10043</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>261</v>
+      </c>
+      <c r="B141" t="s">
+        <v>59</v>
+      </c>
+      <c r="C141">
+        <v>4210602</v>
+      </c>
+      <c r="D141" t="s">
+        <v>41</v>
+      </c>
+      <c r="E141" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F141" t="s">
+        <v>266</v>
+      </c>
+      <c r="G141">
+        <v>75000</v>
+      </c>
+      <c r="H141" t="s">
+        <v>136</v>
+      </c>
+      <c r="J141">
+        <v>75000</v>
+      </c>
+      <c r="L141" t="s">
+        <v>24</v>
+      </c>
+      <c r="M141">
+        <v>4</v>
+      </c>
+      <c r="N141">
+        <v>10074</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>261</v>
+      </c>
+      <c r="B142" t="s">
+        <v>59</v>
+      </c>
+      <c r="C142">
+        <v>4210602</v>
+      </c>
+      <c r="D142" t="s">
+        <v>41</v>
+      </c>
+      <c r="E142" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F142" t="s">
+        <v>267</v>
+      </c>
+      <c r="G142">
+        <v>150000</v>
+      </c>
+      <c r="H142" t="s">
+        <v>268</v>
+      </c>
+      <c r="I142" t="s">
+        <v>269</v>
+      </c>
+      <c r="J142">
+        <v>150000</v>
+      </c>
+      <c r="L142" t="s">
+        <v>24</v>
+      </c>
+      <c r="M142">
+        <v>4</v>
+      </c>
+      <c r="N142">
+        <v>10110</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>262</v>
+      </c>
+      <c r="B143" t="s">
+        <v>63</v>
+      </c>
+      <c r="C143">
+        <v>4210602</v>
+      </c>
+      <c r="D143" t="s">
+        <v>41</v>
+      </c>
+      <c r="E143" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F143" t="s">
+        <v>114</v>
+      </c>
+      <c r="G143">
+        <v>262767</v>
+      </c>
+      <c r="H143" t="s">
+        <v>115</v>
+      </c>
+      <c r="J143">
+        <v>262767</v>
+      </c>
+      <c r="L143" t="s">
+        <v>24</v>
+      </c>
+      <c r="M143">
+        <v>4</v>
+      </c>
+      <c r="N143">
+        <v>9915</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>262</v>
+      </c>
+      <c r="B144" t="s">
+        <v>63</v>
+      </c>
+      <c r="C144">
+        <v>4210602</v>
+      </c>
+      <c r="D144" t="s">
+        <v>41</v>
+      </c>
+      <c r="E144" s="2">
+        <v>46206</v>
+      </c>
+      <c r="F144" t="s">
+        <v>116</v>
+      </c>
+      <c r="G144">
+        <v>179809</v>
+      </c>
+      <c r="H144" t="s">
+        <v>36</v>
+      </c>
+      <c r="J144">
+        <v>179809</v>
+      </c>
+      <c r="L144" t="s">
+        <v>24</v>
+      </c>
+      <c r="M144">
+        <v>4</v>
+      </c>
+      <c r="N144">
+        <v>9939</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>262</v>
+      </c>
+      <c r="B145" t="s">
+        <v>63</v>
+      </c>
+      <c r="C145">
+        <v>4210602</v>
+      </c>
+      <c r="D145" t="s">
+        <v>41</v>
+      </c>
+      <c r="E145" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F145" t="s">
+        <v>270</v>
+      </c>
+      <c r="G145">
+        <v>177860</v>
+      </c>
+      <c r="H145" t="s">
+        <v>271</v>
+      </c>
+      <c r="J145">
+        <v>177860</v>
+      </c>
+      <c r="L145" t="s">
+        <v>24</v>
+      </c>
+      <c r="M145">
+        <v>4</v>
+      </c>
+      <c r="N145">
+        <v>9986</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>262</v>
+      </c>
+      <c r="B146" t="s">
+        <v>63</v>
+      </c>
+      <c r="C146">
+        <v>4210602</v>
+      </c>
+      <c r="D146" t="s">
+        <v>41</v>
+      </c>
+      <c r="E146" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F146" t="s">
+        <v>272</v>
+      </c>
+      <c r="G146">
+        <v>347071</v>
+      </c>
+      <c r="H146" t="s">
+        <v>273</v>
+      </c>
+      <c r="J146">
+        <v>347071</v>
+      </c>
+      <c r="L146" t="s">
+        <v>24</v>
+      </c>
+      <c r="M146">
+        <v>4</v>
+      </c>
+      <c r="N146">
+        <v>10027</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>262</v>
+      </c>
+      <c r="B147" t="s">
+        <v>63</v>
+      </c>
+      <c r="C147">
+        <v>4210602</v>
+      </c>
+      <c r="D147" t="s">
+        <v>41</v>
+      </c>
+      <c r="E147" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F147" t="s">
+        <v>274</v>
+      </c>
+      <c r="G147">
+        <v>199998</v>
+      </c>
+      <c r="H147" t="s">
+        <v>275</v>
+      </c>
+      <c r="J147">
+        <v>199998</v>
+      </c>
+      <c r="L147" t="s">
+        <v>24</v>
+      </c>
+      <c r="M147">
+        <v>4</v>
+      </c>
+      <c r="N147">
+        <v>10045</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>262</v>
+      </c>
+      <c r="B148" t="s">
+        <v>63</v>
+      </c>
+      <c r="C148">
+        <v>4210602</v>
+      </c>
+      <c r="D148" t="s">
+        <v>41</v>
+      </c>
+      <c r="E148" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F148" t="s">
+        <v>276</v>
+      </c>
+      <c r="G148">
+        <v>260015</v>
+      </c>
+      <c r="H148" t="s">
+        <v>277</v>
+      </c>
+      <c r="J148">
+        <v>260015</v>
+      </c>
+      <c r="L148" t="s">
+        <v>24</v>
+      </c>
+      <c r="M148">
+        <v>4</v>
+      </c>
+      <c r="N148">
+        <v>10072</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>262</v>
+      </c>
+      <c r="B149" t="s">
+        <v>63</v>
+      </c>
+      <c r="C149">
+        <v>4210602</v>
+      </c>
+      <c r="D149" t="s">
+        <v>41</v>
+      </c>
+      <c r="E149" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F149" t="s">
+        <v>278</v>
+      </c>
+      <c r="G149">
+        <v>287106</v>
+      </c>
+      <c r="H149" t="s">
+        <v>279</v>
+      </c>
+      <c r="J149">
+        <v>287106</v>
+      </c>
+      <c r="L149" t="s">
+        <v>24</v>
+      </c>
+      <c r="M149">
+        <v>4</v>
+      </c>
+      <c r="N149">
+        <v>10070</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>262</v>
+      </c>
+      <c r="B150" t="s">
+        <v>63</v>
+      </c>
+      <c r="C150">
+        <v>4210602</v>
+      </c>
+      <c r="D150" t="s">
+        <v>41</v>
+      </c>
+      <c r="E150" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F150" t="s">
+        <v>280</v>
+      </c>
+      <c r="G150">
+        <v>325800</v>
+      </c>
+      <c r="H150" t="s">
+        <v>281</v>
+      </c>
+      <c r="J150">
+        <v>325800</v>
+      </c>
+      <c r="L150" t="s">
+        <v>24</v>
+      </c>
+      <c r="M150">
+        <v>4</v>
+      </c>
+      <c r="N150">
+        <v>10102</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>321</v>
+      </c>
+      <c r="B151" t="s">
+        <v>117</v>
+      </c>
+      <c r="C151">
+        <v>4210803</v>
+      </c>
+      <c r="D151" t="s">
+        <v>118</v>
+      </c>
+      <c r="E151" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F151" t="s">
+        <v>119</v>
+      </c>
+      <c r="G151">
+        <v>270253.5</v>
+      </c>
+      <c r="I151" t="s">
+        <v>120</v>
+      </c>
+      <c r="J151">
+        <v>223350</v>
+      </c>
+      <c r="K151">
+        <v>46903.5</v>
+      </c>
+      <c r="L151" t="s">
+        <v>23</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>331</v>
+      </c>
+      <c r="B152" t="s">
+        <v>282</v>
+      </c>
+      <c r="C152">
+        <v>4210701</v>
+      </c>
+      <c r="D152" t="s">
+        <v>20</v>
+      </c>
+      <c r="E152" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F152" t="s">
+        <v>283</v>
+      </c>
+      <c r="G152">
+        <v>392600</v>
+      </c>
+      <c r="I152" t="s">
+        <v>284</v>
+      </c>
+      <c r="J152">
+        <v>392600</v>
+      </c>
+      <c r="L152" t="s">
+        <v>18</v>
+      </c>
+      <c r="M152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>348</v>
+      </c>
+      <c r="B153" t="s">
+        <v>285</v>
+      </c>
+      <c r="C153">
+        <v>4210701</v>
+      </c>
+      <c r="D153" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F153" t="s">
+        <v>286</v>
+      </c>
+      <c r="G153">
+        <v>317947.7</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="J153">
+        <v>262766.7</v>
+      </c>
+      <c r="K153">
+        <v>55181</v>
+      </c>
+      <c r="L153" t="s">
+        <v>18</v>
+      </c>
+      <c r="M153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>355</v>
+      </c>
+      <c r="B154" t="s">
+        <v>64</v>
+      </c>
+      <c r="C154">
+        <v>4210206</v>
+      </c>
+      <c r="D154" t="s">
+        <v>65</v>
+      </c>
+      <c r="E154" s="2">
+        <v>46204</v>
+      </c>
+      <c r="F154" t="s">
+        <v>67</v>
+      </c>
+      <c r="G154">
+        <v>18000</v>
+      </c>
+      <c r="I154" t="s">
+        <v>68</v>
+      </c>
+      <c r="J154">
+        <v>18000</v>
+      </c>
+      <c r="L154" t="s">
+        <v>66</v>
+      </c>
+      <c r="M154">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>355</v>
+      </c>
+      <c r="B155" t="s">
+        <v>64</v>
+      </c>
+      <c r="C155">
+        <v>4210206</v>
+      </c>
+      <c r="D155" t="s">
+        <v>65</v>
+      </c>
+      <c r="E155" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F155" t="s">
+        <v>69</v>
+      </c>
+      <c r="G155">
+        <v>22500</v>
+      </c>
+      <c r="I155" t="s">
+        <v>70</v>
+      </c>
+      <c r="J155">
+        <v>22500</v>
+      </c>
+      <c r="L155" t="s">
+        <v>66</v>
+      </c>
+      <c r="M155">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>355</v>
+      </c>
+      <c r="B156" t="s">
+        <v>64</v>
+      </c>
+      <c r="C156">
+        <v>4210206</v>
+      </c>
+      <c r="D156" t="s">
+        <v>65</v>
+      </c>
+      <c r="E156" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F156" t="s">
+        <v>121</v>
+      </c>
+      <c r="G156">
+        <v>21500</v>
+      </c>
+      <c r="I156" t="s">
+        <v>70</v>
+      </c>
+      <c r="J156">
+        <v>21500</v>
+      </c>
+      <c r="L156" t="s">
+        <v>66</v>
+      </c>
+      <c r="M156">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>355</v>
+      </c>
+      <c r="B157" t="s">
+        <v>64</v>
+      </c>
+      <c r="C157">
+        <v>4210206</v>
+      </c>
+      <c r="D157" t="s">
+        <v>65</v>
+      </c>
+      <c r="E157" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F157" t="s">
+        <v>288</v>
+      </c>
+      <c r="G157">
+        <v>13000</v>
+      </c>
+      <c r="I157" t="s">
+        <v>289</v>
+      </c>
+      <c r="J157">
+        <v>13000</v>
+      </c>
+      <c r="L157" t="s">
+        <v>66</v>
+      </c>
+      <c r="M157">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>355</v>
+      </c>
+      <c r="B158" t="s">
+        <v>64</v>
+      </c>
+      <c r="C158">
+        <v>4210206</v>
+      </c>
+      <c r="D158" t="s">
+        <v>65</v>
+      </c>
+      <c r="E158" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F158" t="s">
+        <v>290</v>
+      </c>
+      <c r="G158">
+        <v>35900</v>
+      </c>
+      <c r="I158" t="s">
+        <v>291</v>
+      </c>
+      <c r="J158">
+        <v>35900</v>
+      </c>
+      <c r="L158" t="s">
+        <v>66</v>
+      </c>
+      <c r="M158">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>355</v>
+      </c>
+      <c r="B159" t="s">
+        <v>64</v>
+      </c>
+      <c r="C159">
+        <v>4210206</v>
+      </c>
+      <c r="D159" t="s">
+        <v>65</v>
+      </c>
+      <c r="E159" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F159" t="s">
+        <v>292</v>
+      </c>
+      <c r="G159">
+        <v>77000</v>
+      </c>
+      <c r="I159" t="s">
+        <v>293</v>
+      </c>
+      <c r="J159">
+        <v>77000</v>
+      </c>
+      <c r="L159" t="s">
+        <v>66</v>
+      </c>
+      <c r="M159">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>355</v>
+      </c>
+      <c r="B160" t="s">
+        <v>64</v>
+      </c>
+      <c r="C160">
+        <v>4210206</v>
+      </c>
+      <c r="D160" t="s">
+        <v>65</v>
+      </c>
+      <c r="E160" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F160" t="s">
+        <v>294</v>
+      </c>
+      <c r="G160">
+        <v>10000</v>
+      </c>
+      <c r="I160" t="s">
+        <v>295</v>
+      </c>
+      <c r="J160">
+        <v>10000</v>
+      </c>
+      <c r="L160" t="s">
+        <v>66</v>
+      </c>
+      <c r="M160">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>355</v>
+      </c>
+      <c r="B161" t="s">
+        <v>64</v>
+      </c>
+      <c r="C161">
+        <v>4210206</v>
+      </c>
+      <c r="D161" t="s">
+        <v>65</v>
+      </c>
+      <c r="E161" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F161" t="s">
+        <v>296</v>
+      </c>
+      <c r="G161">
+        <v>22500</v>
+      </c>
+      <c r="I161" t="s">
+        <v>297</v>
+      </c>
+      <c r="J161">
+        <v>22500</v>
+      </c>
+      <c r="L161" t="s">
+        <v>66</v>
+      </c>
+      <c r="M161">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>355</v>
+      </c>
+      <c r="B162" t="s">
+        <v>64</v>
+      </c>
+      <c r="C162">
+        <v>4210206</v>
+      </c>
+      <c r="D162" t="s">
+        <v>65</v>
+      </c>
+      <c r="E162" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F162" t="s">
+        <v>298</v>
+      </c>
+      <c r="G162">
+        <v>70500</v>
+      </c>
+      <c r="I162" t="s">
+        <v>299</v>
+      </c>
+      <c r="J162">
+        <v>70500</v>
+      </c>
+      <c r="L162" t="s">
+        <v>66</v>
+      </c>
+      <c r="M162">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>355</v>
+      </c>
+      <c r="B163" t="s">
+        <v>64</v>
+      </c>
+      <c r="C163">
+        <v>4210206</v>
+      </c>
+      <c r="D163" t="s">
+        <v>65</v>
+      </c>
+      <c r="E163" s="2">
+        <v>46217</v>
+      </c>
+      <c r="F163" t="s">
+        <v>300</v>
+      </c>
+      <c r="G163">
+        <v>69000</v>
+      </c>
+      <c r="I163" t="s">
+        <v>301</v>
+      </c>
+      <c r="J163">
+        <v>69000</v>
+      </c>
+      <c r="L163" t="s">
+        <v>66</v>
+      </c>
+      <c r="M163">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>355</v>
+      </c>
+      <c r="B164" t="s">
+        <v>64</v>
+      </c>
+      <c r="C164">
+        <v>4210206</v>
+      </c>
+      <c r="D164" t="s">
+        <v>65</v>
+      </c>
+      <c r="E164" s="2">
+        <v>46217</v>
+      </c>
+      <c r="F164" t="s">
+        <v>302</v>
+      </c>
+      <c r="G164">
+        <v>14000</v>
+      </c>
+      <c r="I164" t="s">
+        <v>303</v>
+      </c>
+      <c r="J164">
+        <v>14000</v>
+      </c>
+      <c r="L164" t="s">
+        <v>66</v>
+      </c>
+      <c r="M164">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>355</v>
+      </c>
+      <c r="B165" t="s">
+        <v>64</v>
+      </c>
+      <c r="C165">
+        <v>4210206</v>
+      </c>
+      <c r="D165" t="s">
+        <v>65</v>
+      </c>
+      <c r="E165" s="2">
+        <v>46218</v>
+      </c>
+      <c r="F165" t="s">
+        <v>304</v>
+      </c>
+      <c r="G165">
+        <v>22500</v>
+      </c>
+      <c r="I165" t="s">
+        <v>305</v>
+      </c>
+      <c r="J165">
+        <v>22500</v>
+      </c>
+      <c r="L165" t="s">
+        <v>66</v>
+      </c>
+      <c r="M165">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>355</v>
+      </c>
+      <c r="B166" t="s">
+        <v>64</v>
+      </c>
+      <c r="C166">
+        <v>4210206</v>
+      </c>
+      <c r="D166" t="s">
+        <v>65</v>
+      </c>
+      <c r="E166" s="2">
+        <v>46219</v>
+      </c>
+      <c r="F166" t="s">
+        <v>306</v>
+      </c>
+      <c r="G166">
+        <v>22500</v>
+      </c>
+      <c r="I166" t="s">
+        <v>307</v>
+      </c>
+      <c r="J166">
+        <v>22500</v>
+      </c>
+      <c r="L166" t="s">
+        <v>66</v>
+      </c>
+      <c r="M166">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>370</v>
+      </c>
+      <c r="B167" t="s">
+        <v>308</v>
+      </c>
+      <c r="C167">
+        <v>4211201</v>
+      </c>
+      <c r="D167" t="s">
+        <v>25</v>
+      </c>
+      <c r="E167" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F167" t="s">
+        <v>309</v>
+      </c>
+      <c r="G167">
+        <v>95499.97</v>
+      </c>
+      <c r="I167" t="s">
+        <v>310</v>
+      </c>
+      <c r="J167">
+        <v>80328.97</v>
+      </c>
+      <c r="K167">
+        <v>15171</v>
+      </c>
+      <c r="L167" t="s">
+        <v>18</v>
+      </c>
+      <c r="M167">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>370</v>
+      </c>
+      <c r="B168" t="s">
+        <v>308</v>
+      </c>
+      <c r="C168">
+        <v>4211201</v>
+      </c>
+      <c r="D168" t="s">
+        <v>25</v>
+      </c>
+      <c r="E168" s="2">
+        <v>46216</v>
+      </c>
+      <c r="F168" t="s">
+        <v>311</v>
+      </c>
+      <c r="G168">
+        <v>50000.06</v>
+      </c>
+      <c r="I168" t="s">
+        <v>312</v>
+      </c>
+      <c r="J168">
+        <v>42383.48</v>
+      </c>
+      <c r="K168">
+        <v>7616.58</v>
+      </c>
+      <c r="L168" t="s">
+        <v>18</v>
+      </c>
+      <c r="M168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>382</v>
+      </c>
+      <c r="B169" t="s">
+        <v>122</v>
+      </c>
+      <c r="C169">
+        <v>4210101</v>
+      </c>
+      <c r="D169" t="s">
+        <v>123</v>
+      </c>
+      <c r="E169" s="2">
+        <v>46207</v>
+      </c>
+      <c r="F169" t="s">
+        <v>124</v>
+      </c>
+      <c r="G169">
+        <v>150000</v>
+      </c>
+      <c r="H169">
+        <v>340</v>
+      </c>
+      <c r="I169" t="s">
+        <v>125</v>
+      </c>
+      <c r="J169">
+        <v>150000</v>
+      </c>
+      <c r="L169" t="s">
+        <v>24</v>
+      </c>
+      <c r="M169">
+        <v>4</v>
+      </c>
+      <c r="N169">
+        <v>9977</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>382</v>
+      </c>
+      <c r="B170" t="s">
+        <v>122</v>
+      </c>
+      <c r="C170">
+        <v>4210101</v>
+      </c>
+      <c r="D170" t="s">
+        <v>123</v>
+      </c>
+      <c r="E170" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F170" t="s">
+        <v>126</v>
+      </c>
+      <c r="G170">
+        <v>254000</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J170">
+        <v>254000</v>
+      </c>
+      <c r="L170" t="s">
+        <v>24</v>
+      </c>
+      <c r="M170">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>382</v>
+      </c>
+      <c r="B171" t="s">
+        <v>122</v>
+      </c>
+      <c r="C171">
+        <v>4210101</v>
+      </c>
+      <c r="D171" t="s">
+        <v>123</v>
+      </c>
+      <c r="E171" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F171" t="s">
+        <v>128</v>
+      </c>
+      <c r="G171">
+        <v>115000</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J171">
+        <v>115000</v>
+      </c>
+      <c r="L171" t="s">
+        <v>24</v>
+      </c>
+      <c r="M171">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>382</v>
+      </c>
+      <c r="B172" t="s">
+        <v>122</v>
+      </c>
+      <c r="C172">
+        <v>4210101</v>
+      </c>
+      <c r="D172" t="s">
+        <v>123</v>
+      </c>
+      <c r="E172" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F172" t="s">
+        <v>313</v>
+      </c>
+      <c r="G172">
+        <v>175000</v>
+      </c>
+      <c r="I172" t="s">
+        <v>314</v>
+      </c>
+      <c r="J172">
+        <v>175000</v>
+      </c>
+      <c r="L172" t="s">
+        <v>24</v>
+      </c>
+      <c r="M172">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>382</v>
+      </c>
+      <c r="B173" t="s">
+        <v>122</v>
+      </c>
+      <c r="C173">
+        <v>4210101</v>
+      </c>
+      <c r="D173" t="s">
+        <v>123</v>
+      </c>
+      <c r="E173" s="2">
+        <v>46213</v>
+      </c>
+      <c r="F173" t="s">
+        <v>315</v>
+      </c>
+      <c r="G173">
+        <v>80000</v>
+      </c>
+      <c r="I173" t="s">
+        <v>316</v>
+      </c>
+      <c r="J173">
+        <v>80000</v>
+      </c>
+      <c r="L173" t="s">
+        <v>24</v>
+      </c>
+      <c r="M173">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>382</v>
+      </c>
+      <c r="B174" t="s">
+        <v>122</v>
+      </c>
+      <c r="C174">
+        <v>4210101</v>
+      </c>
+      <c r="D174" t="s">
+        <v>123</v>
+      </c>
+      <c r="E174" s="2">
+        <v>46214</v>
+      </c>
+      <c r="F174" t="s">
+        <v>317</v>
+      </c>
+      <c r="G174">
+        <v>150000</v>
+      </c>
+      <c r="H174">
+        <v>330</v>
+      </c>
+      <c r="I174" t="s">
+        <v>125</v>
+      </c>
+      <c r="J174">
+        <v>150000</v>
+      </c>
+      <c r="L174" t="s">
+        <v>24</v>
+      </c>
+      <c r="M174">
+        <v>4</v>
+      </c>
+      <c r="N174">
+        <v>10130</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175">
         <v>396</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B175" t="s">
         <v>71</v>
       </c>
-      <c r="C60">
+      <c r="C175">
         <v>4210301</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D175" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E175" s="2">
+        <v>46205</v>
+      </c>
+      <c r="F175" t="s">
+        <v>74</v>
+      </c>
+      <c r="G175">
+        <v>98000</v>
+      </c>
+      <c r="I175" t="s">
+        <v>75</v>
+      </c>
+      <c r="J175">
+        <v>98000</v>
+      </c>
+      <c r="L175" t="s">
+        <v>66</v>
+      </c>
+      <c r="M175">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>396</v>
+      </c>
+      <c r="B176" t="s">
+        <v>71</v>
+      </c>
+      <c r="C176">
+        <v>4210301</v>
+      </c>
+      <c r="D176" t="s">
+        <v>72</v>
+      </c>
+      <c r="E176" s="2">
         <v>46209</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F176" t="s">
         <v>130</v>
       </c>
-      <c r="G60">
+      <c r="G176">
         <v>50000</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I176" t="s">
         <v>73</v>
       </c>
-      <c r="J60">
+      <c r="J176">
         <v>50000</v>
       </c>
-      <c r="L60" t="s">
+      <c r="L176" t="s">
         <v>66</v>
       </c>
-      <c r="M60">
+      <c r="M176">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="2"/>
-    </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="2"/>
-    </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="2"/>
-    </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E107" s="2"/>
-    </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E108" s="2"/>
-    </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E109" s="2"/>
-    </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E110" s="2"/>
-    </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E111" s="2"/>
-    </row>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="2"/>
-    </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E115" s="2"/>
-    </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E116" s="2"/>
-    </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E118" s="2"/>
-    </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E119" s="2"/>
-    </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E120" s="2"/>
-    </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E121" s="2"/>
-    </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E126" s="2"/>
-    </row>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E127" s="2"/>
-    </row>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E128" s="2"/>
-    </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E129" s="2"/>
-    </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E134" s="2"/>
-    </row>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E135" s="2"/>
-    </row>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E136" s="2"/>
-    </row>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E137" s="2"/>
-    </row>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E138" s="2"/>
-    </row>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E139" s="2"/>
-    </row>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E140" s="2"/>
-    </row>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E141" s="2"/>
-    </row>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E142" s="2"/>
-    </row>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E143" s="2"/>
-    </row>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E144" s="2"/>
-    </row>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E145" s="2"/>
-    </row>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E146" s="2"/>
-    </row>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E147" s="2"/>
-    </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E148" s="2"/>
-    </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E149" s="2"/>
-    </row>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E150" s="2"/>
-    </row>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E151" s="2"/>
-    </row>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E152" s="2"/>
-    </row>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E153" s="2"/>
-    </row>
-    <row r="154" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E154" s="2"/>
-    </row>
-    <row r="155" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E155" s="2"/>
-    </row>
-    <row r="156" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E156" s="2"/>
-    </row>
-    <row r="157" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E157" s="2"/>
-    </row>
-    <row r="158" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E158" s="2"/>
-    </row>
-    <row r="159" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E159" s="2"/>
-    </row>
-    <row r="160" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E160" s="2"/>
-    </row>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E161" s="2"/>
-    </row>
-    <row r="162" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E162" s="2"/>
-    </row>
-    <row r="163" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E163" s="2"/>
-    </row>
-    <row r="164" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E164" s="2"/>
-    </row>
-    <row r="165" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E165" s="2"/>
-    </row>
-    <row r="166" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E166" s="2"/>
-    </row>
-    <row r="167" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E167" s="2"/>
-    </row>
-    <row r="168" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E168" s="2"/>
-    </row>
-    <row r="169" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E169" s="2"/>
-    </row>
-    <row r="170" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E170" s="2"/>
-    </row>
-    <row r="171" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E171" s="2"/>
-    </row>
-    <row r="172" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E172" s="2"/>
-    </row>
-    <row r="173" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E173" s="2"/>
-    </row>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E174" s="2"/>
-    </row>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E175" s="2"/>
-    </row>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E176" s="2"/>
-    </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E177" s="2"/>
-    </row>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E178" s="2"/>
-    </row>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E179" s="2"/>
-    </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E180" s="2"/>
-    </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E181" s="2"/>
-    </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>396</v>
+      </c>
+      <c r="B177" t="s">
+        <v>71</v>
+      </c>
+      <c r="C177">
+        <v>4210301</v>
+      </c>
+      <c r="D177" t="s">
+        <v>72</v>
+      </c>
+      <c r="E177" s="2">
+        <v>46210</v>
+      </c>
+      <c r="F177" t="s">
+        <v>318</v>
+      </c>
+      <c r="G177">
+        <v>2810482</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J177">
+        <v>2810482</v>
+      </c>
+      <c r="L177" t="s">
+        <v>66</v>
+      </c>
+      <c r="M177">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>396</v>
+      </c>
+      <c r="B178" t="s">
+        <v>71</v>
+      </c>
+      <c r="C178">
+        <v>4210301</v>
+      </c>
+      <c r="D178" t="s">
+        <v>72</v>
+      </c>
+      <c r="E178" s="2">
+        <v>46211</v>
+      </c>
+      <c r="F178" t="s">
+        <v>320</v>
+      </c>
+      <c r="G178">
+        <v>66000</v>
+      </c>
+      <c r="I178" t="s">
+        <v>73</v>
+      </c>
+      <c r="J178">
+        <v>66000</v>
+      </c>
+      <c r="L178" t="s">
+        <v>66</v>
+      </c>
+      <c r="M178">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>396</v>
+      </c>
+      <c r="B179" t="s">
+        <v>71</v>
+      </c>
+      <c r="C179">
+        <v>4210301</v>
+      </c>
+      <c r="D179" t="s">
+        <v>72</v>
+      </c>
+      <c r="E179" s="2">
+        <v>46218</v>
+      </c>
+      <c r="F179" t="s">
+        <v>321</v>
+      </c>
+      <c r="G179">
+        <v>96500</v>
+      </c>
+      <c r="I179" t="s">
+        <v>322</v>
+      </c>
+      <c r="J179">
+        <v>96500</v>
+      </c>
+      <c r="L179" t="s">
+        <v>66</v>
+      </c>
+      <c r="M179">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>396</v>
+      </c>
+      <c r="B180" t="s">
+        <v>71</v>
+      </c>
+      <c r="C180">
+        <v>4210301</v>
+      </c>
+      <c r="D180" t="s">
+        <v>72</v>
+      </c>
+      <c r="E180" s="2">
+        <v>46219</v>
+      </c>
+      <c r="F180" t="s">
+        <v>323</v>
+      </c>
+      <c r="G180">
+        <v>154000</v>
+      </c>
+      <c r="I180" t="s">
+        <v>73</v>
+      </c>
+      <c r="J180">
+        <v>154000</v>
+      </c>
+      <c r="L180" t="s">
+        <v>66</v>
+      </c>
+      <c r="M180">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>396</v>
+      </c>
+      <c r="B181" t="s">
+        <v>71</v>
+      </c>
+      <c r="C181">
+        <v>4210301</v>
+      </c>
+      <c r="D181" t="s">
+        <v>72</v>
+      </c>
+      <c r="E181" s="2">
+        <v>46219</v>
+      </c>
+      <c r="F181" t="s">
+        <v>324</v>
+      </c>
+      <c r="G181">
+        <v>63600</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J181">
+        <v>63600</v>
+      </c>
+      <c r="L181" t="s">
+        <v>66</v>
+      </c>
+      <c r="M181">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E182" s="2"/>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E183" s="2"/>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E184" s="2"/>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E185" s="2"/>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E186" s="2"/>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E187" s="2"/>
     </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E188" s="2"/>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E189" s="2"/>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E190" s="2"/>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E191" s="2"/>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E192" s="2"/>
     </row>
     <row r="193" spans="5:5" x14ac:dyDescent="0.25">

--- a/data/comision_chofer.xlsx
+++ b/data/comision_chofer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos agosto 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E889EE60-7136-4B0F-A2D4-27C89C8D8DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC1D00A-D4DB-4D01-A478-A17CC3A1481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1E10F628-07AB-4992-9A96-720F65123F92}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="15375" windowHeight="7785" xr2:uid="{1E10F628-07AB-4992-9A96-720F65123F92}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="200">
   <si>
     <t>codigo</t>
   </si>
@@ -259,6 +259,382 @@
   </si>
   <si>
     <t>NOX000100011908</t>
+  </si>
+  <si>
+    <t>ESTACION FERREYRA S.R.L.</t>
+  </si>
+  <si>
+    <t>FCA001600044555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       210 CAM 10 MARTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTACIONAMIENTO/PLAYA </t>
+  </si>
+  <si>
+    <t>Peajes</t>
+  </si>
+  <si>
+    <t>NOX000100011925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       204 CAM 4 MARTES</t>
+  </si>
+  <si>
+    <t>GOMERIA S.A</t>
+  </si>
+  <si>
+    <t>Reparación y Mantenimiento de Rodados</t>
+  </si>
+  <si>
+    <t>NOX000100011923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       209 CAM 9 MARTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOMERIA_x000D_
+</t>
+  </si>
+  <si>
+    <t>NOX000100011984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       112 CAM 12 LUNES</t>
+  </si>
+  <si>
+    <t>gomeria</t>
+  </si>
+  <si>
+    <t>NOX000100011992</t>
+  </si>
+  <si>
+    <t>asado lechon</t>
+  </si>
+  <si>
+    <t>NOX000100012076</t>
+  </si>
+  <si>
+    <t>EDULCORANTES X 4</t>
+  </si>
+  <si>
+    <t>Muni Inspeccion Sanitaria</t>
+  </si>
+  <si>
+    <t>Bromatología, SENASA, ITV, RTO</t>
+  </si>
+  <si>
+    <t>NOB000100011931</t>
+  </si>
+  <si>
+    <t>NOX000100011991</t>
+  </si>
+  <si>
+    <t>PLANTA EMBOTELLADORA S.A.S.</t>
+  </si>
+  <si>
+    <t>Agua</t>
+  </si>
+  <si>
+    <t>FCA000400017370</t>
+  </si>
+  <si>
+    <t>BIDONES JULIO 26</t>
+  </si>
+  <si>
+    <t>Costo de Infraestructura</t>
+  </si>
+  <si>
+    <t>G.P COMBUSTIBLES S.A.S.</t>
+  </si>
+  <si>
+    <t>FCA000600004397</t>
+  </si>
+  <si>
+    <t>233 GUIRAO</t>
+  </si>
+  <si>
+    <t>ALT S.A</t>
+  </si>
+  <si>
+    <t>FCA002800030348</t>
+  </si>
+  <si>
+    <t>santiago</t>
+  </si>
+  <si>
+    <t>NOX000100011920</t>
+  </si>
+  <si>
+    <t>NOX000100011954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       321 CAM 21 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011979</t>
+  </si>
+  <si>
+    <t>NOX000100011995</t>
+  </si>
+  <si>
+    <t>NOX000100012006</t>
+  </si>
+  <si>
+    <t>NOX000100012017</t>
+  </si>
+  <si>
+    <t>BELEN EMILIANO AGUSTIN</t>
+  </si>
+  <si>
+    <t>NOX000100011963</t>
+  </si>
+  <si>
+    <t>NOX000100011934</t>
+  </si>
+  <si>
+    <t>NOX000100011964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       322 CAM 22 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011986</t>
+  </si>
+  <si>
+    <t>NOX000100012003</t>
+  </si>
+  <si>
+    <t>NOX000100012014</t>
+  </si>
+  <si>
+    <t>NOX000100012062</t>
+  </si>
+  <si>
+    <t>GUIRAO LUIS ANTONIO</t>
+  </si>
+  <si>
+    <t>NOX000100011880</t>
+  </si>
+  <si>
+    <t>NOX000100011921</t>
+  </si>
+  <si>
+    <t>NOX000100011957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       324 CAM 24 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100012010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       323 CAM 23 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100011987</t>
+  </si>
+  <si>
+    <t>NOX000100012012</t>
+  </si>
+  <si>
+    <t>NOX000100012050</t>
+  </si>
+  <si>
+    <t>NOX000100011935</t>
+  </si>
+  <si>
+    <t>NOX000100012002</t>
+  </si>
+  <si>
+    <t>NOX000100012005</t>
+  </si>
+  <si>
+    <t>NOX000100012009</t>
+  </si>
+  <si>
+    <t>NOX000100012061</t>
+  </si>
+  <si>
+    <t>NOX000100011966</t>
+  </si>
+  <si>
+    <t>NOX000100011997</t>
+  </si>
+  <si>
+    <t>NOX000100011996</t>
+  </si>
+  <si>
+    <t>NOX000100012051</t>
+  </si>
+  <si>
+    <t>NOX000100012052</t>
+  </si>
+  <si>
+    <t>NOX000100011932</t>
+  </si>
+  <si>
+    <t>NOX000100011965</t>
+  </si>
+  <si>
+    <t>NOX000100011967</t>
+  </si>
+  <si>
+    <t>NOX000100011983</t>
+  </si>
+  <si>
+    <t>NOX000100012004</t>
+  </si>
+  <si>
+    <t>NOX000100012015</t>
+  </si>
+  <si>
+    <t>NOX000100011924</t>
+  </si>
+  <si>
+    <t>NOX000100011998</t>
+  </si>
+  <si>
+    <t>NOX000100012013</t>
+  </si>
+  <si>
+    <t>NOX000100012060</t>
+  </si>
+  <si>
+    <t>NOX000100011933</t>
+  </si>
+  <si>
+    <t>NOX000100011958</t>
+  </si>
+  <si>
+    <t>NOX000100011982</t>
+  </si>
+  <si>
+    <t>GUEVARA ENRIQUE LEONARDO</t>
+  </si>
+  <si>
+    <t>NOX000100011929</t>
+  </si>
+  <si>
+    <t>NOX000100011930</t>
+  </si>
+  <si>
+    <t>NOX000100011990</t>
+  </si>
+  <si>
+    <t>NOX000100012001</t>
+  </si>
+  <si>
+    <t>NOX000100012011</t>
+  </si>
+  <si>
+    <t>NOX000100012016</t>
+  </si>
+  <si>
+    <t>NOX000100011926</t>
+  </si>
+  <si>
+    <t>NOX000100011927</t>
+  </si>
+  <si>
+    <t>NOX000100011959</t>
+  </si>
+  <si>
+    <t>NOX000100011981</t>
+  </si>
+  <si>
+    <t>NOX000100011999</t>
+  </si>
+  <si>
+    <t>NOX000100012008</t>
+  </si>
+  <si>
+    <t>NOX000100012057</t>
+  </si>
+  <si>
+    <t>NOX000100011928</t>
+  </si>
+  <si>
+    <t>NOX000100011961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       305 CAM 5 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100012000</t>
+  </si>
+  <si>
+    <t>NOX000100012054</t>
+  </si>
+  <si>
+    <t>NOX000100011922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       212 CAM 12 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100011980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       108 CAM 8 LUNES</t>
+  </si>
+  <si>
+    <t>NOX000100011994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       202 CAM 2 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100012055</t>
+  </si>
+  <si>
+    <t>NOX000100012056</t>
+  </si>
+  <si>
+    <t>camion 326</t>
+  </si>
+  <si>
+    <t>NOX000100011993</t>
+  </si>
+  <si>
+    <t>comida maxi-gus</t>
+  </si>
+  <si>
+    <t>NOX000100011968</t>
+  </si>
+  <si>
+    <t>NOX000100012063</t>
+  </si>
+  <si>
+    <t>comida maxi-nico-gus</t>
+  </si>
+  <si>
+    <t>SUELDO EMPLEADOS</t>
+  </si>
+  <si>
+    <t>Sueldo Bruto</t>
+  </si>
+  <si>
+    <t>NOX000100012007</t>
+  </si>
+  <si>
+    <t>NOX000100011985</t>
+  </si>
+  <si>
+    <t>VIATICOS VENTAS CBA 8/2026</t>
+  </si>
+  <si>
+    <t>NOX000100011988</t>
+  </si>
+  <si>
+    <t>sebastian</t>
+  </si>
+  <si>
+    <t>NOX000100011989</t>
+  </si>
+  <si>
+    <t>claudio</t>
   </si>
 </sst>
 </file>
@@ -701,34 +1077,34 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>4211805</v>
+        <v>4211201</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G3">
-        <v>2000</v>
+        <v>49999.96</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="J3">
-        <v>2000</v>
+        <v>41322.28</v>
+      </c>
+      <c r="K3">
+        <v>8677.68</v>
       </c>
       <c r="L3" t="s">
         <v>14</v>
@@ -737,39 +1113,36 @@
         <v>5</v>
       </c>
       <c r="N3">
-        <v>10620</v>
+        <v>10661</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="C4">
-        <v>4211201</v>
+        <v>4210304</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="G4">
-        <v>79997.070000000007</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
+        <v>3000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
       </c>
       <c r="J4">
-        <v>68279.679999999993</v>
-      </c>
-      <c r="K4">
-        <v>11717.39</v>
+        <v>3000</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -777,37 +1150,40 @@
       <c r="M4">
         <v>5</v>
       </c>
+      <c r="N4">
+        <v>10656</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="C5">
-        <v>4211201</v>
+        <v>4211102</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="E5" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="G5">
-        <v>80000.070000000007</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
+        <v>21780</v>
+      </c>
+      <c r="H5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="J5">
-        <v>68282.679999999993</v>
-      </c>
-      <c r="K5">
-        <v>11717.39</v>
+        <v>21780</v>
       </c>
       <c r="L5" t="s">
         <v>14</v>
@@ -815,469 +1191,478 @@
       <c r="M5">
         <v>5</v>
       </c>
+      <c r="N5">
+        <v>10677</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C6">
-        <v>4210701</v>
+        <v>4211102</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="G6">
-        <v>331434.96999999997</v>
+        <v>67760</v>
+      </c>
+      <c r="H6" t="s">
+        <v>88</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="J6">
-        <v>273913.2</v>
-      </c>
-      <c r="K6">
-        <v>57521.77</v>
+        <v>67760</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <v>10720</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>251</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C7">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G7">
-        <v>81806.789999999994</v>
-      </c>
-      <c r="H7">
-        <v>431</v>
+        <v>2000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
+        <v>51</v>
       </c>
       <c r="J7">
-        <v>81806.789999999994</v>
+        <v>2000</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>10640</v>
+        <v>10620</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>254</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="G8">
-        <v>74540</v>
-      </c>
-      <c r="H8">
-        <v>338</v>
+        <v>60000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>91</v>
       </c>
       <c r="J8">
-        <v>74540</v>
+        <v>60000</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8">
-        <v>4</v>
-      </c>
-      <c r="N8">
-        <v>10635</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>254</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>4210602</v>
+        <v>4211805</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G9">
-        <v>99215</v>
-      </c>
-      <c r="H9">
-        <v>334</v>
+        <v>13400</v>
+      </c>
+      <c r="I9" t="s">
+        <v>93</v>
       </c>
       <c r="J9">
-        <v>99215</v>
+        <v>13400</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9">
-        <v>4</v>
-      </c>
-      <c r="N9">
-        <v>10631</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="C10">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E10" s="2">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="G10">
-        <v>84230.720000000001</v>
+        <v>9000</v>
       </c>
       <c r="H10">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="J10">
-        <v>84230.720000000001</v>
+        <v>9000</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>10632</v>
+        <v>10673</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>255</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="C11">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E11" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="G11">
-        <v>148816.39000000001</v>
+        <v>9000</v>
       </c>
       <c r="H11">
-        <v>435</v>
+        <v>329</v>
       </c>
       <c r="J11">
-        <v>148816.39000000001</v>
+        <v>9000</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>10643</v>
+        <v>10706</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>256</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2">
         <v>46237</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G12">
-        <v>92522</v>
-      </c>
-      <c r="H12">
-        <v>436</v>
+        <v>79997.070000000007</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
       </c>
       <c r="J12">
-        <v>92522</v>
+        <v>68279.679999999993</v>
+      </c>
+      <c r="K12">
+        <v>11717.39</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M12">
-        <v>4</v>
-      </c>
-      <c r="N12">
-        <v>10644</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>257</v>
+        <v>138</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2">
         <v>46237</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G13">
-        <v>80960.759999999995</v>
-      </c>
-      <c r="H13">
-        <v>337</v>
+        <v>80000.070000000007</v>
+      </c>
+      <c r="I13" t="s">
+        <v>25</v>
       </c>
       <c r="J13">
-        <v>80960.759999999995</v>
+        <v>68282.679999999993</v>
+      </c>
+      <c r="K13">
+        <v>11717.39</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M13">
-        <v>4</v>
-      </c>
-      <c r="N13">
-        <v>10634</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C14">
-        <v>4210602</v>
+        <v>4210805</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="E14" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="G14">
-        <v>42314</v>
-      </c>
-      <c r="H14">
-        <v>437</v>
+        <v>293000</v>
+      </c>
+      <c r="I14" t="s">
+        <v>101</v>
       </c>
       <c r="J14">
-        <v>42314</v>
+        <v>242148.76</v>
+      </c>
+      <c r="K14">
+        <v>50851.24</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M14">
-        <v>4</v>
-      </c>
-      <c r="N14">
-        <v>10645</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>258</v>
+        <v>151</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C15">
-        <v>4210602</v>
+        <v>4210701</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G15">
-        <v>144723</v>
-      </c>
-      <c r="H15">
-        <v>438</v>
+        <v>331434.96999999997</v>
+      </c>
+      <c r="I15" t="s">
+        <v>55</v>
       </c>
       <c r="J15">
-        <v>144723</v>
+        <v>273913.2</v>
+      </c>
+      <c r="K15">
+        <v>57521.77</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15">
-        <v>4</v>
-      </c>
-      <c r="N15">
-        <v>10646</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="C16">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2">
-        <v>46235</v>
+        <v>46241</v>
       </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="G16">
-        <v>67600</v>
+        <v>99999.92</v>
       </c>
       <c r="H16">
-        <v>331</v>
+        <v>233</v>
+      </c>
+      <c r="I16" t="s">
+        <v>105</v>
       </c>
       <c r="J16">
-        <v>67600</v>
+        <v>82644.56</v>
+      </c>
+      <c r="K16">
+        <v>17355.36</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>10629</v>
+        <v>10746</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="C17">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="G17">
-        <v>47000</v>
-      </c>
-      <c r="H17">
-        <v>440</v>
+        <v>101001</v>
+      </c>
+      <c r="I17" t="s">
+        <v>108</v>
       </c>
       <c r="J17">
-        <v>47000</v>
+        <v>86285.36</v>
+      </c>
+      <c r="K17">
+        <v>14715.64</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M17">
-        <v>4</v>
-      </c>
-      <c r="N17">
-        <v>10648</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>4210602</v>
@@ -1286,19 +1671,19 @@
         <v>23</v>
       </c>
       <c r="E18" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G18">
-        <v>75000</v>
-      </c>
-      <c r="H18" t="s">
-        <v>68</v>
+        <v>81806.789999999994</v>
+      </c>
+      <c r="H18">
+        <v>431</v>
       </c>
       <c r="J18">
-        <v>75000</v>
+        <v>81806.789999999994</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -1307,15 +1692,15 @@
         <v>4</v>
       </c>
       <c r="N18">
-        <v>10608</v>
+        <v>10640</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>4210602</v>
@@ -1324,19 +1709,19 @@
         <v>23</v>
       </c>
       <c r="E19" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="G19">
-        <v>195095</v>
-      </c>
-      <c r="H19" t="s">
-        <v>38</v>
+        <v>163970</v>
+      </c>
+      <c r="H19">
+        <v>231</v>
       </c>
       <c r="J19">
-        <v>195095</v>
+        <v>163970</v>
       </c>
       <c r="L19" t="s">
         <v>20</v>
@@ -1345,418 +1730,3308 @@
         <v>4</v>
       </c>
       <c r="N19">
-        <v>10617</v>
+        <v>10665</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>348</v>
+        <v>251</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C20">
-        <v>4210701</v>
+        <v>4210602</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E20" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="G20">
-        <v>317947.7</v>
-      </c>
-      <c r="I20" t="s">
-        <v>71</v>
+        <v>160885</v>
+      </c>
+      <c r="H20" t="s">
+        <v>111</v>
       </c>
       <c r="J20">
-        <v>262766.7</v>
-      </c>
-      <c r="K20">
-        <v>55181</v>
+        <v>160885</v>
       </c>
       <c r="L20" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M20">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N20">
+        <v>10698</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>355</v>
+        <v>251</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C21">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E21" s="2">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="G21">
-        <v>32000</v>
-      </c>
-      <c r="I21" t="s">
-        <v>42</v>
+        <v>101597.18</v>
+      </c>
+      <c r="H21">
+        <v>131</v>
       </c>
       <c r="J21">
-        <v>32000</v>
+        <v>101597.18</v>
       </c>
       <c r="L21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N21">
+        <v>10722</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>396</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>4210301</v>
+        <v>4210602</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E22" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="F22" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="G22">
-        <v>209400</v>
-      </c>
-      <c r="I22" t="s">
-        <v>27</v>
+        <v>156076</v>
+      </c>
+      <c r="H22">
+        <v>231</v>
       </c>
       <c r="J22">
-        <v>209400</v>
+        <v>156076</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N22">
+        <v>10744</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
+        <v>251</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23">
+        <v>4210602</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23">
+        <v>109370</v>
+      </c>
+      <c r="H23">
+        <v>331</v>
+      </c>
+      <c r="J23">
+        <v>109370</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>10780</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24">
+        <v>4210602</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F24" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24">
+        <v>86730</v>
+      </c>
+      <c r="H24">
+        <v>131</v>
+      </c>
+      <c r="J24">
+        <v>86730</v>
+      </c>
+      <c r="L24" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>10792</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>252</v>
+      </c>
+      <c r="B25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25">
+        <v>4210602</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25">
+        <v>8200</v>
+      </c>
+      <c r="H25">
+        <v>332</v>
+      </c>
+      <c r="J25">
+        <v>8200</v>
+      </c>
+      <c r="L25" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25">
+        <v>4</v>
+      </c>
+      <c r="N25">
+        <v>10630</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>252</v>
+      </c>
+      <c r="B26" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26">
+        <v>4210602</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26">
+        <v>106203</v>
+      </c>
+      <c r="H26">
+        <v>232</v>
+      </c>
+      <c r="J26">
+        <v>106203</v>
+      </c>
+      <c r="L26" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>10666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>252</v>
+      </c>
+      <c r="B27" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27">
+        <v>4210602</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F27" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27">
+        <v>124600</v>
+      </c>
+      <c r="H27" t="s">
+        <v>120</v>
+      </c>
+      <c r="J27">
+        <v>124600</v>
+      </c>
+      <c r="L27" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27">
+        <v>4</v>
+      </c>
+      <c r="N27">
+        <v>10699</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>252</v>
+      </c>
+      <c r="B28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28">
+        <v>4210602</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28">
+        <v>203500</v>
+      </c>
+      <c r="H28">
+        <v>132</v>
+      </c>
+      <c r="J28">
+        <v>203500</v>
+      </c>
+      <c r="L28" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28">
+        <v>4</v>
+      </c>
+      <c r="N28">
+        <v>10723</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>252</v>
+      </c>
+      <c r="B29" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29">
+        <v>4210602</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F29" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29">
+        <v>112500</v>
+      </c>
+      <c r="H29">
+        <v>232</v>
+      </c>
+      <c r="J29">
+        <v>112500</v>
+      </c>
+      <c r="L29" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
+      </c>
+      <c r="N29">
+        <v>10745</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>252</v>
+      </c>
+      <c r="B30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30">
+        <v>4210602</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F30" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30">
+        <v>124000</v>
+      </c>
+      <c r="H30">
+        <v>332</v>
+      </c>
+      <c r="J30">
+        <v>124000</v>
+      </c>
+      <c r="L30" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30">
+        <v>4</v>
+      </c>
+      <c r="N30">
+        <v>10781</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>252</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31">
+        <v>4210602</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G31">
+        <v>122500</v>
+      </c>
+      <c r="H31">
+        <v>132</v>
+      </c>
+      <c r="J31">
+        <v>122500</v>
+      </c>
+      <c r="L31" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>10793</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>253</v>
+      </c>
+      <c r="B32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32">
+        <v>4210602</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F32" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32">
+        <v>80000</v>
+      </c>
+      <c r="H32">
+        <v>433</v>
+      </c>
+      <c r="J32">
+        <v>80000</v>
+      </c>
+      <c r="L32" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32">
+        <v>4</v>
+      </c>
+      <c r="N32">
+        <v>10641</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>253</v>
+      </c>
+      <c r="B33" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33">
+        <v>4210602</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33">
+        <v>123000</v>
+      </c>
+      <c r="H33">
+        <v>233</v>
+      </c>
+      <c r="J33">
+        <v>123000</v>
+      </c>
+      <c r="L33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33">
+        <v>4</v>
+      </c>
+      <c r="N33">
+        <v>10667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>253</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34">
+        <v>4210602</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F34" t="s">
+        <v>128</v>
+      </c>
+      <c r="G34">
+        <v>147000</v>
+      </c>
+      <c r="H34" t="s">
+        <v>129</v>
+      </c>
+      <c r="J34">
+        <v>147000</v>
+      </c>
+      <c r="L34" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34">
+        <v>4</v>
+      </c>
+      <c r="N34">
+        <v>10701</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>253</v>
+      </c>
+      <c r="B35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35">
+        <v>4210602</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F35" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35">
+        <v>50000</v>
+      </c>
+      <c r="H35" t="s">
+        <v>131</v>
+      </c>
+      <c r="J35">
+        <v>50000</v>
+      </c>
+      <c r="L35" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35">
+        <v>4</v>
+      </c>
+      <c r="N35">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>253</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36">
+        <v>4210602</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F36" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36">
+        <v>127000</v>
+      </c>
+      <c r="H36">
+        <v>133</v>
+      </c>
+      <c r="J36">
+        <v>127000</v>
+      </c>
+      <c r="L36" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36">
+        <v>4</v>
+      </c>
+      <c r="N36">
+        <v>10724</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>253</v>
+      </c>
+      <c r="B37" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37">
+        <v>4210602</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37">
+        <v>130000</v>
+      </c>
+      <c r="H37">
+        <v>233</v>
+      </c>
+      <c r="J37">
+        <v>130000</v>
+      </c>
+      <c r="L37" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+      <c r="N37">
+        <v>10746</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>253</v>
+      </c>
+      <c r="B38" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38">
+        <v>4210602</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F38" t="s">
+        <v>134</v>
+      </c>
+      <c r="G38">
+        <v>126000</v>
+      </c>
+      <c r="H38">
+        <v>133</v>
+      </c>
+      <c r="J38">
+        <v>126000</v>
+      </c>
+      <c r="L38" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38">
+        <v>4</v>
+      </c>
+      <c r="N38">
+        <v>10794</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>254</v>
+      </c>
+      <c r="B39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39">
+        <v>4210602</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F39" t="s">
+        <v>57</v>
+      </c>
+      <c r="G39">
+        <v>74540</v>
+      </c>
+      <c r="H39">
+        <v>338</v>
+      </c>
+      <c r="J39">
+        <v>74540</v>
+      </c>
+      <c r="L39" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39">
+        <v>4</v>
+      </c>
+      <c r="N39">
+        <v>10635</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>254</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40">
+        <v>4210602</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40">
+        <v>99215</v>
+      </c>
+      <c r="H40">
+        <v>334</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40">
+        <v>99215</v>
+      </c>
+      <c r="L40" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40">
+        <v>4</v>
+      </c>
+      <c r="N40">
+        <v>10631</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>254</v>
+      </c>
+      <c r="B41" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41">
+        <v>4210602</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F41" t="s">
+        <v>135</v>
+      </c>
+      <c r="G41">
+        <v>3610</v>
+      </c>
+      <c r="H41">
+        <v>434</v>
+      </c>
+      <c r="J41">
+        <v>3610</v>
+      </c>
+      <c r="L41" t="s">
+        <v>20</v>
+      </c>
+      <c r="M41">
+        <v>4</v>
+      </c>
+      <c r="N41">
+        <v>10642</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>254</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42">
+        <v>4210602</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F42" t="s">
+        <v>136</v>
+      </c>
+      <c r="G42">
+        <v>111265</v>
+      </c>
+      <c r="H42">
+        <v>134</v>
+      </c>
+      <c r="J42">
+        <v>111265</v>
+      </c>
+      <c r="L42" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42">
+        <v>4</v>
+      </c>
+      <c r="N42">
+        <v>10725</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>254</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43">
+        <v>4210602</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F43" t="s">
+        <v>137</v>
+      </c>
+      <c r="G43">
+        <v>89000</v>
+      </c>
+      <c r="H43">
+        <v>234</v>
+      </c>
+      <c r="J43">
+        <v>89000</v>
+      </c>
+      <c r="L43" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43">
+        <v>4</v>
+      </c>
+      <c r="N43">
+        <v>10747</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>254</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44">
+        <v>4210602</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44">
+        <v>107288</v>
+      </c>
+      <c r="H44">
+        <v>334</v>
+      </c>
+      <c r="J44">
+        <v>107288</v>
+      </c>
+      <c r="L44" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="N44">
+        <v>10783</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>254</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45">
+        <v>4210602</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F45" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45">
+        <v>119100</v>
+      </c>
+      <c r="H45">
+        <v>338</v>
+      </c>
+      <c r="J45">
+        <v>119100</v>
+      </c>
+      <c r="L45" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45">
+        <v>4</v>
+      </c>
+      <c r="N45">
+        <v>10787</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>255</v>
+      </c>
+      <c r="B46" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46">
+        <v>4210602</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46">
+        <v>84230.720000000001</v>
+      </c>
+      <c r="H46">
+        <v>335</v>
+      </c>
+      <c r="J46">
+        <v>84230.720000000001</v>
+      </c>
+      <c r="L46" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46">
+        <v>4</v>
+      </c>
+      <c r="N46">
+        <v>10632</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>255</v>
+      </c>
+      <c r="B47" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47">
+        <v>4210602</v>
+      </c>
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F47" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47">
+        <v>148816.39000000001</v>
+      </c>
+      <c r="H47">
+        <v>435</v>
+      </c>
+      <c r="J47">
+        <v>148816.39000000001</v>
+      </c>
+      <c r="L47" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47">
+        <v>10643</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>255</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48">
+        <v>4210602</v>
+      </c>
+      <c r="D48" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F48" t="s">
+        <v>140</v>
+      </c>
+      <c r="G48">
+        <v>86601</v>
+      </c>
+      <c r="H48">
+        <v>235</v>
+      </c>
+      <c r="J48">
+        <v>86601</v>
+      </c>
+      <c r="L48" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48">
+        <v>4</v>
+      </c>
+      <c r="N48">
+        <v>10669</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>255</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49">
+        <v>4210602</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F49" t="s">
+        <v>141</v>
+      </c>
+      <c r="G49">
+        <v>74215</v>
+      </c>
+      <c r="H49">
+        <v>135</v>
+      </c>
+      <c r="J49">
+        <v>74215</v>
+      </c>
+      <c r="L49" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49">
+        <v>4</v>
+      </c>
+      <c r="N49">
+        <v>10726</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>255</v>
+      </c>
+      <c r="B50" t="s">
+        <v>30</v>
+      </c>
+      <c r="C50">
+        <v>4210602</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F50" t="s">
+        <v>142</v>
+      </c>
+      <c r="G50">
+        <v>101718</v>
+      </c>
+      <c r="H50">
+        <v>235</v>
+      </c>
+      <c r="J50">
+        <v>101718</v>
+      </c>
+      <c r="L50" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50">
+        <v>4</v>
+      </c>
+      <c r="N50">
+        <v>10748</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>255</v>
+      </c>
+      <c r="B51" t="s">
+        <v>30</v>
+      </c>
+      <c r="C51">
+        <v>4210602</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F51" t="s">
+        <v>143</v>
+      </c>
+      <c r="G51">
+        <v>92426.9</v>
+      </c>
+      <c r="H51">
+        <v>335</v>
+      </c>
+      <c r="J51">
+        <v>92426.9</v>
+      </c>
+      <c r="L51" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51">
+        <v>4</v>
+      </c>
+      <c r="N51">
+        <v>10784</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>255</v>
+      </c>
+      <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52">
+        <v>4210602</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F52" t="s">
+        <v>144</v>
+      </c>
+      <c r="G52">
+        <v>96221.68</v>
+      </c>
+      <c r="H52">
+        <v>135</v>
+      </c>
+      <c r="J52">
+        <v>96221.68</v>
+      </c>
+      <c r="L52" t="s">
+        <v>20</v>
+      </c>
+      <c r="M52">
+        <v>4</v>
+      </c>
+      <c r="N52">
+        <v>10795</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>256</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53">
+        <v>4210602</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F53" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53">
+        <v>92522</v>
+      </c>
+      <c r="H53">
+        <v>436</v>
+      </c>
+      <c r="J53">
+        <v>92522</v>
+      </c>
+      <c r="L53" t="s">
+        <v>20</v>
+      </c>
+      <c r="M53">
+        <v>4</v>
+      </c>
+      <c r="N53">
+        <v>10644</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>256</v>
+      </c>
+      <c r="B54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54">
+        <v>4210602</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F54" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54">
+        <v>117384</v>
+      </c>
+      <c r="H54">
+        <v>236</v>
+      </c>
+      <c r="J54">
+        <v>117384</v>
+      </c>
+      <c r="L54" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54">
+        <v>4</v>
+      </c>
+      <c r="N54">
+        <v>10670</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>256</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55">
+        <v>4210602</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F55" t="s">
+        <v>146</v>
+      </c>
+      <c r="G55">
+        <v>68801</v>
+      </c>
+      <c r="H55">
+        <v>234</v>
+      </c>
+      <c r="J55">
+        <v>68801</v>
+      </c>
+      <c r="L55" t="s">
+        <v>20</v>
+      </c>
+      <c r="M55">
+        <v>4</v>
+      </c>
+      <c r="N55">
+        <v>10668</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>256</v>
+      </c>
+      <c r="B56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56">
+        <v>4210602</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F56" t="s">
+        <v>147</v>
+      </c>
+      <c r="G56">
+        <v>81309</v>
+      </c>
+      <c r="H56">
+        <v>326</v>
+      </c>
+      <c r="J56">
+        <v>81309</v>
+      </c>
+      <c r="L56" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>10703</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>256</v>
+      </c>
+      <c r="B57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57">
+        <v>4210602</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F57" t="s">
+        <v>148</v>
+      </c>
+      <c r="G57">
+        <v>153511</v>
+      </c>
+      <c r="H57">
+        <v>136</v>
+      </c>
+      <c r="J57">
+        <v>153511</v>
+      </c>
+      <c r="L57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57">
+        <v>4</v>
+      </c>
+      <c r="N57">
+        <v>10727</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>256</v>
+      </c>
+      <c r="B58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58">
+        <v>4210602</v>
+      </c>
+      <c r="D58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F58" t="s">
+        <v>149</v>
+      </c>
+      <c r="G58">
+        <v>135836.13</v>
+      </c>
+      <c r="H58">
+        <v>236</v>
+      </c>
+      <c r="J58">
+        <v>135836.13</v>
+      </c>
+      <c r="L58" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58">
+        <v>4</v>
+      </c>
+      <c r="N58">
+        <v>10749</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>256</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59">
+        <v>4210602</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F59" t="s">
+        <v>150</v>
+      </c>
+      <c r="G59">
+        <v>93500</v>
+      </c>
+      <c r="H59">
+        <v>336</v>
+      </c>
+      <c r="J59">
+        <v>93500</v>
+      </c>
+      <c r="L59" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59">
+        <v>4</v>
+      </c>
+      <c r="N59">
+        <v>10785</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>257</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60">
+        <v>4210602</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F60" t="s">
+        <v>62</v>
+      </c>
+      <c r="G60">
+        <v>80960.759999999995</v>
+      </c>
+      <c r="H60">
+        <v>337</v>
+      </c>
+      <c r="J60">
+        <v>80960.759999999995</v>
+      </c>
+      <c r="L60" t="s">
+        <v>20</v>
+      </c>
+      <c r="M60">
+        <v>4</v>
+      </c>
+      <c r="N60">
+        <v>10634</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>257</v>
+      </c>
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61">
+        <v>4210602</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F61" t="s">
+        <v>63</v>
+      </c>
+      <c r="G61">
+        <v>42314</v>
+      </c>
+      <c r="H61">
+        <v>437</v>
+      </c>
+      <c r="J61">
+        <v>42314</v>
+      </c>
+      <c r="L61" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61">
+        <v>4</v>
+      </c>
+      <c r="N61">
+        <v>10645</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>257</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62">
+        <v>4210602</v>
+      </c>
+      <c r="D62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F62" t="s">
+        <v>151</v>
+      </c>
+      <c r="G62">
+        <v>115782</v>
+      </c>
+      <c r="H62">
+        <v>237</v>
+      </c>
+      <c r="J62">
+        <v>115782</v>
+      </c>
+      <c r="L62" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62">
+        <v>4</v>
+      </c>
+      <c r="N62">
+        <v>10671</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>257</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63">
+        <v>4210602</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F63" t="s">
+        <v>152</v>
+      </c>
+      <c r="G63">
+        <v>36353</v>
+      </c>
+      <c r="H63">
+        <v>137</v>
+      </c>
+      <c r="J63">
+        <v>36353</v>
+      </c>
+      <c r="L63" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63">
+        <v>4</v>
+      </c>
+      <c r="N63">
+        <v>10728</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>257</v>
+      </c>
+      <c r="B64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64">
+        <v>4210602</v>
+      </c>
+      <c r="D64" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F64" t="s">
+        <v>153</v>
+      </c>
+      <c r="G64">
+        <v>112749</v>
+      </c>
+      <c r="H64">
+        <v>237</v>
+      </c>
+      <c r="J64">
+        <v>112749</v>
+      </c>
+      <c r="L64" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64">
+        <v>4</v>
+      </c>
+      <c r="N64">
+        <v>10750</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>257</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65">
+        <v>4210602</v>
+      </c>
+      <c r="D65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F65" t="s">
+        <v>154</v>
+      </c>
+      <c r="G65">
+        <v>66203</v>
+      </c>
+      <c r="H65">
+        <v>337</v>
+      </c>
+      <c r="J65">
+        <v>66203</v>
+      </c>
+      <c r="L65" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65">
+        <v>4</v>
+      </c>
+      <c r="N65">
+        <v>10786</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>258</v>
+      </c>
+      <c r="B66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66">
+        <v>4210602</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F66" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66">
+        <v>144723</v>
+      </c>
+      <c r="H66">
+        <v>438</v>
+      </c>
+      <c r="J66">
+        <v>144723</v>
+      </c>
+      <c r="L66" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66">
+        <v>4</v>
+      </c>
+      <c r="N66">
+        <v>10646</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>258</v>
+      </c>
+      <c r="B67" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67">
+        <v>4210602</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F67" t="s">
+        <v>155</v>
+      </c>
+      <c r="G67">
+        <v>90709.75</v>
+      </c>
+      <c r="H67">
+        <v>238</v>
+      </c>
+      <c r="J67">
+        <v>90709.75</v>
+      </c>
+      <c r="L67" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67">
+        <v>4</v>
+      </c>
+      <c r="N67">
+        <v>10672</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>258</v>
+      </c>
+      <c r="B68" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68">
+        <v>4210602</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F68" t="s">
+        <v>156</v>
+      </c>
+      <c r="G68">
+        <v>82588</v>
+      </c>
+      <c r="H68">
+        <v>328</v>
+      </c>
+      <c r="J68">
+        <v>82588</v>
+      </c>
+      <c r="L68" t="s">
+        <v>20</v>
+      </c>
+      <c r="M68">
+        <v>4</v>
+      </c>
+      <c r="N68">
+        <v>10705</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>258</v>
+      </c>
+      <c r="B69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69">
+        <v>4210602</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F69" t="s">
+        <v>157</v>
+      </c>
+      <c r="G69">
+        <v>108830</v>
+      </c>
+      <c r="H69">
+        <v>138</v>
+      </c>
+      <c r="J69">
+        <v>108830</v>
+      </c>
+      <c r="L69" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69">
+        <v>4</v>
+      </c>
+      <c r="N69">
+        <v>10729</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>259</v>
+      </c>
+      <c r="B70" t="s">
+        <v>158</v>
+      </c>
+      <c r="C70">
+        <v>4210602</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F70" t="s">
+        <v>159</v>
+      </c>
+      <c r="G70">
+        <v>73138</v>
+      </c>
+      <c r="H70">
+        <v>439</v>
+      </c>
+      <c r="J70">
+        <v>73138</v>
+      </c>
+      <c r="L70" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70">
+        <v>4</v>
+      </c>
+      <c r="N70">
+        <v>10647</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>259</v>
+      </c>
+      <c r="B71" t="s">
+        <v>158</v>
+      </c>
+      <c r="C71">
+        <v>4210602</v>
+      </c>
+      <c r="D71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F71" t="s">
+        <v>160</v>
+      </c>
+      <c r="G71">
+        <v>91665</v>
+      </c>
+      <c r="H71">
+        <v>239</v>
+      </c>
+      <c r="J71">
+        <v>91665</v>
+      </c>
+      <c r="L71" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71">
+        <v>4</v>
+      </c>
+      <c r="N71">
+        <v>10673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>259</v>
+      </c>
+      <c r="B72" t="s">
+        <v>158</v>
+      </c>
+      <c r="C72">
+        <v>4210602</v>
+      </c>
+      <c r="D72" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F72" t="s">
+        <v>161</v>
+      </c>
+      <c r="G72">
+        <v>100606</v>
+      </c>
+      <c r="H72">
+        <v>329</v>
+      </c>
+      <c r="J72">
+        <v>100606</v>
+      </c>
+      <c r="L72" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72">
+        <v>4</v>
+      </c>
+      <c r="N72">
+        <v>10706</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>259</v>
+      </c>
+      <c r="B73" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73">
+        <v>4210602</v>
+      </c>
+      <c r="D73" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F73" t="s">
+        <v>162</v>
+      </c>
+      <c r="G73">
+        <v>67555</v>
+      </c>
+      <c r="H73">
+        <v>139</v>
+      </c>
+      <c r="J73">
+        <v>67555</v>
+      </c>
+      <c r="L73" t="s">
+        <v>20</v>
+      </c>
+      <c r="M73">
+        <v>4</v>
+      </c>
+      <c r="N73">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>259</v>
+      </c>
+      <c r="B74" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74">
+        <v>4210602</v>
+      </c>
+      <c r="D74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F74" t="s">
+        <v>163</v>
+      </c>
+      <c r="G74">
+        <v>107162</v>
+      </c>
+      <c r="H74">
+        <v>239</v>
+      </c>
+      <c r="J74">
+        <v>107162</v>
+      </c>
+      <c r="L74" t="s">
+        <v>20</v>
+      </c>
+      <c r="M74">
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>10752</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>259</v>
+      </c>
+      <c r="B75" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75">
+        <v>4210602</v>
+      </c>
+      <c r="D75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F75" t="s">
+        <v>164</v>
+      </c>
+      <c r="G75">
+        <v>166737</v>
+      </c>
+      <c r="H75">
+        <v>339</v>
+      </c>
+      <c r="J75">
+        <v>166737</v>
+      </c>
+      <c r="L75" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75">
+        <v>4</v>
+      </c>
+      <c r="N75">
+        <v>10788</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>260</v>
+      </c>
+      <c r="B76" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76">
+        <v>4210602</v>
+      </c>
+      <c r="D76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F76" t="s">
+        <v>65</v>
+      </c>
+      <c r="G76">
+        <v>67600</v>
+      </c>
+      <c r="H76">
+        <v>331</v>
+      </c>
+      <c r="J76">
+        <v>67600</v>
+      </c>
+      <c r="L76" t="s">
+        <v>20</v>
+      </c>
+      <c r="M76">
+        <v>4</v>
+      </c>
+      <c r="N76">
+        <v>10629</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>260</v>
+      </c>
+      <c r="B77" t="s">
+        <v>34</v>
+      </c>
+      <c r="C77">
+        <v>4210602</v>
+      </c>
+      <c r="D77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F77" t="s">
+        <v>66</v>
+      </c>
+      <c r="G77">
+        <v>47000</v>
+      </c>
+      <c r="H77">
+        <v>440</v>
+      </c>
+      <c r="J77">
+        <v>47000</v>
+      </c>
+      <c r="L77" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77">
+        <v>4</v>
+      </c>
+      <c r="N77">
+        <v>10648</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>260</v>
+      </c>
+      <c r="B78" t="s">
+        <v>34</v>
+      </c>
+      <c r="C78">
+        <v>4210602</v>
+      </c>
+      <c r="D78" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F78" t="s">
+        <v>165</v>
+      </c>
+      <c r="G78">
+        <v>133000</v>
+      </c>
+      <c r="H78">
+        <v>240</v>
+      </c>
+      <c r="J78">
+        <v>133000</v>
+      </c>
+      <c r="L78" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78">
+        <v>4</v>
+      </c>
+      <c r="N78">
+        <v>10674</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>260</v>
+      </c>
+      <c r="B79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79">
+        <v>4210602</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F79" t="s">
+        <v>166</v>
+      </c>
+      <c r="G79">
+        <v>750000</v>
+      </c>
+      <c r="H79">
+        <v>240</v>
+      </c>
+      <c r="J79">
+        <v>750000</v>
+      </c>
+      <c r="L79" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79">
+        <v>4</v>
+      </c>
+      <c r="N79">
+        <v>10674</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>260</v>
+      </c>
+      <c r="B80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80">
+        <v>4210602</v>
+      </c>
+      <c r="D80" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F80" t="s">
+        <v>167</v>
+      </c>
+      <c r="G80">
+        <v>106500</v>
+      </c>
+      <c r="H80">
+        <v>330</v>
+      </c>
+      <c r="J80">
+        <v>106500</v>
+      </c>
+      <c r="L80" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80">
+        <v>4</v>
+      </c>
+      <c r="N80">
+        <v>10707</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>260</v>
+      </c>
+      <c r="B81" t="s">
+        <v>34</v>
+      </c>
+      <c r="C81">
+        <v>4210602</v>
+      </c>
+      <c r="D81" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F81" t="s">
+        <v>168</v>
+      </c>
+      <c r="G81">
+        <v>84400</v>
+      </c>
+      <c r="H81">
+        <v>140</v>
+      </c>
+      <c r="J81">
+        <v>84400</v>
+      </c>
+      <c r="L81" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81">
+        <v>4</v>
+      </c>
+      <c r="N81">
+        <v>10731</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>260</v>
+      </c>
+      <c r="B82" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82">
+        <v>4210602</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F82" t="s">
+        <v>169</v>
+      </c>
+      <c r="G82">
+        <v>94700</v>
+      </c>
+      <c r="H82">
+        <v>240</v>
+      </c>
+      <c r="J82">
+        <v>94700</v>
+      </c>
+      <c r="L82" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82">
+        <v>4</v>
+      </c>
+      <c r="N82">
+        <v>10753</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>260</v>
+      </c>
+      <c r="B83" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83">
+        <v>4210602</v>
+      </c>
+      <c r="D83" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F83" t="s">
+        <v>170</v>
+      </c>
+      <c r="G83">
+        <v>111600</v>
+      </c>
+      <c r="H83">
+        <v>340</v>
+      </c>
+      <c r="J83">
+        <v>111600</v>
+      </c>
+      <c r="L83" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83">
+        <v>10789</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>260</v>
+      </c>
+      <c r="B84" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84">
+        <v>4210602</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F84" t="s">
+        <v>171</v>
+      </c>
+      <c r="G84">
+        <v>55100</v>
+      </c>
+      <c r="H84">
+        <v>140</v>
+      </c>
+      <c r="J84">
+        <v>55100</v>
+      </c>
+      <c r="L84" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84">
+        <v>4</v>
+      </c>
+      <c r="N84">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>261</v>
+      </c>
+      <c r="B85" t="s">
+        <v>35</v>
+      </c>
+      <c r="C85">
+        <v>4210602</v>
+      </c>
+      <c r="D85" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F85" t="s">
+        <v>67</v>
+      </c>
+      <c r="G85">
+        <v>75000</v>
+      </c>
+      <c r="H85" t="s">
+        <v>68</v>
+      </c>
+      <c r="J85">
+        <v>75000</v>
+      </c>
+      <c r="L85" t="s">
+        <v>20</v>
+      </c>
+      <c r="M85">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <v>10608</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>261</v>
+      </c>
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86">
+        <v>4210602</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F86" t="s">
+        <v>172</v>
+      </c>
+      <c r="G86">
+        <v>75000</v>
+      </c>
+      <c r="H86" t="s">
+        <v>77</v>
+      </c>
+      <c r="J86">
+        <v>75000</v>
+      </c>
+      <c r="L86" t="s">
+        <v>20</v>
+      </c>
+      <c r="M86">
+        <v>4</v>
+      </c>
+      <c r="N86">
+        <v>10661</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>261</v>
+      </c>
+      <c r="B87" t="s">
+        <v>35</v>
+      </c>
+      <c r="C87">
+        <v>4210602</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F87" t="s">
+        <v>173</v>
+      </c>
+      <c r="G87">
+        <v>75000</v>
+      </c>
+      <c r="H87" t="s">
+        <v>174</v>
+      </c>
+      <c r="J87">
+        <v>75000</v>
+      </c>
+      <c r="L87" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87">
+        <v>4</v>
+      </c>
+      <c r="N87">
+        <v>10689</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>261</v>
+      </c>
+      <c r="B88" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88">
+        <v>4210602</v>
+      </c>
+      <c r="D88" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F88" t="s">
+        <v>175</v>
+      </c>
+      <c r="G88">
+        <v>75000</v>
+      </c>
+      <c r="H88" t="s">
+        <v>81</v>
+      </c>
+      <c r="J88">
+        <v>75000</v>
+      </c>
+      <c r="L88" t="s">
+        <v>20</v>
+      </c>
+      <c r="M88">
+        <v>4</v>
+      </c>
+      <c r="N88">
+        <v>10734</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>261</v>
+      </c>
+      <c r="B89" t="s">
+        <v>35</v>
+      </c>
+      <c r="C89">
+        <v>4210602</v>
+      </c>
+      <c r="D89" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F89" t="s">
+        <v>176</v>
+      </c>
+      <c r="G89">
+        <v>75000</v>
+      </c>
+      <c r="H89" t="s">
+        <v>68</v>
+      </c>
+      <c r="J89">
+        <v>75000</v>
+      </c>
+      <c r="L89" t="s">
+        <v>20</v>
+      </c>
+      <c r="M89">
+        <v>4</v>
+      </c>
+      <c r="N89">
+        <v>10758</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>262</v>
+      </c>
+      <c r="B90" t="s">
+        <v>37</v>
+      </c>
+      <c r="C90">
+        <v>4210602</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F90" t="s">
+        <v>69</v>
+      </c>
+      <c r="G90">
+        <v>195095</v>
+      </c>
+      <c r="H90" t="s">
+        <v>38</v>
+      </c>
+      <c r="J90">
+        <v>195095</v>
+      </c>
+      <c r="L90" t="s">
+        <v>20</v>
+      </c>
+      <c r="M90">
+        <v>4</v>
+      </c>
+      <c r="N90">
+        <v>10617</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>262</v>
+      </c>
+      <c r="B91" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91">
+        <v>4210602</v>
+      </c>
+      <c r="D91" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F91" t="s">
+        <v>177</v>
+      </c>
+      <c r="G91">
+        <v>299858</v>
+      </c>
+      <c r="H91" t="s">
+        <v>178</v>
+      </c>
+      <c r="J91">
+        <v>299858</v>
+      </c>
+      <c r="L91" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91">
+        <v>4</v>
+      </c>
+      <c r="N91">
+        <v>10663</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>262</v>
+      </c>
+      <c r="B92" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92">
+        <v>4210602</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F92" t="s">
+        <v>179</v>
+      </c>
+      <c r="G92">
+        <v>199783</v>
+      </c>
+      <c r="H92" t="s">
+        <v>180</v>
+      </c>
+      <c r="J92">
+        <v>199783</v>
+      </c>
+      <c r="L92" t="s">
+        <v>20</v>
+      </c>
+      <c r="M92">
+        <v>4</v>
+      </c>
+      <c r="N92">
+        <v>10716</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>262</v>
+      </c>
+      <c r="B93" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93">
+        <v>4210602</v>
+      </c>
+      <c r="D93" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F93" t="s">
+        <v>181</v>
+      </c>
+      <c r="G93">
+        <v>209985</v>
+      </c>
+      <c r="H93" t="s">
+        <v>182</v>
+      </c>
+      <c r="J93">
+        <v>209985</v>
+      </c>
+      <c r="L93" t="s">
+        <v>20</v>
+      </c>
+      <c r="M93">
+        <v>4</v>
+      </c>
+      <c r="N93">
+        <v>10732</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>262</v>
+      </c>
+      <c r="B94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C94">
+        <v>4210602</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F94" t="s">
+        <v>183</v>
+      </c>
+      <c r="G94">
+        <v>192876</v>
+      </c>
+      <c r="H94" t="s">
+        <v>38</v>
+      </c>
+      <c r="J94">
+        <v>192876</v>
+      </c>
+      <c r="L94" t="s">
+        <v>20</v>
+      </c>
+      <c r="M94">
+        <v>4</v>
+      </c>
+      <c r="N94">
+        <v>10767</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>262</v>
+      </c>
+      <c r="B95" t="s">
+        <v>37</v>
+      </c>
+      <c r="C95">
+        <v>4210602</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F95" t="s">
+        <v>184</v>
+      </c>
+      <c r="G95">
+        <v>147748</v>
+      </c>
+      <c r="H95" t="s">
+        <v>38</v>
+      </c>
+      <c r="I95" t="s">
+        <v>185</v>
+      </c>
+      <c r="J95">
+        <v>147748</v>
+      </c>
+      <c r="L95" t="s">
+        <v>20</v>
+      </c>
+      <c r="M95">
+        <v>4</v>
+      </c>
+      <c r="N95">
+        <v>10767</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>348</v>
+      </c>
+      <c r="B96" t="s">
+        <v>39</v>
+      </c>
+      <c r="C96">
+        <v>4210701</v>
+      </c>
+      <c r="D96" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F96" t="s">
+        <v>70</v>
+      </c>
+      <c r="G96">
+        <v>317947.7</v>
+      </c>
+      <c r="I96" t="s">
+        <v>71</v>
+      </c>
+      <c r="J96">
+        <v>262766.7</v>
+      </c>
+      <c r="K96">
+        <v>55181</v>
+      </c>
+      <c r="L96" t="s">
+        <v>14</v>
+      </c>
+      <c r="M96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>355</v>
+      </c>
+      <c r="B97" t="s">
+        <v>40</v>
+      </c>
+      <c r="C97">
+        <v>4210206</v>
+      </c>
+      <c r="D97" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F97" t="s">
+        <v>72</v>
+      </c>
+      <c r="G97">
+        <v>32000</v>
+      </c>
+      <c r="I97" t="s">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>32000</v>
+      </c>
+      <c r="L97" t="s">
+        <v>22</v>
+      </c>
+      <c r="M97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>355</v>
+      </c>
+      <c r="B98" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98">
+        <v>4210206</v>
+      </c>
+      <c r="D98" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F98" t="s">
+        <v>186</v>
+      </c>
+      <c r="G98">
+        <v>21500</v>
+      </c>
+      <c r="I98" t="s">
+        <v>187</v>
+      </c>
+      <c r="J98">
+        <v>21500</v>
+      </c>
+      <c r="L98" t="s">
+        <v>22</v>
+      </c>
+      <c r="M98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>355</v>
+      </c>
+      <c r="B99" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99">
+        <v>4210206</v>
+      </c>
+      <c r="D99" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F99" t="s">
+        <v>188</v>
+      </c>
+      <c r="G99">
+        <v>31000</v>
+      </c>
+      <c r="I99" t="s">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>31000</v>
+      </c>
+      <c r="L99" t="s">
+        <v>22</v>
+      </c>
+      <c r="M99">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>355</v>
+      </c>
+      <c r="B100" t="s">
+        <v>40</v>
+      </c>
+      <c r="C100">
+        <v>4210206</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F100" t="s">
+        <v>189</v>
+      </c>
+      <c r="G100">
+        <v>31500</v>
+      </c>
+      <c r="I100" t="s">
+        <v>190</v>
+      </c>
+      <c r="J100">
+        <v>31500</v>
+      </c>
+      <c r="L100" t="s">
+        <v>22</v>
+      </c>
+      <c r="M100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>382</v>
+      </c>
+      <c r="B101" t="s">
+        <v>191</v>
+      </c>
+      <c r="C101">
+        <v>4210101</v>
+      </c>
+      <c r="D101" t="s">
+        <v>192</v>
+      </c>
+      <c r="E101" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F101" t="s">
+        <v>193</v>
+      </c>
+      <c r="G101">
+        <v>150000</v>
+      </c>
+      <c r="H101">
+        <v>331</v>
+      </c>
+      <c r="J101">
+        <v>150000</v>
+      </c>
+      <c r="L101" t="s">
+        <v>20</v>
+      </c>
+      <c r="M101">
+        <v>4</v>
+      </c>
+      <c r="N101">
+        <v>10780</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102">
         <v>396</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B102" t="s">
         <v>43</v>
       </c>
-      <c r="C23">
+      <c r="C102">
         <v>4210301</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D102" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E102" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F102" t="s">
+        <v>73</v>
+      </c>
+      <c r="G102">
+        <v>209400</v>
+      </c>
+      <c r="I102" t="s">
+        <v>27</v>
+      </c>
+      <c r="J102">
+        <v>209400</v>
+      </c>
+      <c r="L102" t="s">
+        <v>22</v>
+      </c>
+      <c r="M102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>396</v>
+      </c>
+      <c r="B103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C103">
+        <v>4210301</v>
+      </c>
+      <c r="D103" t="s">
+        <v>44</v>
+      </c>
+      <c r="E103" s="2">
         <v>46238</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F103" t="s">
         <v>74</v>
       </c>
-      <c r="G23">
+      <c r="G103">
         <v>60000</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I103" t="s">
         <v>45</v>
       </c>
-      <c r="J23">
+      <c r="J103">
         <v>60000</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L103" t="s">
         <v>22</v>
       </c>
-      <c r="M23">
+      <c r="M103">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E40" s="2"/>
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="2"/>
-    </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="2"/>
-    </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="2"/>
-    </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="2"/>
-    </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="2"/>
-    </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="2"/>
-    </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="2"/>
-    </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="2"/>
-    </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>396</v>
+      </c>
+      <c r="B104" t="s">
+        <v>43</v>
+      </c>
+      <c r="C104">
+        <v>4210301</v>
+      </c>
+      <c r="D104" t="s">
+        <v>44</v>
+      </c>
+      <c r="E104" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F104" t="s">
+        <v>194</v>
+      </c>
+      <c r="G104">
+        <v>2815200</v>
+      </c>
+      <c r="I104" t="s">
+        <v>195</v>
+      </c>
+      <c r="J104">
+        <v>2815200</v>
+      </c>
+      <c r="L104" t="s">
+        <v>22</v>
+      </c>
+      <c r="M104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>396</v>
+      </c>
+      <c r="B105" t="s">
+        <v>43</v>
+      </c>
+      <c r="C105">
+        <v>4210301</v>
+      </c>
+      <c r="D105" t="s">
+        <v>44</v>
+      </c>
+      <c r="E105" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F105" t="s">
+        <v>196</v>
+      </c>
+      <c r="G105">
+        <v>6000</v>
+      </c>
+      <c r="I105" t="s">
+        <v>197</v>
+      </c>
+      <c r="J105">
+        <v>6000</v>
+      </c>
+      <c r="L105" t="s">
+        <v>22</v>
+      </c>
+      <c r="M105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>396</v>
+      </c>
+      <c r="B106" t="s">
+        <v>43</v>
+      </c>
+      <c r="C106">
+        <v>4210301</v>
+      </c>
+      <c r="D106" t="s">
+        <v>44</v>
+      </c>
+      <c r="E106" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F106" t="s">
+        <v>198</v>
+      </c>
+      <c r="G106">
+        <v>74500</v>
+      </c>
+      <c r="I106" t="s">
+        <v>199</v>
+      </c>
+      <c r="J106">
+        <v>74500</v>
+      </c>
+      <c r="L106" t="s">
+        <v>22</v>
+      </c>
+      <c r="M106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E107" s="2"/>
     </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E108" s="2"/>
     </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E109" s="2"/>
     </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E110" s="2"/>
     </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E111" s="2"/>
     </row>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E112" s="2"/>
     </row>
     <row r="113" spans="5:5" x14ac:dyDescent="0.25">

--- a/data/comision_chofer.xlsx
+++ b/data/comision_chofer.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos agosto 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC1D00A-D4DB-4D01-A478-A17CC3A1481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E314597-6338-4A9F-B060-57C46BBF1BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="1815" windowWidth="15375" windowHeight="7785" xr2:uid="{1E10F628-07AB-4992-9A96-720F65123F92}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1E10F628-07AB-4992-9A96-720F65123F92}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="14"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="345">
   <si>
     <t>codigo</t>
   </si>
@@ -635,6 +635,441 @@
   </si>
   <si>
     <t>claudio</t>
+  </si>
+  <si>
+    <t>COMPUTACION IDEA SRL</t>
+  </si>
+  <si>
+    <t>FCA000100012080</t>
+  </si>
+  <si>
+    <t>CAPACITACION GESCOM</t>
+  </si>
+  <si>
+    <t>FCA000100012274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GESSCOM ABONO </t>
+  </si>
+  <si>
+    <t>FCA001600044637</t>
+  </si>
+  <si>
+    <t>NOX000100012167</t>
+  </si>
+  <si>
+    <t>NOX000100012141</t>
+  </si>
+  <si>
+    <t>DESARROLLO POWER BI</t>
+  </si>
+  <si>
+    <t>NOX000100012177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       317 CAM 17 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100012178</t>
+  </si>
+  <si>
+    <t>CAFE X2KG</t>
+  </si>
+  <si>
+    <t>NOX000100012053</t>
+  </si>
+  <si>
+    <t>NOX000100012085</t>
+  </si>
+  <si>
+    <t>NOX000100012121</t>
+  </si>
+  <si>
+    <t>NOX000100012154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       223 CAM 23 MARTES</t>
+  </si>
+  <si>
+    <t>FCA003600031037</t>
+  </si>
+  <si>
+    <t>FCA003600031085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPELLINO DOMINGO PEDRO </t>
+  </si>
+  <si>
+    <t>FCA000900076807</t>
+  </si>
+  <si>
+    <t>OKINET SRL</t>
+  </si>
+  <si>
+    <t>Alquileres de Impresoras</t>
+  </si>
+  <si>
+    <t>FCA000300015200</t>
+  </si>
+  <si>
+    <t>ALQUILER IMPRESORAS</t>
+  </si>
+  <si>
+    <t>UNION CONSTRUCTORES DE MAQUINAS S A</t>
+  </si>
+  <si>
+    <t>FCA000200003757</t>
+  </si>
+  <si>
+    <t>UCOMA ALQUILER AGOSTO 28</t>
+  </si>
+  <si>
+    <t>NEA000200006999</t>
+  </si>
+  <si>
+    <t>UCOMA 50% IMPUESTO SELLOS</t>
+  </si>
+  <si>
+    <t>NEA000200007011</t>
+  </si>
+  <si>
+    <t>UCOMA- EXPENSAS JULIO 26</t>
+  </si>
+  <si>
+    <t>NEA000200007031</t>
+  </si>
+  <si>
+    <t>UCOMA- ENERGIA JULIO 26</t>
+  </si>
+  <si>
+    <t>LAVORIS S.R.L.</t>
+  </si>
+  <si>
+    <t>Gastos Médicos</t>
+  </si>
+  <si>
+    <t>FCA000200107850</t>
+  </si>
+  <si>
+    <t>PREOCUPACIONNAL - BOCANEGRA LEONEL</t>
+  </si>
+  <si>
+    <t>NOX000100012155</t>
+  </si>
+  <si>
+    <t>GUIRAO 223</t>
+  </si>
+  <si>
+    <t>NOX000100012082</t>
+  </si>
+  <si>
+    <t>NOX000100012108</t>
+  </si>
+  <si>
+    <t>NOX000100012140</t>
+  </si>
+  <si>
+    <t>NOX000100012150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       221 CAM 21 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100012175</t>
+  </si>
+  <si>
+    <t>NOX000100012195</t>
+  </si>
+  <si>
+    <t>NOX000100012088</t>
+  </si>
+  <si>
+    <t>NOX000100012118</t>
+  </si>
+  <si>
+    <t>NOX000100012142</t>
+  </si>
+  <si>
+    <t>NOX000100012156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       222 CAM 22 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100012157</t>
+  </si>
+  <si>
+    <t>NOX000100012110</t>
+  </si>
+  <si>
+    <t>NOX000100012111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       341 combustible</t>
+  </si>
+  <si>
+    <t>NOX000100012077</t>
+  </si>
+  <si>
+    <t>NOX000100012164</t>
+  </si>
+  <si>
+    <t>NOX000100012145</t>
+  </si>
+  <si>
+    <t>NOX000100012153</t>
+  </si>
+  <si>
+    <t>NOX000100012196</t>
+  </si>
+  <si>
+    <t>NOX000100012119</t>
+  </si>
+  <si>
+    <t>NOX000100012144</t>
+  </si>
+  <si>
+    <t>NOX000100012143</t>
+  </si>
+  <si>
+    <t>NOX000100012158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       224 CAM 24 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100012202</t>
+  </si>
+  <si>
+    <t>NOX000100012116</t>
+  </si>
+  <si>
+    <t>NOX000100012115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       325 CAM 25 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100012151</t>
+  </si>
+  <si>
+    <t>NOX000100012160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       225 CAM 25 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100012161</t>
+  </si>
+  <si>
+    <t>NOX000100012087</t>
+  </si>
+  <si>
+    <t>NOX000100012086</t>
+  </si>
+  <si>
+    <t>NOX000100012109</t>
+  </si>
+  <si>
+    <t>NOX000100012134</t>
+  </si>
+  <si>
+    <t>NOX000100012162</t>
+  </si>
+  <si>
+    <t>NOX000100012174</t>
+  </si>
+  <si>
+    <t>NOX000100012172</t>
+  </si>
+  <si>
+    <t>NOX000100012173</t>
+  </si>
+  <si>
+    <t>CAM 331</t>
+  </si>
+  <si>
+    <t>NOX000100012138</t>
+  </si>
+  <si>
+    <t>NOX000100012147</t>
+  </si>
+  <si>
+    <t>NOX000100012148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       137 COMIS DE CAM 331</t>
+  </si>
+  <si>
+    <t>NOX000100012163</t>
+  </si>
+  <si>
+    <t>NOX000100012200</t>
+  </si>
+  <si>
+    <t>NOX000100012201</t>
+  </si>
+  <si>
+    <t>CAMION 437</t>
+  </si>
+  <si>
+    <t>NOX000100012205</t>
+  </si>
+  <si>
+    <t>NOX000100012058</t>
+  </si>
+  <si>
+    <t>NOX000100012113</t>
+  </si>
+  <si>
+    <t>NOX000100012112</t>
+  </si>
+  <si>
+    <t>NOX000100012146</t>
+  </si>
+  <si>
+    <t>NOX000100012165</t>
+  </si>
+  <si>
+    <t>NOX000100012204</t>
+  </si>
+  <si>
+    <t>NOX000100012079</t>
+  </si>
+  <si>
+    <t>NOX000100012084</t>
+  </si>
+  <si>
+    <t>NOX000100012120</t>
+  </si>
+  <si>
+    <t>NOX000100012168</t>
+  </si>
+  <si>
+    <t>NOX000100012166</t>
+  </si>
+  <si>
+    <t>NOX000100012194</t>
+  </si>
+  <si>
+    <t>NOX000100012080</t>
+  </si>
+  <si>
+    <t>NOX000100012114</t>
+  </si>
+  <si>
+    <t>NOX000100012135</t>
+  </si>
+  <si>
+    <t>NOX000100012169</t>
+  </si>
+  <si>
+    <t>NOX000100012159</t>
+  </si>
+  <si>
+    <t>NOX000100012197</t>
+  </si>
+  <si>
+    <t>NOX000100012089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       110 CAM 10 LUNES</t>
+  </si>
+  <si>
+    <t>NOX000100012081</t>
+  </si>
+  <si>
+    <t>NOX000100012094</t>
+  </si>
+  <si>
+    <t>NOX000100012170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       213 CAM 13 MARTES</t>
+  </si>
+  <si>
+    <t>NOX000100012199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       302 CAM 2 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>NOX000100012083</t>
+  </si>
+  <si>
+    <t>NOX000100012139</t>
+  </si>
+  <si>
+    <t>NOX000100012171</t>
+  </si>
+  <si>
+    <t>NOX000100012198</t>
+  </si>
+  <si>
+    <t>LUCAM S A</t>
+  </si>
+  <si>
+    <t>FCA008100015125</t>
+  </si>
+  <si>
+    <t>MARTIN RODRIGO ULLA LOPEZ</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>FCA100100006466</t>
+  </si>
+  <si>
+    <t>ABOINO INTERNET AGISTO 26</t>
+  </si>
+  <si>
+    <t>NOX000100012091</t>
+  </si>
+  <si>
+    <t>NOX000100012092</t>
+  </si>
+  <si>
+    <t>COMIDA GUS-NICO</t>
+  </si>
+  <si>
+    <t>NOX000100012093</t>
+  </si>
+  <si>
+    <t>COMIDA VTA.  MESA SEBA</t>
+  </si>
+  <si>
+    <t>NOX000100012090</t>
+  </si>
+  <si>
+    <t>NOX000100012255</t>
+  </si>
+  <si>
+    <t>COMIDA GUS-NICO-MAXI</t>
+  </si>
+  <si>
+    <t>NOX000100012254</t>
+  </si>
+  <si>
+    <t>NOX000100012176</t>
+  </si>
+  <si>
+    <t>MITO</t>
+  </si>
+  <si>
+    <t>NOX000100012095</t>
+  </si>
+  <si>
+    <t>NOX000100012117</t>
+  </si>
+  <si>
+    <t>NOX000100012152</t>
+  </si>
+  <si>
+    <t>NOX000100012206</t>
+  </si>
+  <si>
+    <t>COMIDA GU-NICO</t>
   </si>
 </sst>
 </file>
@@ -1039,151 +1474,149 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="C2">
-        <v>4211806</v>
+        <v>4210701</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>201</v>
       </c>
       <c r="G2">
-        <v>112300</v>
+        <v>2512673.91</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>202</v>
       </c>
       <c r="J2">
-        <v>92809.919999999998</v>
+        <v>2076590</v>
       </c>
       <c r="K2">
-        <v>19490.080000000002</v>
+        <v>436083.91</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="C3">
-        <v>4211201</v>
+        <v>4210701</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="G3">
-        <v>49999.96</v>
-      </c>
-      <c r="H3" t="s">
-        <v>77</v>
+        <v>819491.4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>204</v>
       </c>
       <c r="J3">
-        <v>41322.28</v>
+        <v>677265.62</v>
       </c>
       <c r="K3">
-        <v>8677.68</v>
+        <v>142225.78</v>
       </c>
       <c r="L3" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="M3">
-        <v>5</v>
-      </c>
-      <c r="N3">
-        <v>10661</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C4">
-        <v>4210304</v>
+        <v>4211806</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G4">
-        <v>3000</v>
-      </c>
-      <c r="H4" t="s">
-        <v>81</v>
+        <v>112300</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
       </c>
       <c r="J4">
-        <v>3000</v>
+        <v>92809.919999999998</v>
+      </c>
+      <c r="K4">
+        <v>19490.080000000002</v>
       </c>
       <c r="L4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M4">
-        <v>5</v>
-      </c>
-      <c r="N4">
-        <v>10656</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C5">
-        <v>4211102</v>
+        <v>4211201</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2">
         <v>46238</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G5">
-        <v>21780</v>
+        <v>49999.96</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>86</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="I5" s="1"/>
       <c r="J5">
-        <v>21780</v>
+        <v>41322.28</v>
+      </c>
+      <c r="K5">
+        <v>8677.68</v>
       </c>
       <c r="L5" t="s">
         <v>14</v>
@@ -1192,39 +1625,39 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>10677</v>
+        <v>10661</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C6">
-        <v>4211102</v>
+        <v>4211201</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="G6">
-        <v>67760</v>
+        <v>79999.929999999993</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="J6">
-        <v>67760</v>
+        <v>66115.64</v>
+      </c>
+      <c r="K6">
+        <v>13884.29</v>
       </c>
       <c r="L6" t="s">
         <v>14</v>
@@ -1233,39 +1666,36 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>10720</v>
+        <v>10804</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C7">
-        <v>4211805</v>
+        <v>4210304</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G7">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="J7">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="L7" t="s">
         <v>14</v>
@@ -1274,106 +1704,118 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>10620</v>
+        <v>10656</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="C8">
-        <v>4211805</v>
+        <v>4210304</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>206</v>
       </c>
       <c r="G8">
-        <v>60000</v>
-      </c>
-      <c r="I8" t="s">
-        <v>91</v>
+        <v>3000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>111</v>
       </c>
       <c r="J8">
-        <v>60000</v>
+        <v>3000</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <v>10932</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="C9">
-        <v>4211805</v>
+        <v>4211102</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="G9">
-        <v>13400</v>
-      </c>
-      <c r="I9" t="s">
-        <v>93</v>
+        <v>21780</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="J9">
-        <v>13400</v>
+        <v>21780</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>10677</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C10">
-        <v>4211410</v>
+        <v>4211102</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="G10">
-        <v>9000</v>
-      </c>
-      <c r="H10">
-        <v>239</v>
+        <v>67760</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" t="s">
+        <v>89</v>
       </c>
       <c r="J10">
-        <v>9000</v>
+        <v>67760</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
@@ -1382,36 +1824,39 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>10673</v>
+        <v>10720</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>4211410</v>
+        <v>4211805</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2">
-        <v>46239</v>
+        <v>46235</v>
       </c>
       <c r="F11" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="G11">
-        <v>9000</v>
-      </c>
-      <c r="H11">
-        <v>329</v>
+        <v>2000</v>
+      </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>51</v>
       </c>
       <c r="J11">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="L11" t="s">
         <v>14</v>
@@ -1420,115 +1865,106 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>10706</v>
+        <v>10620</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>4211201</v>
+        <v>4211805</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="G12">
-        <v>79997.070000000007</v>
+        <v>60000</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="J12">
-        <v>68279.679999999993</v>
-      </c>
-      <c r="K12">
-        <v>11717.39</v>
+        <v>60000</v>
       </c>
       <c r="L12" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C13">
-        <v>4211201</v>
+        <v>4211805</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E13" s="2">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="G13">
-        <v>80000.070000000007</v>
+        <v>13400</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="J13">
-        <v>68282.679999999993</v>
-      </c>
-      <c r="K13">
-        <v>11717.39</v>
+        <v>13400</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>4210805</v>
+        <v>4211805</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>207</v>
       </c>
       <c r="G14">
-        <v>293000</v>
+        <v>800000</v>
       </c>
       <c r="I14" t="s">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="J14">
-        <v>242148.76</v>
-      </c>
-      <c r="K14">
-        <v>50851.24</v>
+        <v>800000</v>
       </c>
       <c r="L14" t="s">
         <v>102</v>
@@ -1539,34 +1975,31 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>4210701</v>
+        <v>4211805</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2">
-        <v>46238</v>
+        <v>46249</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>209</v>
       </c>
       <c r="G15">
-        <v>331434.96999999997</v>
-      </c>
-      <c r="I15" t="s">
-        <v>55</v>
+        <v>8367.7800000000007</v>
+      </c>
+      <c r="H15" t="s">
+        <v>210</v>
       </c>
       <c r="J15">
-        <v>273913.2</v>
-      </c>
-      <c r="K15">
-        <v>57521.77</v>
+        <v>8367.7800000000007</v>
       </c>
       <c r="L15" t="s">
         <v>21</v>
@@ -1574,81 +2007,72 @@
       <c r="M15">
         <v>6</v>
       </c>
+      <c r="N15">
+        <v>10930</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>228</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="C16">
-        <v>4211201</v>
+        <v>4211805</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="F16" t="s">
-        <v>104</v>
+        <v>211</v>
       </c>
       <c r="G16">
-        <v>99999.92</v>
-      </c>
-      <c r="H16">
-        <v>233</v>
+        <v>88000</v>
       </c>
       <c r="I16" t="s">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="J16">
-        <v>82644.56</v>
-      </c>
-      <c r="K16">
-        <v>17355.36</v>
+        <v>88000</v>
       </c>
       <c r="L16" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M16">
-        <v>5</v>
-      </c>
-      <c r="N16">
-        <v>10746</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C17">
-        <v>4211201</v>
+        <v>4211410</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="E17" s="2">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="G17">
-        <v>101001</v>
-      </c>
-      <c r="I17" t="s">
-        <v>108</v>
+        <v>9000</v>
+      </c>
+      <c r="H17">
+        <v>239</v>
       </c>
       <c r="J17">
-        <v>86285.36</v>
-      </c>
-      <c r="K17">
-        <v>14715.64</v>
+        <v>9000</v>
       </c>
       <c r="L17" t="s">
         <v>14</v>
@@ -1656,811 +2080,820 @@
       <c r="M17">
         <v>5</v>
       </c>
+      <c r="N17">
+        <v>10673</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C18">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G18">
-        <v>81806.789999999994</v>
+        <v>9000</v>
       </c>
       <c r="H18">
-        <v>431</v>
+        <v>329</v>
       </c>
       <c r="J18">
-        <v>81806.789999999994</v>
+        <v>9000</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>10640</v>
+        <v>10706</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C19">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E19" s="2">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>213</v>
       </c>
       <c r="G19">
-        <v>163970</v>
+        <v>11000</v>
       </c>
       <c r="H19">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="J19">
-        <v>163970</v>
+        <v>11000</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>10665</v>
+        <v>10795</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C20">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E20" s="2">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="G20">
-        <v>160885</v>
-      </c>
-      <c r="H20" t="s">
-        <v>111</v>
+        <v>9000</v>
+      </c>
+      <c r="H20">
+        <v>239</v>
       </c>
       <c r="J20">
-        <v>160885</v>
+        <v>9000</v>
       </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>10698</v>
+        <v>10823</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C21">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="F21" t="s">
-        <v>112</v>
+        <v>215</v>
       </c>
       <c r="G21">
-        <v>101597.18</v>
+        <v>9000</v>
       </c>
       <c r="H21">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="J21">
-        <v>101597.18</v>
+        <v>9000</v>
       </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>10722</v>
+        <v>10848</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>251</v>
+        <v>135</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C22">
-        <v>4210602</v>
+        <v>4211410</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="F22" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="G22">
-        <v>156076</v>
-      </c>
-      <c r="H22">
-        <v>231</v>
+        <v>17500</v>
+      </c>
+      <c r="H22" t="s">
+        <v>217</v>
       </c>
       <c r="J22">
-        <v>156076</v>
+        <v>17500</v>
       </c>
       <c r="L22" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>10744</v>
+        <v>10904</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E23" s="2">
-        <v>46242</v>
+        <v>46237</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="G23">
-        <v>109370</v>
-      </c>
-      <c r="H23">
-        <v>331</v>
+        <v>79997.070000000007</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
       </c>
       <c r="J23">
-        <v>109370</v>
+        <v>68279.679999999993</v>
+      </c>
+      <c r="K23">
+        <v>11717.39</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M23">
-        <v>4</v>
-      </c>
-      <c r="N23">
-        <v>10780</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C24">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E24" s="2">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="G24">
-        <v>86730</v>
-      </c>
-      <c r="H24">
-        <v>131</v>
+        <v>80000.070000000007</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
       </c>
       <c r="J24">
-        <v>86730</v>
+        <v>68282.679999999993</v>
+      </c>
+      <c r="K24">
+        <v>11717.39</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M24">
-        <v>4</v>
-      </c>
-      <c r="N24">
-        <v>10792</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C25">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E25" s="2">
-        <v>46235</v>
+        <v>46248</v>
       </c>
       <c r="F25" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="G25">
-        <v>8200</v>
-      </c>
-      <c r="H25">
-        <v>332</v>
+        <v>70000.11</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
       </c>
       <c r="J25">
-        <v>8200</v>
+        <v>59800.08</v>
+      </c>
+      <c r="K25">
+        <v>10200.030000000001</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M25">
-        <v>4</v>
-      </c>
-      <c r="N25">
-        <v>10630</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="C26">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E26" s="2">
-        <v>46238</v>
+        <v>46252</v>
       </c>
       <c r="F26" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="G26">
-        <v>106203</v>
-      </c>
-      <c r="H26">
-        <v>232</v>
+        <v>80000.06</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
       </c>
       <c r="J26">
-        <v>106203</v>
+        <v>68342.89</v>
+      </c>
+      <c r="K26">
+        <v>11657.17</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M26">
-        <v>4</v>
-      </c>
-      <c r="N26">
-        <v>10666</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="C27">
-        <v>4210602</v>
+        <v>4210805</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="E27" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="F27" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G27">
-        <v>124600</v>
-      </c>
-      <c r="H27" t="s">
-        <v>120</v>
+        <v>293000</v>
+      </c>
+      <c r="I27" t="s">
+        <v>101</v>
       </c>
       <c r="J27">
-        <v>124600</v>
+        <v>242148.76</v>
+      </c>
+      <c r="K27">
+        <v>50851.24</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M27">
-        <v>4</v>
-      </c>
-      <c r="N27">
-        <v>10699</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>252</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>4210602</v>
+        <v>4210701</v>
       </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E28" s="2">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="G28">
-        <v>203500</v>
-      </c>
-      <c r="H28">
-        <v>132</v>
+        <v>331434.96999999997</v>
+      </c>
+      <c r="I28" t="s">
+        <v>55</v>
       </c>
       <c r="J28">
-        <v>203500</v>
+        <v>273913.2</v>
+      </c>
+      <c r="K28">
+        <v>57521.77</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M28">
-        <v>4</v>
-      </c>
-      <c r="N28">
-        <v>10723</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>252</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="C29">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E29" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F29" t="s">
-        <v>122</v>
+        <v>221</v>
       </c>
       <c r="G29">
-        <v>112500</v>
+        <v>59999.96</v>
       </c>
       <c r="H29">
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="J29">
-        <v>112500</v>
+        <v>49586.74</v>
+      </c>
+      <c r="K29">
+        <v>10413.219999999999</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29">
-        <v>10745</v>
+        <v>10782</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>252</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="C30">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="E30" s="2">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="F30" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="G30">
-        <v>124000</v>
-      </c>
-      <c r="H30">
-        <v>332</v>
+        <v>641754.96</v>
+      </c>
+      <c r="I30" t="s">
+        <v>225</v>
       </c>
       <c r="J30">
-        <v>124000</v>
+        <v>530376</v>
+      </c>
+      <c r="K30">
+        <v>111378.96</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M30">
-        <v>4</v>
-      </c>
-      <c r="N30">
-        <v>10781</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>226</v>
       </c>
       <c r="C31">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="E31" s="2">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>227</v>
       </c>
       <c r="G31">
-        <v>122500</v>
-      </c>
-      <c r="H31">
-        <v>132</v>
+        <v>25876614.219999999</v>
+      </c>
+      <c r="I31" t="s">
+        <v>228</v>
       </c>
       <c r="J31">
-        <v>122500</v>
+        <v>21385631.719999999</v>
+      </c>
+      <c r="K31">
+        <v>4490982.5</v>
       </c>
       <c r="L31" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M31">
-        <v>4</v>
-      </c>
-      <c r="N31">
-        <v>10793</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C32">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="E32" s="2">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="F32" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="G32">
-        <v>80000</v>
-      </c>
-      <c r="H32">
-        <v>433</v>
+        <v>1356770</v>
+      </c>
+      <c r="I32" t="s">
+        <v>230</v>
       </c>
       <c r="J32">
-        <v>80000</v>
+        <v>1356770</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M32">
-        <v>4</v>
-      </c>
-      <c r="N32">
-        <v>10641</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C33">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="E33" s="2">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="F33" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="G33">
-        <v>123000</v>
-      </c>
-      <c r="H33">
-        <v>233</v>
+        <v>6727486.3499999996</v>
+      </c>
+      <c r="I33" t="s">
+        <v>232</v>
       </c>
       <c r="J33">
-        <v>123000</v>
+        <v>5744812.9500000002</v>
+      </c>
+      <c r="K33">
+        <v>982673.4</v>
       </c>
       <c r="L33" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M33">
-        <v>4</v>
-      </c>
-      <c r="N33">
-        <v>10667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="C34">
-        <v>4210602</v>
+        <v>4210904</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>223</v>
       </c>
       <c r="E34" s="2">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="F34" t="s">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="G34">
-        <v>147000</v>
-      </c>
-      <c r="H34" t="s">
-        <v>129</v>
+        <v>2887503.23</v>
+      </c>
+      <c r="I34" t="s">
+        <v>234</v>
       </c>
       <c r="J34">
-        <v>147000</v>
+        <v>2887503.23</v>
       </c>
       <c r="L34" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M34">
-        <v>4</v>
-      </c>
-      <c r="N34">
-        <v>10701</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>235</v>
       </c>
       <c r="C35">
-        <v>4210602</v>
+        <v>4210203</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>236</v>
       </c>
       <c r="E35" s="2">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="F35" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="G35">
-        <v>50000</v>
-      </c>
-      <c r="H35" t="s">
-        <v>131</v>
+        <v>99704</v>
+      </c>
+      <c r="I35" t="s">
+        <v>238</v>
       </c>
       <c r="J35">
-        <v>50000</v>
+        <v>82400</v>
+      </c>
+      <c r="K35">
+        <v>17304</v>
       </c>
       <c r="L35" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="M35">
-        <v>4</v>
-      </c>
-      <c r="N35">
-        <v>10700</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C36">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E36" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="F36" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="G36">
-        <v>127000</v>
+        <v>99999.92</v>
       </c>
       <c r="H36">
-        <v>133</v>
+        <v>233</v>
+      </c>
+      <c r="I36" t="s">
+        <v>105</v>
       </c>
       <c r="J36">
-        <v>127000</v>
+        <v>82644.56</v>
+      </c>
+      <c r="K36">
+        <v>17355.36</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>10724</v>
+        <v>10746</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>253</v>
+        <v>228</v>
       </c>
       <c r="B37" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C37">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E37" s="2">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="G37">
-        <v>130000</v>
-      </c>
-      <c r="H37">
-        <v>233</v>
+        <v>100000.02</v>
+      </c>
+      <c r="H37" t="s">
+        <v>217</v>
+      </c>
+      <c r="I37" t="s">
+        <v>240</v>
       </c>
       <c r="J37">
-        <v>130000</v>
+        <v>100000.02</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N37">
-        <v>10746</v>
+        <v>10904</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C38">
-        <v>4210602</v>
+        <v>4211201</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E38" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="F38" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="G38">
-        <v>126000</v>
-      </c>
-      <c r="H38">
-        <v>133</v>
+        <v>101001</v>
+      </c>
+      <c r="I38" t="s">
+        <v>108</v>
       </c>
       <c r="J38">
-        <v>126000</v>
+        <v>86285.36</v>
+      </c>
+      <c r="K38">
+        <v>14715.64</v>
       </c>
       <c r="L38" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M38">
-        <v>4</v>
-      </c>
-      <c r="N38">
-        <v>10794</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39">
         <v>4210602</v>
@@ -2469,19 +2902,19 @@
         <v>23</v>
       </c>
       <c r="E39" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G39">
-        <v>74540</v>
+        <v>81806.789999999994</v>
       </c>
       <c r="H39">
-        <v>338</v>
+        <v>431</v>
       </c>
       <c r="J39">
-        <v>74540</v>
+        <v>81806.789999999994</v>
       </c>
       <c r="L39" t="s">
         <v>20</v>
@@ -2490,15 +2923,15 @@
         <v>4</v>
       </c>
       <c r="N39">
-        <v>10635</v>
+        <v>10640</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40">
         <v>4210602</v>
@@ -2507,20 +2940,20 @@
         <v>23</v>
       </c>
       <c r="E40" s="2">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="G40">
-        <v>99215</v>
+        <v>163970</v>
       </c>
       <c r="H40">
-        <v>334</v>
+        <v>231</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40">
-        <v>99215</v>
+        <v>163970</v>
       </c>
       <c r="L40" t="s">
         <v>20</v>
@@ -2529,15 +2962,15 @@
         <v>4</v>
       </c>
       <c r="N40">
-        <v>10631</v>
+        <v>10665</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41">
         <v>4210602</v>
@@ -2546,19 +2979,19 @@
         <v>23</v>
       </c>
       <c r="E41" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F41" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="G41">
-        <v>3610</v>
-      </c>
-      <c r="H41">
-        <v>434</v>
+        <v>160885</v>
+      </c>
+      <c r="H41" t="s">
+        <v>111</v>
       </c>
       <c r="J41">
-        <v>3610</v>
+        <v>160885</v>
       </c>
       <c r="L41" t="s">
         <v>20</v>
@@ -2567,15 +3000,15 @@
         <v>4</v>
       </c>
       <c r="N41">
-        <v>10642</v>
+        <v>10698</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42">
         <v>4210602</v>
@@ -2587,16 +3020,16 @@
         <v>46240</v>
       </c>
       <c r="F42" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="G42">
-        <v>111265</v>
+        <v>101597.18</v>
       </c>
       <c r="H42">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J42">
-        <v>111265</v>
+        <v>101597.18</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
@@ -2605,15 +3038,15 @@
         <v>4</v>
       </c>
       <c r="N42">
-        <v>10725</v>
+        <v>10722</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43">
         <v>4210602</v>
@@ -2625,16 +3058,16 @@
         <v>46241</v>
       </c>
       <c r="F43" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="G43">
-        <v>89000</v>
+        <v>156076</v>
       </c>
       <c r="H43">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J43">
-        <v>89000</v>
+        <v>156076</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -2643,15 +3076,15 @@
         <v>4</v>
       </c>
       <c r="N43">
-        <v>10747</v>
+        <v>10744</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44">
         <v>4210602</v>
@@ -2663,16 +3096,16 @@
         <v>46242</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G44">
-        <v>107288</v>
+        <v>109370</v>
       </c>
       <c r="H44">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J44">
-        <v>107288</v>
+        <v>109370</v>
       </c>
       <c r="L44" t="s">
         <v>20</v>
@@ -2681,15 +3114,15 @@
         <v>4</v>
       </c>
       <c r="N44">
-        <v>10783</v>
+        <v>10780</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45">
         <v>4210602</v>
@@ -2698,19 +3131,19 @@
         <v>23</v>
       </c>
       <c r="E45" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="F45" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="G45">
-        <v>119100</v>
+        <v>86730</v>
       </c>
       <c r="H45">
-        <v>338</v>
+        <v>131</v>
       </c>
       <c r="J45">
-        <v>119100</v>
+        <v>86730</v>
       </c>
       <c r="L45" t="s">
         <v>20</v>
@@ -2719,15 +3152,15 @@
         <v>4</v>
       </c>
       <c r="N45">
-        <v>10787</v>
+        <v>10792</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C46">
         <v>4210602</v>
@@ -2736,19 +3169,19 @@
         <v>23</v>
       </c>
       <c r="E46" s="2">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="G46">
-        <v>84230.720000000001</v>
+        <v>188882</v>
       </c>
       <c r="H46">
-        <v>335</v>
+        <v>231</v>
       </c>
       <c r="J46">
-        <v>84230.720000000001</v>
+        <v>188882</v>
       </c>
       <c r="L46" t="s">
         <v>20</v>
@@ -2757,15 +3190,15 @@
         <v>4</v>
       </c>
       <c r="N46">
-        <v>10632</v>
+        <v>10815</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C47">
         <v>4210602</v>
@@ -2774,19 +3207,19 @@
         <v>23</v>
       </c>
       <c r="E47" s="2">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>242</v>
       </c>
       <c r="G47">
-        <v>148816.39000000001</v>
-      </c>
-      <c r="H47">
-        <v>435</v>
+        <v>193305</v>
+      </c>
+      <c r="H47" t="s">
+        <v>111</v>
       </c>
       <c r="J47">
-        <v>148816.39000000001</v>
+        <v>193305</v>
       </c>
       <c r="L47" t="s">
         <v>20</v>
@@ -2795,15 +3228,15 @@
         <v>4</v>
       </c>
       <c r="N47">
-        <v>10643</v>
+        <v>10840</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C48">
         <v>4210602</v>
@@ -2812,19 +3245,19 @@
         <v>23</v>
       </c>
       <c r="E48" s="2">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="F48" t="s">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="G48">
-        <v>86601</v>
+        <v>109859.02</v>
       </c>
       <c r="H48">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="J48">
-        <v>86601</v>
+        <v>109859.02</v>
       </c>
       <c r="L48" t="s">
         <v>20</v>
@@ -2833,15 +3266,15 @@
         <v>4</v>
       </c>
       <c r="N48">
-        <v>10669</v>
+        <v>10870</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C49">
         <v>4210602</v>
@@ -2850,19 +3283,19 @@
         <v>23</v>
       </c>
       <c r="E49" s="2">
-        <v>46240</v>
+        <v>46248</v>
       </c>
       <c r="F49" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="G49">
-        <v>74215</v>
-      </c>
-      <c r="H49">
-        <v>135</v>
+        <v>204175</v>
+      </c>
+      <c r="H49" t="s">
+        <v>245</v>
       </c>
       <c r="J49">
-        <v>74215</v>
+        <v>204175</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
@@ -2871,15 +3304,15 @@
         <v>4</v>
       </c>
       <c r="N49">
-        <v>10726</v>
+        <v>10902</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C50">
         <v>4210602</v>
@@ -2888,19 +3321,19 @@
         <v>23</v>
       </c>
       <c r="E50" s="2">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="F50" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="G50">
-        <v>101718</v>
+        <v>94955</v>
       </c>
       <c r="H50">
-        <v>235</v>
+        <v>331</v>
       </c>
       <c r="J50">
-        <v>101718</v>
+        <v>94955</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
@@ -2909,15 +3342,15 @@
         <v>4</v>
       </c>
       <c r="N50">
-        <v>10748</v>
+        <v>10937</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51">
         <v>4210602</v>
@@ -2926,19 +3359,19 @@
         <v>23</v>
       </c>
       <c r="E51" s="2">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="F51" t="s">
-        <v>143</v>
+        <v>247</v>
       </c>
       <c r="G51">
-        <v>92426.9</v>
+        <v>62491</v>
       </c>
       <c r="H51">
-        <v>335</v>
+        <v>431</v>
       </c>
       <c r="J51">
-        <v>92426.9</v>
+        <v>62491</v>
       </c>
       <c r="L51" t="s">
         <v>20</v>
@@ -2947,15 +3380,15 @@
         <v>4</v>
       </c>
       <c r="N51">
-        <v>10784</v>
+        <v>10950</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
       <c r="C52">
         <v>4210602</v>
@@ -2964,19 +3397,19 @@
         <v>23</v>
       </c>
       <c r="E52" s="2">
-        <v>46244</v>
+        <v>46235</v>
       </c>
       <c r="F52" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="G52">
-        <v>96221.68</v>
+        <v>8200</v>
       </c>
       <c r="H52">
-        <v>135</v>
+        <v>332</v>
       </c>
       <c r="J52">
-        <v>96221.68</v>
+        <v>8200</v>
       </c>
       <c r="L52" t="s">
         <v>20</v>
@@ -2985,15 +3418,15 @@
         <v>4</v>
       </c>
       <c r="N52">
-        <v>10795</v>
+        <v>10630</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C53">
         <v>4210602</v>
@@ -3002,19 +3435,19 @@
         <v>23</v>
       </c>
       <c r="E53" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F53" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="G53">
-        <v>92522</v>
+        <v>106203</v>
       </c>
       <c r="H53">
-        <v>436</v>
+        <v>232</v>
       </c>
       <c r="J53">
-        <v>92522</v>
+        <v>106203</v>
       </c>
       <c r="L53" t="s">
         <v>20</v>
@@ -3023,15 +3456,15 @@
         <v>4</v>
       </c>
       <c r="N53">
-        <v>10644</v>
+        <v>10666</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C54">
         <v>4210602</v>
@@ -3040,19 +3473,19 @@
         <v>23</v>
       </c>
       <c r="E54" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F54" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="G54">
-        <v>117384</v>
-      </c>
-      <c r="H54">
-        <v>236</v>
+        <v>124600</v>
+      </c>
+      <c r="H54" t="s">
+        <v>120</v>
       </c>
       <c r="J54">
-        <v>117384</v>
+        <v>124600</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
@@ -3061,15 +3494,15 @@
         <v>4</v>
       </c>
       <c r="N54">
-        <v>10670</v>
+        <v>10699</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C55">
         <v>4210602</v>
@@ -3078,19 +3511,19 @@
         <v>23</v>
       </c>
       <c r="E55" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F55" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="G55">
-        <v>68801</v>
+        <v>203500</v>
       </c>
       <c r="H55">
-        <v>234</v>
+        <v>132</v>
       </c>
       <c r="J55">
-        <v>68801</v>
+        <v>203500</v>
       </c>
       <c r="L55" t="s">
         <v>20</v>
@@ -3099,15 +3532,15 @@
         <v>4</v>
       </c>
       <c r="N55">
-        <v>10668</v>
+        <v>10723</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C56">
         <v>4210602</v>
@@ -3116,19 +3549,19 @@
         <v>23</v>
       </c>
       <c r="E56" s="2">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F56" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="G56">
-        <v>81309</v>
+        <v>112500</v>
       </c>
       <c r="H56">
-        <v>326</v>
+        <v>232</v>
       </c>
       <c r="J56">
-        <v>81309</v>
+        <v>112500</v>
       </c>
       <c r="L56" t="s">
         <v>20</v>
@@ -3137,15 +3570,15 @@
         <v>4</v>
       </c>
       <c r="N56">
-        <v>10703</v>
+        <v>10745</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C57">
         <v>4210602</v>
@@ -3154,19 +3587,19 @@
         <v>23</v>
       </c>
       <c r="E57" s="2">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="F57" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="G57">
-        <v>153511</v>
+        <v>124000</v>
       </c>
       <c r="H57">
-        <v>136</v>
+        <v>332</v>
       </c>
       <c r="J57">
-        <v>153511</v>
+        <v>124000</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
@@ -3175,15 +3608,15 @@
         <v>4</v>
       </c>
       <c r="N57">
-        <v>10727</v>
+        <v>10781</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B58" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C58">
         <v>4210602</v>
@@ -3192,19 +3625,19 @@
         <v>23</v>
       </c>
       <c r="E58" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F58" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="G58">
-        <v>135836.13</v>
+        <v>122500</v>
       </c>
       <c r="H58">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="J58">
-        <v>135836.13</v>
+        <v>122500</v>
       </c>
       <c r="L58" t="s">
         <v>20</v>
@@ -3213,15 +3646,15 @@
         <v>4</v>
       </c>
       <c r="N58">
-        <v>10749</v>
+        <v>10793</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
       <c r="C59">
         <v>4210602</v>
@@ -3230,19 +3663,19 @@
         <v>23</v>
       </c>
       <c r="E59" s="2">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="F59" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
       <c r="G59">
-        <v>93500</v>
+        <v>88000</v>
       </c>
       <c r="H59">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="J59">
-        <v>93500</v>
+        <v>88000</v>
       </c>
       <c r="L59" t="s">
         <v>20</v>
@@ -3251,15 +3684,15 @@
         <v>4</v>
       </c>
       <c r="N59">
-        <v>10785</v>
+        <v>10816</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C60">
         <v>4210602</v>
@@ -3268,19 +3701,19 @@
         <v>23</v>
       </c>
       <c r="E60" s="2">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="G60">
-        <v>80960.759999999995</v>
-      </c>
-      <c r="H60">
-        <v>337</v>
+        <v>205963</v>
+      </c>
+      <c r="H60" t="s">
+        <v>120</v>
       </c>
       <c r="J60">
-        <v>80960.759999999995</v>
+        <v>205963</v>
       </c>
       <c r="L60" t="s">
         <v>20</v>
@@ -3289,15 +3722,15 @@
         <v>4</v>
       </c>
       <c r="N60">
-        <v>10634</v>
+        <v>10841</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C61">
         <v>4210602</v>
@@ -3306,19 +3739,19 @@
         <v>23</v>
       </c>
       <c r="E61" s="2">
-        <v>46237</v>
+        <v>46247</v>
       </c>
       <c r="F61" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="G61">
-        <v>42314</v>
+        <v>200000</v>
       </c>
       <c r="H61">
-        <v>437</v>
+        <v>132</v>
       </c>
       <c r="J61">
-        <v>42314</v>
+        <v>200000</v>
       </c>
       <c r="L61" t="s">
         <v>20</v>
@@ -3327,15 +3760,15 @@
         <v>4</v>
       </c>
       <c r="N61">
-        <v>10645</v>
+        <v>10871</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C62">
         <v>4210602</v>
@@ -3344,19 +3777,19 @@
         <v>23</v>
       </c>
       <c r="E62" s="2">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="F62" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="G62">
-        <v>115782</v>
-      </c>
-      <c r="H62">
-        <v>237</v>
+        <v>82900</v>
+      </c>
+      <c r="H62" t="s">
+        <v>252</v>
       </c>
       <c r="J62">
-        <v>115782</v>
+        <v>82900</v>
       </c>
       <c r="L62" t="s">
         <v>20</v>
@@ -3365,15 +3798,15 @@
         <v>4</v>
       </c>
       <c r="N62">
-        <v>10671</v>
+        <v>10903</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="C63">
         <v>4210602</v>
@@ -3382,19 +3815,19 @@
         <v>23</v>
       </c>
       <c r="E63" s="2">
-        <v>46240</v>
+        <v>46249</v>
       </c>
       <c r="F63" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="G63">
-        <v>36353</v>
+        <v>85600</v>
       </c>
       <c r="H63">
-        <v>137</v>
+        <v>332</v>
       </c>
       <c r="J63">
-        <v>36353</v>
+        <v>85600</v>
       </c>
       <c r="L63" t="s">
         <v>20</v>
@@ -3403,15 +3836,15 @@
         <v>4</v>
       </c>
       <c r="N63">
-        <v>10728</v>
+        <v>10938</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="C64">
         <v>4210602</v>
@@ -3420,19 +3853,19 @@
         <v>23</v>
       </c>
       <c r="E64" s="2">
-        <v>46241</v>
+        <v>46235</v>
       </c>
       <c r="F64" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="G64">
-        <v>112749</v>
+        <v>20000</v>
       </c>
       <c r="H64">
-        <v>237</v>
+        <v>341</v>
       </c>
       <c r="J64">
-        <v>112749</v>
+        <v>20000</v>
       </c>
       <c r="L64" t="s">
         <v>20</v>
@@ -3441,15 +3874,15 @@
         <v>4</v>
       </c>
       <c r="N64">
-        <v>10750</v>
+        <v>10638</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>125</v>
       </c>
       <c r="C65">
         <v>4210602</v>
@@ -3458,19 +3891,19 @@
         <v>23</v>
       </c>
       <c r="E65" s="2">
-        <v>46242</v>
+        <v>46235</v>
       </c>
       <c r="F65" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="G65">
-        <v>66203</v>
-      </c>
-      <c r="H65">
-        <v>337</v>
+        <v>40000</v>
+      </c>
+      <c r="H65" t="s">
+        <v>256</v>
       </c>
       <c r="J65">
-        <v>66203</v>
+        <v>40000</v>
       </c>
       <c r="L65" t="s">
         <v>20</v>
@@ -3479,15 +3912,15 @@
         <v>4</v>
       </c>
       <c r="N65">
-        <v>10786</v>
+        <v>10638</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="C66">
         <v>4210602</v>
@@ -3499,16 +3932,16 @@
         <v>46237</v>
       </c>
       <c r="F66" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="G66">
-        <v>144723</v>
+        <v>80000</v>
       </c>
       <c r="H66">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="J66">
-        <v>144723</v>
+        <v>80000</v>
       </c>
       <c r="L66" t="s">
         <v>20</v>
@@ -3517,15 +3950,15 @@
         <v>4</v>
       </c>
       <c r="N66">
-        <v>10646</v>
+        <v>10641</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="C67">
         <v>4210602</v>
@@ -3537,16 +3970,16 @@
         <v>46238</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="G67">
-        <v>90709.75</v>
+        <v>123000</v>
       </c>
       <c r="H67">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J67">
-        <v>90709.75</v>
+        <v>123000</v>
       </c>
       <c r="L67" t="s">
         <v>20</v>
@@ -3555,15 +3988,15 @@
         <v>4</v>
       </c>
       <c r="N67">
-        <v>10672</v>
+        <v>10667</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="C68">
         <v>4210602</v>
@@ -3575,16 +4008,16 @@
         <v>46239</v>
       </c>
       <c r="F68" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="G68">
-        <v>82588</v>
-      </c>
-      <c r="H68">
-        <v>328</v>
+        <v>147000</v>
+      </c>
+      <c r="H68" t="s">
+        <v>129</v>
       </c>
       <c r="J68">
-        <v>82588</v>
+        <v>147000</v>
       </c>
       <c r="L68" t="s">
         <v>20</v>
@@ -3593,15 +4026,15 @@
         <v>4</v>
       </c>
       <c r="N68">
-        <v>10705</v>
+        <v>10701</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="C69">
         <v>4210602</v>
@@ -3610,19 +4043,19 @@
         <v>23</v>
       </c>
       <c r="E69" s="2">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="F69" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="G69">
-        <v>108830</v>
-      </c>
-      <c r="H69">
-        <v>138</v>
+        <v>50000</v>
+      </c>
+      <c r="H69" t="s">
+        <v>131</v>
       </c>
       <c r="J69">
-        <v>108830</v>
+        <v>50000</v>
       </c>
       <c r="L69" t="s">
         <v>20</v>
@@ -3631,15 +4064,15 @@
         <v>4</v>
       </c>
       <c r="N69">
-        <v>10729</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B70" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="C70">
         <v>4210602</v>
@@ -3648,19 +4081,19 @@
         <v>23</v>
       </c>
       <c r="E70" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F70" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="G70">
-        <v>73138</v>
+        <v>127000</v>
       </c>
       <c r="H70">
-        <v>439</v>
+        <v>133</v>
       </c>
       <c r="J70">
-        <v>73138</v>
+        <v>127000</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
@@ -3669,15 +4102,15 @@
         <v>4</v>
       </c>
       <c r="N70">
-        <v>10647</v>
+        <v>10724</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B71" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="C71">
         <v>4210602</v>
@@ -3686,19 +4119,19 @@
         <v>23</v>
       </c>
       <c r="E71" s="2">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F71" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="G71">
-        <v>91665</v>
+        <v>130000</v>
       </c>
       <c r="H71">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="J71">
-        <v>91665</v>
+        <v>130000</v>
       </c>
       <c r="L71" t="s">
         <v>20</v>
@@ -3707,15 +4140,15 @@
         <v>4</v>
       </c>
       <c r="N71">
-        <v>10673</v>
+        <v>10746</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B72" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="C72">
         <v>4210602</v>
@@ -3724,19 +4157,19 @@
         <v>23</v>
       </c>
       <c r="E72" s="2">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="F72" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="G72">
-        <v>100606</v>
+        <v>126000</v>
       </c>
       <c r="H72">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="J72">
-        <v>100606</v>
+        <v>126000</v>
       </c>
       <c r="L72" t="s">
         <v>20</v>
@@ -3745,15 +4178,15 @@
         <v>4</v>
       </c>
       <c r="N72">
-        <v>10706</v>
+        <v>10794</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B73" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="C73">
         <v>4210602</v>
@@ -3762,19 +4195,19 @@
         <v>23</v>
       </c>
       <c r="E73" s="2">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="F73" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="G73">
-        <v>67555</v>
+        <v>95000</v>
       </c>
       <c r="H73">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="J73">
-        <v>67555</v>
+        <v>95000</v>
       </c>
       <c r="L73" t="s">
         <v>20</v>
@@ -3783,15 +4216,15 @@
         <v>4</v>
       </c>
       <c r="N73">
-        <v>10730</v>
+        <v>10817</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="C74">
         <v>4210602</v>
@@ -3800,19 +4233,19 @@
         <v>23</v>
       </c>
       <c r="E74" s="2">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="F74" t="s">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="G74">
-        <v>107162</v>
-      </c>
-      <c r="H74">
-        <v>239</v>
+        <v>82000</v>
+      </c>
+      <c r="H74" t="s">
+        <v>131</v>
       </c>
       <c r="J74">
-        <v>107162</v>
+        <v>82000</v>
       </c>
       <c r="L74" t="s">
         <v>20</v>
@@ -3821,36 +4254,36 @@
         <v>4</v>
       </c>
       <c r="N74">
-        <v>10752</v>
+        <v>10842</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75">
+        <v>253</v>
+      </c>
+      <c r="B75" t="s">
+        <v>125</v>
+      </c>
+      <c r="C75">
+        <v>4210602</v>
+      </c>
+      <c r="D75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F75" t="s">
         <v>259</v>
       </c>
-      <c r="B75" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75">
-        <v>4210602</v>
-      </c>
-      <c r="D75" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="2">
-        <v>46242</v>
-      </c>
-      <c r="F75" t="s">
-        <v>164</v>
-      </c>
       <c r="G75">
-        <v>166737</v>
+        <v>174000</v>
       </c>
       <c r="H75">
-        <v>339</v>
+        <v>133</v>
       </c>
       <c r="J75">
-        <v>166737</v>
+        <v>174000</v>
       </c>
       <c r="L75" t="s">
         <v>20</v>
@@ -3859,36 +4292,36 @@
         <v>4</v>
       </c>
       <c r="N75">
-        <v>10788</v>
+        <v>10872</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76">
+        <v>253</v>
+      </c>
+      <c r="B76" t="s">
+        <v>125</v>
+      </c>
+      <c r="C76">
+        <v>4210602</v>
+      </c>
+      <c r="D76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F76" t="s">
         <v>260</v>
       </c>
-      <c r="B76" t="s">
-        <v>34</v>
-      </c>
-      <c r="C76">
-        <v>4210602</v>
-      </c>
-      <c r="D76" t="s">
-        <v>23</v>
-      </c>
-      <c r="E76" s="2">
-        <v>46235</v>
-      </c>
-      <c r="F76" t="s">
-        <v>65</v>
-      </c>
       <c r="G76">
-        <v>67600</v>
-      </c>
-      <c r="H76">
-        <v>331</v>
+        <v>139000</v>
+      </c>
+      <c r="H76" t="s">
+        <v>217</v>
       </c>
       <c r="J76">
-        <v>67600</v>
+        <v>139000</v>
       </c>
       <c r="L76" t="s">
         <v>20</v>
@@ -3897,15 +4330,15 @@
         <v>4</v>
       </c>
       <c r="N76">
-        <v>10629</v>
+        <v>10904</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="C77">
         <v>4210602</v>
@@ -3914,19 +4347,19 @@
         <v>23</v>
       </c>
       <c r="E77" s="2">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="F77" t="s">
-        <v>66</v>
+        <v>261</v>
       </c>
       <c r="G77">
-        <v>47000</v>
+        <v>90000</v>
       </c>
       <c r="H77">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="J77">
-        <v>47000</v>
+        <v>90000</v>
       </c>
       <c r="L77" t="s">
         <v>20</v>
@@ -3935,15 +4368,15 @@
         <v>4</v>
       </c>
       <c r="N77">
-        <v>10648</v>
+        <v>10951</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C78">
         <v>4210602</v>
@@ -3952,19 +4385,19 @@
         <v>23</v>
       </c>
       <c r="E78" s="2">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="F78" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="G78">
-        <v>133000</v>
+        <v>74540</v>
       </c>
       <c r="H78">
-        <v>240</v>
+        <v>338</v>
       </c>
       <c r="J78">
-        <v>133000</v>
+        <v>74540</v>
       </c>
       <c r="L78" t="s">
         <v>20</v>
@@ -3973,15 +4406,15 @@
         <v>4</v>
       </c>
       <c r="N78">
-        <v>10674</v>
+        <v>10635</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C79">
         <v>4210602</v>
@@ -3990,19 +4423,19 @@
         <v>23</v>
       </c>
       <c r="E79" s="2">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="F79" t="s">
-        <v>166</v>
+        <v>58</v>
       </c>
       <c r="G79">
-        <v>750000</v>
+        <v>99215</v>
       </c>
       <c r="H79">
-        <v>240</v>
+        <v>334</v>
       </c>
       <c r="J79">
-        <v>750000</v>
+        <v>99215</v>
       </c>
       <c r="L79" t="s">
         <v>20</v>
@@ -4011,15 +4444,15 @@
         <v>4</v>
       </c>
       <c r="N79">
-        <v>10674</v>
+        <v>10631</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C80">
         <v>4210602</v>
@@ -4028,19 +4461,19 @@
         <v>23</v>
       </c>
       <c r="E80" s="2">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="F80" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="G80">
-        <v>106500</v>
+        <v>3610</v>
       </c>
       <c r="H80">
-        <v>330</v>
+        <v>434</v>
       </c>
       <c r="J80">
-        <v>106500</v>
+        <v>3610</v>
       </c>
       <c r="L80" t="s">
         <v>20</v>
@@ -4049,15 +4482,15 @@
         <v>4</v>
       </c>
       <c r="N80">
-        <v>10707</v>
+        <v>10642</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C81">
         <v>4210602</v>
@@ -4069,16 +4502,16 @@
         <v>46240</v>
       </c>
       <c r="F81" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="G81">
-        <v>84400</v>
+        <v>111265</v>
       </c>
       <c r="H81">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J81">
-        <v>84400</v>
+        <v>111265</v>
       </c>
       <c r="L81" t="s">
         <v>20</v>
@@ -4087,15 +4520,15 @@
         <v>4</v>
       </c>
       <c r="N81">
-        <v>10731</v>
+        <v>10725</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C82">
         <v>4210602</v>
@@ -4107,16 +4540,16 @@
         <v>46241</v>
       </c>
       <c r="F82" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="G82">
-        <v>94700</v>
+        <v>89000</v>
       </c>
       <c r="H82">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="J82">
-        <v>94700</v>
+        <v>89000</v>
       </c>
       <c r="L82" t="s">
         <v>20</v>
@@ -4125,15 +4558,15 @@
         <v>4</v>
       </c>
       <c r="N82">
-        <v>10753</v>
+        <v>10747</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C83">
         <v>4210602</v>
@@ -4145,16 +4578,16 @@
         <v>46242</v>
       </c>
       <c r="F83" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="G83">
-        <v>111600</v>
+        <v>107288</v>
       </c>
       <c r="H83">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="J83">
-        <v>111600</v>
+        <v>107288</v>
       </c>
       <c r="L83" t="s">
         <v>20</v>
@@ -4163,15 +4596,15 @@
         <v>4</v>
       </c>
       <c r="N83">
-        <v>10789</v>
+        <v>10783</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C84">
         <v>4210602</v>
@@ -4180,19 +4613,19 @@
         <v>23</v>
       </c>
       <c r="E84" s="2">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="F84" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="G84">
-        <v>55100</v>
+        <v>119100</v>
       </c>
       <c r="H84">
-        <v>140</v>
+        <v>338</v>
       </c>
       <c r="J84">
-        <v>55100</v>
+        <v>119100</v>
       </c>
       <c r="L84" t="s">
         <v>20</v>
@@ -4201,15 +4634,15 @@
         <v>4</v>
       </c>
       <c r="N84">
-        <v>10800</v>
+        <v>10787</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C85">
         <v>4210602</v>
@@ -4218,19 +4651,19 @@
         <v>23</v>
       </c>
       <c r="E85" s="2">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="F85" t="s">
-        <v>67</v>
+        <v>262</v>
       </c>
       <c r="G85">
-        <v>75000</v>
-      </c>
-      <c r="H85" t="s">
-        <v>68</v>
+        <v>83838</v>
+      </c>
+      <c r="H85">
+        <v>234</v>
       </c>
       <c r="J85">
-        <v>75000</v>
+        <v>83838</v>
       </c>
       <c r="L85" t="s">
         <v>20</v>
@@ -4239,15 +4672,15 @@
         <v>4</v>
       </c>
       <c r="N85">
-        <v>10608</v>
+        <v>10818</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C86">
         <v>4210602</v>
@@ -4256,19 +4689,19 @@
         <v>23</v>
       </c>
       <c r="E86" s="2">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="F86" t="s">
-        <v>172</v>
+        <v>263</v>
       </c>
       <c r="G86">
-        <v>75000</v>
+        <v>123442</v>
       </c>
       <c r="H86" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="J86">
-        <v>75000</v>
+        <v>123442</v>
       </c>
       <c r="L86" t="s">
         <v>20</v>
@@ -4277,15 +4710,15 @@
         <v>4</v>
       </c>
       <c r="N86">
-        <v>10661</v>
+        <v>10843</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C87">
         <v>4210602</v>
@@ -4294,19 +4727,19 @@
         <v>23</v>
       </c>
       <c r="E87" s="2">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="F87" t="s">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="G87">
-        <v>75000</v>
-      </c>
-      <c r="H87" t="s">
-        <v>174</v>
+        <v>69025</v>
+      </c>
+      <c r="H87">
+        <v>134</v>
       </c>
       <c r="J87">
-        <v>75000</v>
+        <v>69025</v>
       </c>
       <c r="L87" t="s">
         <v>20</v>
@@ -4315,15 +4748,15 @@
         <v>4</v>
       </c>
       <c r="N87">
-        <v>10689</v>
+        <v>10873</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B88" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C88">
         <v>4210602</v>
@@ -4332,19 +4765,19 @@
         <v>23</v>
       </c>
       <c r="E88" s="2">
-        <v>46241</v>
+        <v>46249</v>
       </c>
       <c r="F88" t="s">
-        <v>175</v>
+        <v>265</v>
       </c>
       <c r="G88">
-        <v>75000</v>
+        <v>99753</v>
       </c>
       <c r="H88" t="s">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="J88">
-        <v>75000</v>
+        <v>99753</v>
       </c>
       <c r="L88" t="s">
         <v>20</v>
@@ -4353,15 +4786,15 @@
         <v>4</v>
       </c>
       <c r="N88">
-        <v>10734</v>
+        <v>10905</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B89" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C89">
         <v>4210602</v>
@@ -4370,19 +4803,19 @@
         <v>23</v>
       </c>
       <c r="E89" s="2">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="F89" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="G89">
-        <v>75000</v>
-      </c>
-      <c r="H89" t="s">
-        <v>68</v>
+        <v>90846</v>
+      </c>
+      <c r="H89">
+        <v>334</v>
       </c>
       <c r="J89">
-        <v>75000</v>
+        <v>90846</v>
       </c>
       <c r="L89" t="s">
         <v>20</v>
@@ -4391,15 +4824,15 @@
         <v>4</v>
       </c>
       <c r="N89">
-        <v>10758</v>
+        <v>10939</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C90">
         <v>4210602</v>
@@ -4408,19 +4841,19 @@
         <v>23</v>
       </c>
       <c r="E90" s="2">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="F90" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G90">
-        <v>195095</v>
-      </c>
-      <c r="H90" t="s">
-        <v>38</v>
+        <v>84230.720000000001</v>
+      </c>
+      <c r="H90">
+        <v>335</v>
       </c>
       <c r="J90">
-        <v>195095</v>
+        <v>84230.720000000001</v>
       </c>
       <c r="L90" t="s">
         <v>20</v>
@@ -4429,15 +4862,15 @@
         <v>4</v>
       </c>
       <c r="N90">
-        <v>10617</v>
+        <v>10632</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C91">
         <v>4210602</v>
@@ -4446,19 +4879,19 @@
         <v>23</v>
       </c>
       <c r="E91" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="F91" t="s">
-        <v>177</v>
+        <v>60</v>
       </c>
       <c r="G91">
-        <v>299858</v>
-      </c>
-      <c r="H91" t="s">
-        <v>178</v>
+        <v>148816.39000000001</v>
+      </c>
+      <c r="H91">
+        <v>435</v>
       </c>
       <c r="J91">
-        <v>299858</v>
+        <v>148816.39000000001</v>
       </c>
       <c r="L91" t="s">
         <v>20</v>
@@ -4467,15 +4900,15 @@
         <v>4</v>
       </c>
       <c r="N91">
-        <v>10663</v>
+        <v>10643</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C92">
         <v>4210602</v>
@@ -4484,19 +4917,19 @@
         <v>23</v>
       </c>
       <c r="E92" s="2">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="F92" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="G92">
-        <v>199783</v>
-      </c>
-      <c r="H92" t="s">
-        <v>180</v>
+        <v>86601</v>
+      </c>
+      <c r="H92">
+        <v>235</v>
       </c>
       <c r="J92">
-        <v>199783</v>
+        <v>86601</v>
       </c>
       <c r="L92" t="s">
         <v>20</v>
@@ -4505,15 +4938,15 @@
         <v>4</v>
       </c>
       <c r="N92">
-        <v>10716</v>
+        <v>10669</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C93">
         <v>4210602</v>
@@ -4522,19 +4955,19 @@
         <v>23</v>
       </c>
       <c r="E93" s="2">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="F93" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="G93">
-        <v>209985</v>
-      </c>
-      <c r="H93" t="s">
-        <v>182</v>
+        <v>74215</v>
+      </c>
+      <c r="H93">
+        <v>135</v>
       </c>
       <c r="J93">
-        <v>209985</v>
+        <v>74215</v>
       </c>
       <c r="L93" t="s">
         <v>20</v>
@@ -4543,15 +4976,15 @@
         <v>4</v>
       </c>
       <c r="N93">
-        <v>10732</v>
+        <v>10726</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C94">
         <v>4210602</v>
@@ -4560,19 +4993,19 @@
         <v>23</v>
       </c>
       <c r="E94" s="2">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="F94" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="G94">
-        <v>192876</v>
-      </c>
-      <c r="H94" t="s">
-        <v>38</v>
+        <v>101718</v>
+      </c>
+      <c r="H94">
+        <v>235</v>
       </c>
       <c r="J94">
-        <v>192876</v>
+        <v>101718</v>
       </c>
       <c r="L94" t="s">
         <v>20</v>
@@ -4581,15 +5014,15 @@
         <v>4</v>
       </c>
       <c r="N94">
-        <v>10767</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C95">
         <v>4210602</v>
@@ -4601,19 +5034,16 @@
         <v>46242</v>
       </c>
       <c r="F95" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="G95">
-        <v>147748</v>
-      </c>
-      <c r="H95" t="s">
-        <v>38</v>
-      </c>
-      <c r="I95" t="s">
-        <v>185</v>
+        <v>92426.9</v>
+      </c>
+      <c r="H95">
+        <v>335</v>
       </c>
       <c r="J95">
-        <v>147748</v>
+        <v>92426.9</v>
       </c>
       <c r="L95" t="s">
         <v>20</v>
@@ -4622,214 +5052,226 @@
         <v>4</v>
       </c>
       <c r="N95">
-        <v>10767</v>
+        <v>10784</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C96">
-        <v>4210701</v>
+        <v>4210602</v>
       </c>
       <c r="D96" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E96" s="2">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="F96" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="G96">
-        <v>317947.7</v>
-      </c>
-      <c r="I96" t="s">
-        <v>71</v>
+        <v>96221.68</v>
+      </c>
+      <c r="H96">
+        <v>135</v>
       </c>
       <c r="J96">
-        <v>262766.7</v>
-      </c>
-      <c r="K96">
-        <v>55181</v>
+        <v>96221.68</v>
       </c>
       <c r="L96" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M96">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="N96">
+        <v>10795</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C97">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D97" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E97" s="2">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F97" t="s">
-        <v>72</v>
+        <v>268</v>
       </c>
       <c r="G97">
-        <v>32000</v>
-      </c>
-      <c r="I97" t="s">
-        <v>42</v>
+        <v>148805</v>
+      </c>
+      <c r="H97">
+        <v>235</v>
       </c>
       <c r="J97">
-        <v>32000</v>
+        <v>148805</v>
       </c>
       <c r="L97" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M97">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N97">
+        <v>10819</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C98">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E98" s="2">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="F98" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="G98">
-        <v>21500</v>
-      </c>
-      <c r="I98" t="s">
-        <v>187</v>
+        <v>77950</v>
+      </c>
+      <c r="H98" t="s">
+        <v>270</v>
       </c>
       <c r="J98">
-        <v>21500</v>
+        <v>77950</v>
       </c>
       <c r="L98" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M98">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N98">
+        <v>10844</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C99">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D99" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E99" s="2">
-        <v>46240</v>
+        <v>46247</v>
       </c>
       <c r="F99" t="s">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="G99">
-        <v>31000</v>
-      </c>
-      <c r="I99" t="s">
-        <v>42</v>
+        <v>80653.7</v>
+      </c>
+      <c r="H99">
+        <v>135</v>
       </c>
       <c r="J99">
-        <v>31000</v>
+        <v>80653.7</v>
       </c>
       <c r="L99" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M99">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N99">
+        <v>10874</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="B100" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C100">
-        <v>4210206</v>
+        <v>4210602</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E100" s="2">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="F100" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="G100">
-        <v>31500</v>
-      </c>
-      <c r="I100" t="s">
-        <v>190</v>
+        <v>153283</v>
+      </c>
+      <c r="H100" t="s">
+        <v>273</v>
       </c>
       <c r="J100">
-        <v>31500</v>
+        <v>153283</v>
       </c>
       <c r="L100" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M100">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N100">
+        <v>10906</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>382</v>
+        <v>255</v>
       </c>
       <c r="B101" t="s">
-        <v>191</v>
+        <v>30</v>
       </c>
       <c r="C101">
-        <v>4210101</v>
+        <v>4210602</v>
       </c>
       <c r="D101" t="s">
-        <v>192</v>
+        <v>23</v>
       </c>
       <c r="E101" s="2">
-        <v>46242</v>
+        <v>46249</v>
       </c>
       <c r="F101" t="s">
-        <v>193</v>
+        <v>274</v>
       </c>
       <c r="G101">
-        <v>150000</v>
+        <v>191880</v>
       </c>
       <c r="H101">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J101">
-        <v>150000</v>
+        <v>191880</v>
       </c>
       <c r="L101" t="s">
         <v>20</v>
@@ -4838,539 +5280,4151 @@
         <v>4</v>
       </c>
       <c r="N101">
-        <v>10780</v>
+        <v>10940</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>396</v>
+        <v>256</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C102">
-        <v>4210301</v>
+        <v>4210602</v>
       </c>
       <c r="D102" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E102" s="2">
         <v>46237</v>
       </c>
       <c r="F102" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="G102">
-        <v>209400</v>
-      </c>
-      <c r="I102" t="s">
-        <v>27</v>
+        <v>92522</v>
+      </c>
+      <c r="H102">
+        <v>436</v>
       </c>
       <c r="J102">
-        <v>209400</v>
+        <v>92522</v>
       </c>
       <c r="L102" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M102">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N102">
+        <v>10644</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>396</v>
+        <v>256</v>
       </c>
       <c r="B103" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C103">
-        <v>4210301</v>
+        <v>4210602</v>
       </c>
       <c r="D103" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E103" s="2">
         <v>46238</v>
       </c>
       <c r="F103" t="s">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="G103">
-        <v>60000</v>
-      </c>
-      <c r="I103" t="s">
-        <v>45</v>
+        <v>117384</v>
+      </c>
+      <c r="H103">
+        <v>236</v>
       </c>
       <c r="J103">
-        <v>60000</v>
+        <v>117384</v>
       </c>
       <c r="L103" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M103">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N103">
+        <v>10670</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>396</v>
+        <v>256</v>
       </c>
       <c r="B104" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C104">
-        <v>4210301</v>
+        <v>4210602</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E104" s="2">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F104" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
       <c r="G104">
-        <v>2815200</v>
-      </c>
-      <c r="I104" t="s">
-        <v>195</v>
+        <v>68801</v>
+      </c>
+      <c r="H104">
+        <v>234</v>
       </c>
       <c r="J104">
-        <v>2815200</v>
+        <v>68801</v>
       </c>
       <c r="L104" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M104">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N104">
+        <v>10668</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>396</v>
+        <v>256</v>
       </c>
       <c r="B105" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C105">
-        <v>4210301</v>
+        <v>4210602</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E105" s="2">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F105" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="G105">
-        <v>6000</v>
-      </c>
-      <c r="I105" t="s">
-        <v>197</v>
+        <v>81309</v>
+      </c>
+      <c r="H105">
+        <v>326</v>
       </c>
       <c r="J105">
-        <v>6000</v>
+        <v>81309</v>
       </c>
       <c r="L105" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M105">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="N105">
+        <v>10703</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106">
+        <v>256</v>
+      </c>
+      <c r="B106" t="s">
+        <v>31</v>
+      </c>
+      <c r="C106">
+        <v>4210602</v>
+      </c>
+      <c r="D106" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F106" t="s">
+        <v>148</v>
+      </c>
+      <c r="G106">
+        <v>153511</v>
+      </c>
+      <c r="H106">
+        <v>136</v>
+      </c>
+      <c r="J106">
+        <v>153511</v>
+      </c>
+      <c r="L106" t="s">
+        <v>20</v>
+      </c>
+      <c r="M106">
+        <v>4</v>
+      </c>
+      <c r="N106">
+        <v>10727</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>256</v>
+      </c>
+      <c r="B107" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107">
+        <v>4210602</v>
+      </c>
+      <c r="D107" t="s">
+        <v>23</v>
+      </c>
+      <c r="E107" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F107" t="s">
+        <v>149</v>
+      </c>
+      <c r="G107">
+        <v>135836.13</v>
+      </c>
+      <c r="H107">
+        <v>236</v>
+      </c>
+      <c r="J107">
+        <v>135836.13</v>
+      </c>
+      <c r="L107" t="s">
+        <v>20</v>
+      </c>
+      <c r="M107">
+        <v>4</v>
+      </c>
+      <c r="N107">
+        <v>10749</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>256</v>
+      </c>
+      <c r="B108" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108">
+        <v>4210602</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F108" t="s">
+        <v>150</v>
+      </c>
+      <c r="G108">
+        <v>93500</v>
+      </c>
+      <c r="H108">
+        <v>336</v>
+      </c>
+      <c r="J108">
+        <v>93500</v>
+      </c>
+      <c r="L108" t="s">
+        <v>20</v>
+      </c>
+      <c r="M108">
+        <v>4</v>
+      </c>
+      <c r="N108">
+        <v>10785</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>256</v>
+      </c>
+      <c r="B109" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109">
+        <v>4210602</v>
+      </c>
+      <c r="D109" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F109" t="s">
+        <v>275</v>
+      </c>
+      <c r="G109">
+        <v>26555</v>
+      </c>
+      <c r="H109">
+        <v>136</v>
+      </c>
+      <c r="J109">
+        <v>26555</v>
+      </c>
+      <c r="L109" t="s">
+        <v>20</v>
+      </c>
+      <c r="M109">
+        <v>4</v>
+      </c>
+      <c r="N109">
+        <v>10796</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>256</v>
+      </c>
+      <c r="B110" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110">
+        <v>4210602</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F110" t="s">
+        <v>276</v>
+      </c>
+      <c r="G110">
+        <v>110988</v>
+      </c>
+      <c r="H110">
+        <v>236</v>
+      </c>
+      <c r="J110">
+        <v>110988</v>
+      </c>
+      <c r="L110" t="s">
+        <v>20</v>
+      </c>
+      <c r="M110">
+        <v>4</v>
+      </c>
+      <c r="N110">
+        <v>10820</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>256</v>
+      </c>
+      <c r="B111" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111">
+        <v>4210602</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F111" t="s">
+        <v>277</v>
+      </c>
+      <c r="G111">
+        <v>88291.61</v>
+      </c>
+      <c r="H111">
+        <v>326</v>
+      </c>
+      <c r="J111">
+        <v>88291.61</v>
+      </c>
+      <c r="L111" t="s">
+        <v>20</v>
+      </c>
+      <c r="M111">
+        <v>4</v>
+      </c>
+      <c r="N111">
+        <v>10845</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>256</v>
+      </c>
+      <c r="B112" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112">
+        <v>4210602</v>
+      </c>
+      <c r="D112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F112" t="s">
+        <v>278</v>
+      </c>
+      <c r="G112">
+        <v>175282</v>
+      </c>
+      <c r="H112">
+        <v>136</v>
+      </c>
+      <c r="J112">
+        <v>175282</v>
+      </c>
+      <c r="L112" t="s">
+        <v>20</v>
+      </c>
+      <c r="M112">
+        <v>4</v>
+      </c>
+      <c r="N112">
+        <v>10875</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>256</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113">
+        <v>4210602</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F113" t="s">
+        <v>279</v>
+      </c>
+      <c r="G113">
+        <v>398069</v>
+      </c>
+      <c r="H113">
+        <v>226</v>
+      </c>
+      <c r="J113">
+        <v>398069</v>
+      </c>
+      <c r="L113" t="s">
+        <v>20</v>
+      </c>
+      <c r="M113">
+        <v>4</v>
+      </c>
+      <c r="N113">
+        <v>10907</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>256</v>
+      </c>
+      <c r="B114" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114">
+        <v>4210602</v>
+      </c>
+      <c r="D114" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F114" t="s">
+        <v>280</v>
+      </c>
+      <c r="G114">
+        <v>119363.1</v>
+      </c>
+      <c r="H114">
+        <v>336</v>
+      </c>
+      <c r="J114">
+        <v>119363.1</v>
+      </c>
+      <c r="L114" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114">
+        <v>4</v>
+      </c>
+      <c r="N114">
+        <v>10941</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>257</v>
+      </c>
+      <c r="B115" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115">
+        <v>4210602</v>
+      </c>
+      <c r="D115" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F115" t="s">
+        <v>62</v>
+      </c>
+      <c r="G115">
+        <v>80960.759999999995</v>
+      </c>
+      <c r="H115">
+        <v>337</v>
+      </c>
+      <c r="J115">
+        <v>80960.759999999995</v>
+      </c>
+      <c r="L115" t="s">
+        <v>20</v>
+      </c>
+      <c r="M115">
+        <v>4</v>
+      </c>
+      <c r="N115">
+        <v>10634</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>257</v>
+      </c>
+      <c r="B116" t="s">
+        <v>32</v>
+      </c>
+      <c r="C116">
+        <v>4210602</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F116" t="s">
+        <v>63</v>
+      </c>
+      <c r="G116">
+        <v>42314</v>
+      </c>
+      <c r="H116">
+        <v>437</v>
+      </c>
+      <c r="J116">
+        <v>42314</v>
+      </c>
+      <c r="L116" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116">
+        <v>4</v>
+      </c>
+      <c r="N116">
+        <v>10645</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>257</v>
+      </c>
+      <c r="B117" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117">
+        <v>4210602</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F117" t="s">
+        <v>151</v>
+      </c>
+      <c r="G117">
+        <v>115782</v>
+      </c>
+      <c r="H117">
+        <v>237</v>
+      </c>
+      <c r="J117">
+        <v>115782</v>
+      </c>
+      <c r="L117" t="s">
+        <v>20</v>
+      </c>
+      <c r="M117">
+        <v>4</v>
+      </c>
+      <c r="N117">
+        <v>10671</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>257</v>
+      </c>
+      <c r="B118" t="s">
+        <v>32</v>
+      </c>
+      <c r="C118">
+        <v>4210602</v>
+      </c>
+      <c r="D118" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F118" t="s">
+        <v>152</v>
+      </c>
+      <c r="G118">
+        <v>36353</v>
+      </c>
+      <c r="H118">
+        <v>137</v>
+      </c>
+      <c r="J118">
+        <v>36353</v>
+      </c>
+      <c r="L118" t="s">
+        <v>20</v>
+      </c>
+      <c r="M118">
+        <v>4</v>
+      </c>
+      <c r="N118">
+        <v>10728</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>257</v>
+      </c>
+      <c r="B119" t="s">
+        <v>32</v>
+      </c>
+      <c r="C119">
+        <v>4210602</v>
+      </c>
+      <c r="D119" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F119" t="s">
+        <v>153</v>
+      </c>
+      <c r="G119">
+        <v>112749</v>
+      </c>
+      <c r="H119">
+        <v>237</v>
+      </c>
+      <c r="J119">
+        <v>112749</v>
+      </c>
+      <c r="L119" t="s">
+        <v>20</v>
+      </c>
+      <c r="M119">
+        <v>4</v>
+      </c>
+      <c r="N119">
+        <v>10750</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>257</v>
+      </c>
+      <c r="B120" t="s">
+        <v>32</v>
+      </c>
+      <c r="C120">
+        <v>4210602</v>
+      </c>
+      <c r="D120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F120" t="s">
+        <v>154</v>
+      </c>
+      <c r="G120">
+        <v>66203</v>
+      </c>
+      <c r="H120">
+        <v>337</v>
+      </c>
+      <c r="J120">
+        <v>66203</v>
+      </c>
+      <c r="L120" t="s">
+        <v>20</v>
+      </c>
+      <c r="M120">
+        <v>4</v>
+      </c>
+      <c r="N120">
+        <v>10786</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>257</v>
+      </c>
+      <c r="B121" t="s">
+        <v>32</v>
+      </c>
+      <c r="C121">
+        <v>4210602</v>
+      </c>
+      <c r="D121" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F121" t="s">
+        <v>281</v>
+      </c>
+      <c r="G121">
+        <v>122823</v>
+      </c>
+      <c r="H121">
+        <v>237</v>
+      </c>
+      <c r="J121">
+        <v>122823</v>
+      </c>
+      <c r="L121" t="s">
+        <v>20</v>
+      </c>
+      <c r="M121">
+        <v>4</v>
+      </c>
+      <c r="N121">
+        <v>10821</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>257</v>
+      </c>
+      <c r="B122" t="s">
+        <v>32</v>
+      </c>
+      <c r="C122">
+        <v>4210602</v>
+      </c>
+      <c r="D122" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F122" t="s">
+        <v>282</v>
+      </c>
+      <c r="G122">
+        <v>12000</v>
+      </c>
+      <c r="H122">
+        <v>237</v>
+      </c>
+      <c r="I122" t="s">
+        <v>283</v>
+      </c>
+      <c r="J122">
+        <v>12000</v>
+      </c>
+      <c r="L122" t="s">
+        <v>20</v>
+      </c>
+      <c r="M122">
+        <v>4</v>
+      </c>
+      <c r="N122">
+        <v>10821</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>257</v>
+      </c>
+      <c r="B123" t="s">
+        <v>32</v>
+      </c>
+      <c r="C123">
+        <v>4210602</v>
+      </c>
+      <c r="D123" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F123" t="s">
+        <v>284</v>
+      </c>
+      <c r="G123">
+        <v>122963.23</v>
+      </c>
+      <c r="H123">
+        <v>327</v>
+      </c>
+      <c r="J123">
+        <v>122963.23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>20</v>
+      </c>
+      <c r="M123">
+        <v>4</v>
+      </c>
+      <c r="N123">
+        <v>10846</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>257</v>
+      </c>
+      <c r="B124" t="s">
+        <v>32</v>
+      </c>
+      <c r="C124">
+        <v>4210602</v>
+      </c>
+      <c r="D124" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F124" t="s">
+        <v>285</v>
+      </c>
+      <c r="G124">
+        <v>154103</v>
+      </c>
+      <c r="H124">
+        <v>137</v>
+      </c>
+      <c r="J124">
+        <v>154103</v>
+      </c>
+      <c r="L124" t="s">
+        <v>20</v>
+      </c>
+      <c r="M124">
+        <v>4</v>
+      </c>
+      <c r="N124">
+        <v>10876</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>257</v>
+      </c>
+      <c r="B125" t="s">
+        <v>32</v>
+      </c>
+      <c r="C125">
+        <v>4210602</v>
+      </c>
+      <c r="D125" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F125" t="s">
+        <v>286</v>
+      </c>
+      <c r="G125">
+        <v>12000</v>
+      </c>
+      <c r="H125" t="s">
+        <v>287</v>
+      </c>
+      <c r="J125">
+        <v>12000</v>
+      </c>
+      <c r="L125" t="s">
+        <v>20</v>
+      </c>
+      <c r="M125">
+        <v>4</v>
+      </c>
+      <c r="N125">
+        <v>10876</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>257</v>
+      </c>
+      <c r="B126" t="s">
+        <v>32</v>
+      </c>
+      <c r="C126">
+        <v>4210602</v>
+      </c>
+      <c r="D126" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F126" t="s">
+        <v>288</v>
+      </c>
+      <c r="G126">
+        <v>187603</v>
+      </c>
+      <c r="H126">
+        <v>227</v>
+      </c>
+      <c r="J126">
+        <v>187603</v>
+      </c>
+      <c r="L126" t="s">
+        <v>20</v>
+      </c>
+      <c r="M126">
+        <v>4</v>
+      </c>
+      <c r="N126">
+        <v>10908</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>257</v>
+      </c>
+      <c r="B127" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127">
+        <v>4210602</v>
+      </c>
+      <c r="D127" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F127" t="s">
+        <v>289</v>
+      </c>
+      <c r="G127">
+        <v>70821</v>
+      </c>
+      <c r="H127">
+        <v>337</v>
+      </c>
+      <c r="J127">
+        <v>70821</v>
+      </c>
+      <c r="L127" t="s">
+        <v>20</v>
+      </c>
+      <c r="M127">
+        <v>4</v>
+      </c>
+      <c r="N127">
+        <v>10942</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>257</v>
+      </c>
+      <c r="B128" t="s">
+        <v>32</v>
+      </c>
+      <c r="C128">
+        <v>4210602</v>
+      </c>
+      <c r="D128" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F128" t="s">
+        <v>290</v>
+      </c>
+      <c r="G128">
+        <v>19000</v>
+      </c>
+      <c r="H128">
+        <v>337</v>
+      </c>
+      <c r="I128" t="s">
+        <v>291</v>
+      </c>
+      <c r="J128">
+        <v>19000</v>
+      </c>
+      <c r="L128" t="s">
+        <v>20</v>
+      </c>
+      <c r="M128">
+        <v>4</v>
+      </c>
+      <c r="N128">
+        <v>10942</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>257</v>
+      </c>
+      <c r="B129" t="s">
+        <v>32</v>
+      </c>
+      <c r="C129">
+        <v>4210602</v>
+      </c>
+      <c r="D129" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" s="2">
+        <v>46252</v>
+      </c>
+      <c r="F129" t="s">
+        <v>292</v>
+      </c>
+      <c r="G129">
+        <v>14000</v>
+      </c>
+      <c r="H129">
+        <v>437</v>
+      </c>
+      <c r="J129">
+        <v>14000</v>
+      </c>
+      <c r="L129" t="s">
+        <v>20</v>
+      </c>
+      <c r="M129">
+        <v>4</v>
+      </c>
+      <c r="N129">
+        <v>10954</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>258</v>
+      </c>
+      <c r="B130" t="s">
+        <v>33</v>
+      </c>
+      <c r="C130">
+        <v>4210602</v>
+      </c>
+      <c r="D130" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F130" t="s">
+        <v>64</v>
+      </c>
+      <c r="G130">
+        <v>144723</v>
+      </c>
+      <c r="H130">
+        <v>438</v>
+      </c>
+      <c r="J130">
+        <v>144723</v>
+      </c>
+      <c r="L130" t="s">
+        <v>20</v>
+      </c>
+      <c r="M130">
+        <v>4</v>
+      </c>
+      <c r="N130">
+        <v>10646</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>258</v>
+      </c>
+      <c r="B131" t="s">
+        <v>33</v>
+      </c>
+      <c r="C131">
+        <v>4210602</v>
+      </c>
+      <c r="D131" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F131" t="s">
+        <v>155</v>
+      </c>
+      <c r="G131">
+        <v>90709.75</v>
+      </c>
+      <c r="H131">
+        <v>238</v>
+      </c>
+      <c r="J131">
+        <v>90709.75</v>
+      </c>
+      <c r="L131" t="s">
+        <v>20</v>
+      </c>
+      <c r="M131">
+        <v>4</v>
+      </c>
+      <c r="N131">
+        <v>10672</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>258</v>
+      </c>
+      <c r="B132" t="s">
+        <v>33</v>
+      </c>
+      <c r="C132">
+        <v>4210602</v>
+      </c>
+      <c r="D132" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F132" t="s">
+        <v>156</v>
+      </c>
+      <c r="G132">
+        <v>82588</v>
+      </c>
+      <c r="H132">
+        <v>328</v>
+      </c>
+      <c r="J132">
+        <v>82588</v>
+      </c>
+      <c r="L132" t="s">
+        <v>20</v>
+      </c>
+      <c r="M132">
+        <v>4</v>
+      </c>
+      <c r="N132">
+        <v>10705</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>258</v>
+      </c>
+      <c r="B133" t="s">
+        <v>33</v>
+      </c>
+      <c r="C133">
+        <v>4210602</v>
+      </c>
+      <c r="D133" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F133" t="s">
+        <v>157</v>
+      </c>
+      <c r="G133">
+        <v>108830</v>
+      </c>
+      <c r="H133">
+        <v>138</v>
+      </c>
+      <c r="J133">
+        <v>108830</v>
+      </c>
+      <c r="L133" t="s">
+        <v>20</v>
+      </c>
+      <c r="M133">
+        <v>4</v>
+      </c>
+      <c r="N133">
+        <v>10729</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>258</v>
+      </c>
+      <c r="B134" t="s">
+        <v>33</v>
+      </c>
+      <c r="C134">
+        <v>4210602</v>
+      </c>
+      <c r="D134" t="s">
+        <v>23</v>
+      </c>
+      <c r="E134" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F134" t="s">
+        <v>293</v>
+      </c>
+      <c r="G134">
+        <v>153492</v>
+      </c>
+      <c r="H134">
+        <v>138</v>
+      </c>
+      <c r="J134">
+        <v>153492</v>
+      </c>
+      <c r="L134" t="s">
+        <v>20</v>
+      </c>
+      <c r="M134">
+        <v>4</v>
+      </c>
+      <c r="N134">
+        <v>10798</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>258</v>
+      </c>
+      <c r="B135" t="s">
+        <v>33</v>
+      </c>
+      <c r="C135">
+        <v>4210602</v>
+      </c>
+      <c r="D135" t="s">
+        <v>23</v>
+      </c>
+      <c r="E135" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F135" t="s">
+        <v>294</v>
+      </c>
+      <c r="G135">
+        <v>77500</v>
+      </c>
+      <c r="H135">
+        <v>238</v>
+      </c>
+      <c r="J135">
+        <v>77500</v>
+      </c>
+      <c r="L135" t="s">
+        <v>20</v>
+      </c>
+      <c r="M135">
+        <v>4</v>
+      </c>
+      <c r="N135">
+        <v>10822</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>258</v>
+      </c>
+      <c r="B136" t="s">
+        <v>33</v>
+      </c>
+      <c r="C136">
+        <v>4210602</v>
+      </c>
+      <c r="D136" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F136" t="s">
+        <v>295</v>
+      </c>
+      <c r="G136">
+        <v>77785.22</v>
+      </c>
+      <c r="H136">
+        <v>328</v>
+      </c>
+      <c r="J136">
+        <v>77785.22</v>
+      </c>
+      <c r="L136" t="s">
+        <v>20</v>
+      </c>
+      <c r="M136">
+        <v>4</v>
+      </c>
+      <c r="N136">
+        <v>10847</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>258</v>
+      </c>
+      <c r="B137" t="s">
+        <v>33</v>
+      </c>
+      <c r="C137">
+        <v>4210602</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F137" t="s">
+        <v>296</v>
+      </c>
+      <c r="G137">
+        <v>110257.7</v>
+      </c>
+      <c r="H137">
+        <v>138</v>
+      </c>
+      <c r="J137">
+        <v>110257.7</v>
+      </c>
+      <c r="L137" t="s">
+        <v>20</v>
+      </c>
+      <c r="M137">
+        <v>4</v>
+      </c>
+      <c r="N137">
+        <v>10877</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>258</v>
+      </c>
+      <c r="B138" t="s">
+        <v>33</v>
+      </c>
+      <c r="C138">
+        <v>4210602</v>
+      </c>
+      <c r="D138" t="s">
+        <v>23</v>
+      </c>
+      <c r="E138" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F138" t="s">
+        <v>297</v>
+      </c>
+      <c r="G138">
+        <v>89875</v>
+      </c>
+      <c r="H138">
+        <v>228</v>
+      </c>
+      <c r="J138">
+        <v>89875</v>
+      </c>
+      <c r="L138" t="s">
+        <v>20</v>
+      </c>
+      <c r="M138">
+        <v>4</v>
+      </c>
+      <c r="N138">
+        <v>10909</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>258</v>
+      </c>
+      <c r="B139" t="s">
+        <v>33</v>
+      </c>
+      <c r="C139">
+        <v>4210602</v>
+      </c>
+      <c r="D139" t="s">
+        <v>23</v>
+      </c>
+      <c r="E139" s="2">
+        <v>46252</v>
+      </c>
+      <c r="F139" t="s">
+        <v>298</v>
+      </c>
+      <c r="G139">
+        <v>115064.14</v>
+      </c>
+      <c r="H139">
+        <v>438</v>
+      </c>
+      <c r="J139">
+        <v>115064.14</v>
+      </c>
+      <c r="L139" t="s">
+        <v>20</v>
+      </c>
+      <c r="M139">
+        <v>4</v>
+      </c>
+      <c r="N139">
+        <v>10956</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>259</v>
+      </c>
+      <c r="B140" t="s">
+        <v>158</v>
+      </c>
+      <c r="C140">
+        <v>4210602</v>
+      </c>
+      <c r="D140" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F140" t="s">
+        <v>159</v>
+      </c>
+      <c r="G140">
+        <v>73138</v>
+      </c>
+      <c r="H140">
+        <v>439</v>
+      </c>
+      <c r="J140">
+        <v>73138</v>
+      </c>
+      <c r="L140" t="s">
+        <v>20</v>
+      </c>
+      <c r="M140">
+        <v>4</v>
+      </c>
+      <c r="N140">
+        <v>10647</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>259</v>
+      </c>
+      <c r="B141" t="s">
+        <v>158</v>
+      </c>
+      <c r="C141">
+        <v>4210602</v>
+      </c>
+      <c r="D141" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F141" t="s">
+        <v>160</v>
+      </c>
+      <c r="G141">
+        <v>91665</v>
+      </c>
+      <c r="H141">
+        <v>239</v>
+      </c>
+      <c r="J141">
+        <v>91665</v>
+      </c>
+      <c r="L141" t="s">
+        <v>20</v>
+      </c>
+      <c r="M141">
+        <v>4</v>
+      </c>
+      <c r="N141">
+        <v>10673</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>259</v>
+      </c>
+      <c r="B142" t="s">
+        <v>158</v>
+      </c>
+      <c r="C142">
+        <v>4210602</v>
+      </c>
+      <c r="D142" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F142" t="s">
+        <v>161</v>
+      </c>
+      <c r="G142">
+        <v>100606</v>
+      </c>
+      <c r="H142">
+        <v>329</v>
+      </c>
+      <c r="J142">
+        <v>100606</v>
+      </c>
+      <c r="L142" t="s">
+        <v>20</v>
+      </c>
+      <c r="M142">
+        <v>4</v>
+      </c>
+      <c r="N142">
+        <v>10706</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>259</v>
+      </c>
+      <c r="B143" t="s">
+        <v>158</v>
+      </c>
+      <c r="C143">
+        <v>4210602</v>
+      </c>
+      <c r="D143" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F143" t="s">
+        <v>162</v>
+      </c>
+      <c r="G143">
+        <v>67555</v>
+      </c>
+      <c r="H143">
+        <v>139</v>
+      </c>
+      <c r="J143">
+        <v>67555</v>
+      </c>
+      <c r="L143" t="s">
+        <v>20</v>
+      </c>
+      <c r="M143">
+        <v>4</v>
+      </c>
+      <c r="N143">
+        <v>10730</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>259</v>
+      </c>
+      <c r="B144" t="s">
+        <v>158</v>
+      </c>
+      <c r="C144">
+        <v>4210602</v>
+      </c>
+      <c r="D144" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F144" t="s">
+        <v>163</v>
+      </c>
+      <c r="G144">
+        <v>107162</v>
+      </c>
+      <c r="H144">
+        <v>239</v>
+      </c>
+      <c r="J144">
+        <v>107162</v>
+      </c>
+      <c r="L144" t="s">
+        <v>20</v>
+      </c>
+      <c r="M144">
+        <v>4</v>
+      </c>
+      <c r="N144">
+        <v>10752</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>259</v>
+      </c>
+      <c r="B145" t="s">
+        <v>158</v>
+      </c>
+      <c r="C145">
+        <v>4210602</v>
+      </c>
+      <c r="D145" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F145" t="s">
+        <v>164</v>
+      </c>
+      <c r="G145">
+        <v>166737</v>
+      </c>
+      <c r="H145">
+        <v>339</v>
+      </c>
+      <c r="J145">
+        <v>166737</v>
+      </c>
+      <c r="L145" t="s">
+        <v>20</v>
+      </c>
+      <c r="M145">
+        <v>4</v>
+      </c>
+      <c r="N145">
+        <v>10788</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>259</v>
+      </c>
+      <c r="B146" t="s">
+        <v>158</v>
+      </c>
+      <c r="C146">
+        <v>4210602</v>
+      </c>
+      <c r="D146" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F146" t="s">
+        <v>299</v>
+      </c>
+      <c r="G146">
+        <v>78103</v>
+      </c>
+      <c r="H146">
+        <v>139</v>
+      </c>
+      <c r="J146">
+        <v>78103</v>
+      </c>
+      <c r="L146" t="s">
+        <v>20</v>
+      </c>
+      <c r="M146">
+        <v>4</v>
+      </c>
+      <c r="N146">
+        <v>10799</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>259</v>
+      </c>
+      <c r="B147" t="s">
+        <v>158</v>
+      </c>
+      <c r="C147">
+        <v>4210602</v>
+      </c>
+      <c r="D147" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F147" t="s">
+        <v>300</v>
+      </c>
+      <c r="G147">
+        <v>118555</v>
+      </c>
+      <c r="H147">
+        <v>239</v>
+      </c>
+      <c r="J147">
+        <v>118555</v>
+      </c>
+      <c r="L147" t="s">
+        <v>20</v>
+      </c>
+      <c r="M147">
+        <v>4</v>
+      </c>
+      <c r="N147">
+        <v>10823</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>259</v>
+      </c>
+      <c r="B148" t="s">
+        <v>158</v>
+      </c>
+      <c r="C148">
+        <v>4210602</v>
+      </c>
+      <c r="D148" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F148" t="s">
+        <v>301</v>
+      </c>
+      <c r="G148">
+        <v>150483</v>
+      </c>
+      <c r="H148">
+        <v>329</v>
+      </c>
+      <c r="J148">
+        <v>150483</v>
+      </c>
+      <c r="L148" t="s">
+        <v>20</v>
+      </c>
+      <c r="M148">
+        <v>4</v>
+      </c>
+      <c r="N148">
+        <v>10848</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>259</v>
+      </c>
+      <c r="B149" t="s">
+        <v>158</v>
+      </c>
+      <c r="C149">
+        <v>4210602</v>
+      </c>
+      <c r="D149" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F149" t="s">
+        <v>302</v>
+      </c>
+      <c r="G149">
+        <v>116062</v>
+      </c>
+      <c r="H149">
+        <v>139</v>
+      </c>
+      <c r="J149">
+        <v>116062</v>
+      </c>
+      <c r="L149" t="s">
+        <v>20</v>
+      </c>
+      <c r="M149">
+        <v>4</v>
+      </c>
+      <c r="N149">
+        <v>10878</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>259</v>
+      </c>
+      <c r="B150" t="s">
+        <v>158</v>
+      </c>
+      <c r="C150">
+        <v>4210602</v>
+      </c>
+      <c r="D150" t="s">
+        <v>23</v>
+      </c>
+      <c r="E150" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F150" t="s">
+        <v>303</v>
+      </c>
+      <c r="G150">
+        <v>145253</v>
+      </c>
+      <c r="H150">
+        <v>229</v>
+      </c>
+      <c r="J150">
+        <v>145253</v>
+      </c>
+      <c r="L150" t="s">
+        <v>20</v>
+      </c>
+      <c r="M150">
+        <v>4</v>
+      </c>
+      <c r="N150">
+        <v>10910</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>259</v>
+      </c>
+      <c r="B151" t="s">
+        <v>158</v>
+      </c>
+      <c r="C151">
+        <v>4210602</v>
+      </c>
+      <c r="D151" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F151" t="s">
+        <v>304</v>
+      </c>
+      <c r="G151">
+        <v>152469</v>
+      </c>
+      <c r="H151">
+        <v>339</v>
+      </c>
+      <c r="J151">
+        <v>152469</v>
+      </c>
+      <c r="L151" t="s">
+        <v>20</v>
+      </c>
+      <c r="M151">
+        <v>4</v>
+      </c>
+      <c r="N151">
+        <v>10944</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>260</v>
+      </c>
+      <c r="B152" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152">
+        <v>4210602</v>
+      </c>
+      <c r="D152" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F152" t="s">
+        <v>65</v>
+      </c>
+      <c r="G152">
+        <v>67600</v>
+      </c>
+      <c r="H152">
+        <v>331</v>
+      </c>
+      <c r="J152">
+        <v>67600</v>
+      </c>
+      <c r="L152" t="s">
+        <v>20</v>
+      </c>
+      <c r="M152">
+        <v>4</v>
+      </c>
+      <c r="N152">
+        <v>10629</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>260</v>
+      </c>
+      <c r="B153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C153">
+        <v>4210602</v>
+      </c>
+      <c r="D153" t="s">
+        <v>23</v>
+      </c>
+      <c r="E153" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F153" t="s">
+        <v>66</v>
+      </c>
+      <c r="G153">
+        <v>47000</v>
+      </c>
+      <c r="H153">
+        <v>440</v>
+      </c>
+      <c r="J153">
+        <v>47000</v>
+      </c>
+      <c r="L153" t="s">
+        <v>20</v>
+      </c>
+      <c r="M153">
+        <v>4</v>
+      </c>
+      <c r="N153">
+        <v>10648</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
+        <v>34</v>
+      </c>
+      <c r="C154">
+        <v>4210602</v>
+      </c>
+      <c r="D154" t="s">
+        <v>23</v>
+      </c>
+      <c r="E154" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F154" t="s">
+        <v>165</v>
+      </c>
+      <c r="G154">
+        <v>133000</v>
+      </c>
+      <c r="H154">
+        <v>240</v>
+      </c>
+      <c r="J154">
+        <v>133000</v>
+      </c>
+      <c r="L154" t="s">
+        <v>20</v>
+      </c>
+      <c r="M154">
+        <v>4</v>
+      </c>
+      <c r="N154">
+        <v>10674</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>260</v>
+      </c>
+      <c r="B155" t="s">
+        <v>34</v>
+      </c>
+      <c r="C155">
+        <v>4210602</v>
+      </c>
+      <c r="D155" t="s">
+        <v>23</v>
+      </c>
+      <c r="E155" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F155" t="s">
+        <v>166</v>
+      </c>
+      <c r="G155">
+        <v>750000</v>
+      </c>
+      <c r="H155">
+        <v>240</v>
+      </c>
+      <c r="J155">
+        <v>750000</v>
+      </c>
+      <c r="L155" t="s">
+        <v>20</v>
+      </c>
+      <c r="M155">
+        <v>4</v>
+      </c>
+      <c r="N155">
+        <v>10674</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>260</v>
+      </c>
+      <c r="B156" t="s">
+        <v>34</v>
+      </c>
+      <c r="C156">
+        <v>4210602</v>
+      </c>
+      <c r="D156" t="s">
+        <v>23</v>
+      </c>
+      <c r="E156" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F156" t="s">
+        <v>167</v>
+      </c>
+      <c r="G156">
+        <v>106500</v>
+      </c>
+      <c r="H156">
+        <v>330</v>
+      </c>
+      <c r="J156">
+        <v>106500</v>
+      </c>
+      <c r="L156" t="s">
+        <v>20</v>
+      </c>
+      <c r="M156">
+        <v>4</v>
+      </c>
+      <c r="N156">
+        <v>10707</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>260</v>
+      </c>
+      <c r="B157" t="s">
+        <v>34</v>
+      </c>
+      <c r="C157">
+        <v>4210602</v>
+      </c>
+      <c r="D157" t="s">
+        <v>23</v>
+      </c>
+      <c r="E157" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F157" t="s">
+        <v>168</v>
+      </c>
+      <c r="G157">
+        <v>84400</v>
+      </c>
+      <c r="H157">
+        <v>140</v>
+      </c>
+      <c r="J157">
+        <v>84400</v>
+      </c>
+      <c r="L157" t="s">
+        <v>20</v>
+      </c>
+      <c r="M157">
+        <v>4</v>
+      </c>
+      <c r="N157">
+        <v>10731</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>260</v>
+      </c>
+      <c r="B158" t="s">
+        <v>34</v>
+      </c>
+      <c r="C158">
+        <v>4210602</v>
+      </c>
+      <c r="D158" t="s">
+        <v>23</v>
+      </c>
+      <c r="E158" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F158" t="s">
+        <v>169</v>
+      </c>
+      <c r="G158">
+        <v>94700</v>
+      </c>
+      <c r="H158">
+        <v>240</v>
+      </c>
+      <c r="J158">
+        <v>94700</v>
+      </c>
+      <c r="L158" t="s">
+        <v>20</v>
+      </c>
+      <c r="M158">
+        <v>4</v>
+      </c>
+      <c r="N158">
+        <v>10753</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>260</v>
+      </c>
+      <c r="B159" t="s">
+        <v>34</v>
+      </c>
+      <c r="C159">
+        <v>4210602</v>
+      </c>
+      <c r="D159" t="s">
+        <v>23</v>
+      </c>
+      <c r="E159" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F159" t="s">
+        <v>170</v>
+      </c>
+      <c r="G159">
+        <v>111600</v>
+      </c>
+      <c r="H159">
+        <v>340</v>
+      </c>
+      <c r="J159">
+        <v>111600</v>
+      </c>
+      <c r="L159" t="s">
+        <v>20</v>
+      </c>
+      <c r="M159">
+        <v>4</v>
+      </c>
+      <c r="N159">
+        <v>10789</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>260</v>
+      </c>
+      <c r="B160" t="s">
+        <v>34</v>
+      </c>
+      <c r="C160">
+        <v>4210602</v>
+      </c>
+      <c r="D160" t="s">
+        <v>23</v>
+      </c>
+      <c r="E160" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F160" t="s">
+        <v>171</v>
+      </c>
+      <c r="G160">
+        <v>55100</v>
+      </c>
+      <c r="H160">
+        <v>140</v>
+      </c>
+      <c r="J160">
+        <v>55100</v>
+      </c>
+      <c r="L160" t="s">
+        <v>20</v>
+      </c>
+      <c r="M160">
+        <v>4</v>
+      </c>
+      <c r="N160">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>260</v>
+      </c>
+      <c r="B161" t="s">
+        <v>34</v>
+      </c>
+      <c r="C161">
+        <v>4210602</v>
+      </c>
+      <c r="D161" t="s">
+        <v>23</v>
+      </c>
+      <c r="E161" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F161" t="s">
+        <v>305</v>
+      </c>
+      <c r="G161">
+        <v>86600</v>
+      </c>
+      <c r="H161">
+        <v>240</v>
+      </c>
+      <c r="J161">
+        <v>86600</v>
+      </c>
+      <c r="L161" t="s">
+        <v>20</v>
+      </c>
+      <c r="M161">
+        <v>4</v>
+      </c>
+      <c r="N161">
+        <v>10824</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>260</v>
+      </c>
+      <c r="B162" t="s">
+        <v>34</v>
+      </c>
+      <c r="C162">
+        <v>4210602</v>
+      </c>
+      <c r="D162" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F162" t="s">
+        <v>306</v>
+      </c>
+      <c r="G162">
+        <v>118500</v>
+      </c>
+      <c r="H162">
+        <v>330</v>
+      </c>
+      <c r="J162">
+        <v>118500</v>
+      </c>
+      <c r="L162" t="s">
+        <v>20</v>
+      </c>
+      <c r="M162">
+        <v>4</v>
+      </c>
+      <c r="N162">
+        <v>10849</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>260</v>
+      </c>
+      <c r="B163" t="s">
+        <v>34</v>
+      </c>
+      <c r="C163">
+        <v>4210602</v>
+      </c>
+      <c r="D163" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F163" t="s">
+        <v>307</v>
+      </c>
+      <c r="G163">
+        <v>86500</v>
+      </c>
+      <c r="H163">
+        <v>140</v>
+      </c>
+      <c r="J163">
+        <v>86500</v>
+      </c>
+      <c r="L163" t="s">
+        <v>20</v>
+      </c>
+      <c r="M163">
+        <v>4</v>
+      </c>
+      <c r="N163">
+        <v>10879</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>260</v>
+      </c>
+      <c r="B164" t="s">
+        <v>34</v>
+      </c>
+      <c r="C164">
+        <v>4210602</v>
+      </c>
+      <c r="D164" t="s">
+        <v>23</v>
+      </c>
+      <c r="E164" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F164" t="s">
+        <v>308</v>
+      </c>
+      <c r="G164">
+        <v>87400</v>
+      </c>
+      <c r="H164">
+        <v>230</v>
+      </c>
+      <c r="J164">
+        <v>87400</v>
+      </c>
+      <c r="L164" t="s">
+        <v>20</v>
+      </c>
+      <c r="M164">
+        <v>4</v>
+      </c>
+      <c r="N164">
+        <v>10911</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>260</v>
+      </c>
+      <c r="B165" t="s">
+        <v>34</v>
+      </c>
+      <c r="C165">
+        <v>4210602</v>
+      </c>
+      <c r="D165" t="s">
+        <v>23</v>
+      </c>
+      <c r="E165" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F165" t="s">
+        <v>309</v>
+      </c>
+      <c r="G165">
+        <v>82300</v>
+      </c>
+      <c r="H165">
+        <v>340</v>
+      </c>
+      <c r="J165">
+        <v>82300</v>
+      </c>
+      <c r="L165" t="s">
+        <v>20</v>
+      </c>
+      <c r="M165">
+        <v>4</v>
+      </c>
+      <c r="N165">
+        <v>10945</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>260</v>
+      </c>
+      <c r="B166" t="s">
+        <v>34</v>
+      </c>
+      <c r="C166">
+        <v>4210602</v>
+      </c>
+      <c r="D166" t="s">
+        <v>23</v>
+      </c>
+      <c r="E166" s="2">
+        <v>46252</v>
+      </c>
+      <c r="F166" t="s">
+        <v>310</v>
+      </c>
+      <c r="G166">
+        <v>42800</v>
+      </c>
+      <c r="H166">
+        <v>440</v>
+      </c>
+      <c r="J166">
+        <v>42800</v>
+      </c>
+      <c r="L166" t="s">
+        <v>20</v>
+      </c>
+      <c r="M166">
+        <v>4</v>
+      </c>
+      <c r="N166">
+        <v>10958</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>261</v>
+      </c>
+      <c r="B167" t="s">
+        <v>35</v>
+      </c>
+      <c r="C167">
+        <v>4210602</v>
+      </c>
+      <c r="D167" t="s">
+        <v>23</v>
+      </c>
+      <c r="E167" s="2">
+        <v>46235</v>
+      </c>
+      <c r="F167" t="s">
+        <v>67</v>
+      </c>
+      <c r="G167">
+        <v>75000</v>
+      </c>
+      <c r="H167" t="s">
+        <v>68</v>
+      </c>
+      <c r="J167">
+        <v>75000</v>
+      </c>
+      <c r="L167" t="s">
+        <v>20</v>
+      </c>
+      <c r="M167">
+        <v>4</v>
+      </c>
+      <c r="N167">
+        <v>10608</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>261</v>
+      </c>
+      <c r="B168" t="s">
+        <v>35</v>
+      </c>
+      <c r="C168">
+        <v>4210602</v>
+      </c>
+      <c r="D168" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F168" t="s">
+        <v>172</v>
+      </c>
+      <c r="G168">
+        <v>75000</v>
+      </c>
+      <c r="H168" t="s">
+        <v>77</v>
+      </c>
+      <c r="J168">
+        <v>75000</v>
+      </c>
+      <c r="L168" t="s">
+        <v>20</v>
+      </c>
+      <c r="M168">
+        <v>4</v>
+      </c>
+      <c r="N168">
+        <v>10661</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>261</v>
+      </c>
+      <c r="B169" t="s">
+        <v>35</v>
+      </c>
+      <c r="C169">
+        <v>4210602</v>
+      </c>
+      <c r="D169" t="s">
+        <v>23</v>
+      </c>
+      <c r="E169" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F169" t="s">
+        <v>173</v>
+      </c>
+      <c r="G169">
+        <v>75000</v>
+      </c>
+      <c r="H169" t="s">
+        <v>174</v>
+      </c>
+      <c r="J169">
+        <v>75000</v>
+      </c>
+      <c r="L169" t="s">
+        <v>20</v>
+      </c>
+      <c r="M169">
+        <v>4</v>
+      </c>
+      <c r="N169">
+        <v>10689</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>261</v>
+      </c>
+      <c r="B170" t="s">
+        <v>35</v>
+      </c>
+      <c r="C170">
+        <v>4210602</v>
+      </c>
+      <c r="D170" t="s">
+        <v>23</v>
+      </c>
+      <c r="E170" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F170" t="s">
+        <v>311</v>
+      </c>
+      <c r="G170">
+        <v>75000</v>
+      </c>
+      <c r="H170" t="s">
+        <v>312</v>
+      </c>
+      <c r="J170">
+        <v>75000</v>
+      </c>
+      <c r="L170" t="s">
+        <v>20</v>
+      </c>
+      <c r="M170">
+        <v>4</v>
+      </c>
+      <c r="N170">
+        <v>10718</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>261</v>
+      </c>
+      <c r="B171" t="s">
+        <v>35</v>
+      </c>
+      <c r="C171">
+        <v>4210602</v>
+      </c>
+      <c r="D171" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F171" t="s">
+        <v>175</v>
+      </c>
+      <c r="G171">
+        <v>75000</v>
+      </c>
+      <c r="H171" t="s">
+        <v>81</v>
+      </c>
+      <c r="J171">
+        <v>75000</v>
+      </c>
+      <c r="L171" t="s">
+        <v>20</v>
+      </c>
+      <c r="M171">
+        <v>4</v>
+      </c>
+      <c r="N171">
+        <v>10734</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>261</v>
+      </c>
+      <c r="B172" t="s">
+        <v>35</v>
+      </c>
+      <c r="C172">
+        <v>4210602</v>
+      </c>
+      <c r="D172" t="s">
+        <v>23</v>
+      </c>
+      <c r="E172" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F172" t="s">
+        <v>176</v>
+      </c>
+      <c r="G172">
+        <v>75000</v>
+      </c>
+      <c r="H172" t="s">
+        <v>68</v>
+      </c>
+      <c r="J172">
+        <v>75000</v>
+      </c>
+      <c r="L172" t="s">
+        <v>20</v>
+      </c>
+      <c r="M172">
+        <v>4</v>
+      </c>
+      <c r="N172">
+        <v>10758</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>261</v>
+      </c>
+      <c r="B173" t="s">
+        <v>35</v>
+      </c>
+      <c r="C173">
+        <v>4210602</v>
+      </c>
+      <c r="D173" t="s">
+        <v>23</v>
+      </c>
+      <c r="E173" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F173" t="s">
+        <v>313</v>
+      </c>
+      <c r="G173">
+        <v>75000</v>
+      </c>
+      <c r="H173" t="s">
+        <v>182</v>
+      </c>
+      <c r="J173">
+        <v>75000</v>
+      </c>
+      <c r="L173" t="s">
+        <v>20</v>
+      </c>
+      <c r="M173">
+        <v>4</v>
+      </c>
+      <c r="N173">
+        <v>10804</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>261</v>
+      </c>
+      <c r="B174" t="s">
+        <v>35</v>
+      </c>
+      <c r="C174">
+        <v>4210602</v>
+      </c>
+      <c r="D174" t="s">
+        <v>23</v>
+      </c>
+      <c r="E174" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F174" t="s">
+        <v>314</v>
+      </c>
+      <c r="G174">
+        <v>75000</v>
+      </c>
+      <c r="H174" t="s">
+        <v>36</v>
+      </c>
+      <c r="J174">
+        <v>75000</v>
+      </c>
+      <c r="L174" t="s">
+        <v>20</v>
+      </c>
+      <c r="M174">
+        <v>4</v>
+      </c>
+      <c r="N174">
+        <v>10839</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>261</v>
+      </c>
+      <c r="B175" t="s">
+        <v>35</v>
+      </c>
+      <c r="C175">
+        <v>4210602</v>
+      </c>
+      <c r="D175" t="s">
+        <v>23</v>
+      </c>
+      <c r="E175" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F175" t="s">
+        <v>315</v>
+      </c>
+      <c r="G175">
+        <v>75000</v>
+      </c>
+      <c r="H175" t="s">
+        <v>316</v>
+      </c>
+      <c r="J175">
+        <v>75000</v>
+      </c>
+      <c r="L175" t="s">
+        <v>20</v>
+      </c>
+      <c r="M175">
+        <v>4</v>
+      </c>
+      <c r="N175">
+        <v>10898</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>261</v>
+      </c>
+      <c r="B176" t="s">
+        <v>35</v>
+      </c>
+      <c r="C176">
+        <v>4210602</v>
+      </c>
+      <c r="D176" t="s">
+        <v>23</v>
+      </c>
+      <c r="E176" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F176" t="s">
+        <v>317</v>
+      </c>
+      <c r="G176">
+        <v>75000</v>
+      </c>
+      <c r="H176" t="s">
+        <v>318</v>
+      </c>
+      <c r="J176">
+        <v>75000</v>
+      </c>
+      <c r="L176" t="s">
+        <v>20</v>
+      </c>
+      <c r="M176">
+        <v>4</v>
+      </c>
+      <c r="N176">
+        <v>10917</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>262</v>
+      </c>
+      <c r="B177" t="s">
+        <v>37</v>
+      </c>
+      <c r="C177">
+        <v>4210602</v>
+      </c>
+      <c r="D177" t="s">
+        <v>23</v>
+      </c>
+      <c r="E177" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F177" t="s">
+        <v>69</v>
+      </c>
+      <c r="G177">
+        <v>195095</v>
+      </c>
+      <c r="H177" t="s">
+        <v>38</v>
+      </c>
+      <c r="J177">
+        <v>195095</v>
+      </c>
+      <c r="L177" t="s">
+        <v>20</v>
+      </c>
+      <c r="M177">
+        <v>4</v>
+      </c>
+      <c r="N177">
+        <v>10617</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>262</v>
+      </c>
+      <c r="B178" t="s">
+        <v>37</v>
+      </c>
+      <c r="C178">
+        <v>4210602</v>
+      </c>
+      <c r="D178" t="s">
+        <v>23</v>
+      </c>
+      <c r="E178" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F178" t="s">
+        <v>177</v>
+      </c>
+      <c r="G178">
+        <v>299858</v>
+      </c>
+      <c r="H178" t="s">
+        <v>178</v>
+      </c>
+      <c r="J178">
+        <v>299858</v>
+      </c>
+      <c r="L178" t="s">
+        <v>20</v>
+      </c>
+      <c r="M178">
+        <v>4</v>
+      </c>
+      <c r="N178">
+        <v>10663</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>262</v>
+      </c>
+      <c r="B179" t="s">
+        <v>37</v>
+      </c>
+      <c r="C179">
+        <v>4210602</v>
+      </c>
+      <c r="D179" t="s">
+        <v>23</v>
+      </c>
+      <c r="E179" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F179" t="s">
+        <v>179</v>
+      </c>
+      <c r="G179">
+        <v>199783</v>
+      </c>
+      <c r="H179" t="s">
+        <v>180</v>
+      </c>
+      <c r="J179">
+        <v>199783</v>
+      </c>
+      <c r="L179" t="s">
+        <v>20</v>
+      </c>
+      <c r="M179">
+        <v>4</v>
+      </c>
+      <c r="N179">
+        <v>10716</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>262</v>
+      </c>
+      <c r="B180" t="s">
+        <v>37</v>
+      </c>
+      <c r="C180">
+        <v>4210602</v>
+      </c>
+      <c r="D180" t="s">
+        <v>23</v>
+      </c>
+      <c r="E180" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F180" t="s">
+        <v>181</v>
+      </c>
+      <c r="G180">
+        <v>209985</v>
+      </c>
+      <c r="H180" t="s">
+        <v>182</v>
+      </c>
+      <c r="J180">
+        <v>209985</v>
+      </c>
+      <c r="L180" t="s">
+        <v>20</v>
+      </c>
+      <c r="M180">
+        <v>4</v>
+      </c>
+      <c r="N180">
+        <v>10732</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>262</v>
+      </c>
+      <c r="B181" t="s">
+        <v>37</v>
+      </c>
+      <c r="C181">
+        <v>4210602</v>
+      </c>
+      <c r="D181" t="s">
+        <v>23</v>
+      </c>
+      <c r="E181" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F181" t="s">
+        <v>183</v>
+      </c>
+      <c r="G181">
+        <v>192876</v>
+      </c>
+      <c r="H181" t="s">
+        <v>38</v>
+      </c>
+      <c r="J181">
+        <v>192876</v>
+      </c>
+      <c r="L181" t="s">
+        <v>20</v>
+      </c>
+      <c r="M181">
+        <v>4</v>
+      </c>
+      <c r="N181">
+        <v>10767</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>262</v>
+      </c>
+      <c r="B182" t="s">
+        <v>37</v>
+      </c>
+      <c r="C182">
+        <v>4210602</v>
+      </c>
+      <c r="D182" t="s">
+        <v>23</v>
+      </c>
+      <c r="E182" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F182" t="s">
+        <v>184</v>
+      </c>
+      <c r="G182">
+        <v>147748</v>
+      </c>
+      <c r="H182" t="s">
+        <v>38</v>
+      </c>
+      <c r="I182" t="s">
+        <v>185</v>
+      </c>
+      <c r="J182">
+        <v>147748</v>
+      </c>
+      <c r="L182" t="s">
+        <v>20</v>
+      </c>
+      <c r="M182">
+        <v>4</v>
+      </c>
+      <c r="N182">
+        <v>10767</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>262</v>
+      </c>
+      <c r="B183" t="s">
+        <v>37</v>
+      </c>
+      <c r="C183">
+        <v>4210602</v>
+      </c>
+      <c r="D183" t="s">
+        <v>23</v>
+      </c>
+      <c r="E183" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F183" t="s">
+        <v>319</v>
+      </c>
+      <c r="G183">
+        <v>274610</v>
+      </c>
+      <c r="H183" t="s">
+        <v>178</v>
+      </c>
+      <c r="J183">
+        <v>274610</v>
+      </c>
+      <c r="L183" t="s">
+        <v>20</v>
+      </c>
+      <c r="M183">
+        <v>4</v>
+      </c>
+      <c r="N183">
+        <v>10813</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>262</v>
+      </c>
+      <c r="B184" t="s">
+        <v>37</v>
+      </c>
+      <c r="C184">
+        <v>4210602</v>
+      </c>
+      <c r="D184" t="s">
+        <v>23</v>
+      </c>
+      <c r="E184" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F184" t="s">
+        <v>320</v>
+      </c>
+      <c r="G184">
+        <v>256183</v>
+      </c>
+      <c r="H184" t="s">
+        <v>180</v>
+      </c>
+      <c r="J184">
+        <v>256183</v>
+      </c>
+      <c r="L184" t="s">
+        <v>20</v>
+      </c>
+      <c r="M184">
+        <v>4</v>
+      </c>
+      <c r="N184">
+        <v>10863</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>262</v>
+      </c>
+      <c r="B185" t="s">
+        <v>37</v>
+      </c>
+      <c r="C185">
+        <v>4210602</v>
+      </c>
+      <c r="D185" t="s">
+        <v>23</v>
+      </c>
+      <c r="E185" s="2">
+        <v>46248</v>
+      </c>
+      <c r="F185" t="s">
+        <v>321</v>
+      </c>
+      <c r="G185">
+        <v>129998</v>
+      </c>
+      <c r="H185" t="s">
+        <v>182</v>
+      </c>
+      <c r="J185">
+        <v>129998</v>
+      </c>
+      <c r="L185" t="s">
+        <v>20</v>
+      </c>
+      <c r="M185">
+        <v>4</v>
+      </c>
+      <c r="N185">
+        <v>10889</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>262</v>
+      </c>
+      <c r="B186" t="s">
+        <v>37</v>
+      </c>
+      <c r="C186">
+        <v>4210602</v>
+      </c>
+      <c r="D186" t="s">
+        <v>23</v>
+      </c>
+      <c r="E186" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F186" t="s">
+        <v>322</v>
+      </c>
+      <c r="G186">
+        <v>148135</v>
+      </c>
+      <c r="H186" t="s">
+        <v>38</v>
+      </c>
+      <c r="J186">
+        <v>148135</v>
+      </c>
+      <c r="L186" t="s">
+        <v>20</v>
+      </c>
+      <c r="M186">
+        <v>4</v>
+      </c>
+      <c r="N186">
+        <v>10925</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>312</v>
+      </c>
+      <c r="B187" t="s">
+        <v>323</v>
+      </c>
+      <c r="C187">
+        <v>4211201</v>
+      </c>
+      <c r="D187" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F187" t="s">
+        <v>324</v>
+      </c>
+      <c r="G187">
+        <v>79999.199999999997</v>
+      </c>
+      <c r="H187" t="s">
+        <v>312</v>
+      </c>
+      <c r="J187">
+        <v>66115.039999999994</v>
+      </c>
+      <c r="K187">
+        <v>13884.16</v>
+      </c>
+      <c r="L187" t="s">
+        <v>14</v>
+      </c>
+      <c r="M187">
+        <v>5</v>
+      </c>
+      <c r="N187">
+        <v>10865</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>321</v>
+      </c>
+      <c r="B188" t="s">
+        <v>325</v>
+      </c>
+      <c r="C188">
+        <v>4210803</v>
+      </c>
+      <c r="D188" t="s">
+        <v>326</v>
+      </c>
+      <c r="E188" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F188" t="s">
+        <v>327</v>
+      </c>
+      <c r="G188">
+        <v>271342.5</v>
+      </c>
+      <c r="I188" t="s">
+        <v>328</v>
+      </c>
+      <c r="J188">
+        <v>224250</v>
+      </c>
+      <c r="K188">
+        <v>47092.5</v>
+      </c>
+      <c r="L188" t="s">
+        <v>102</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>348</v>
+      </c>
+      <c r="B189" t="s">
+        <v>39</v>
+      </c>
+      <c r="C189">
+        <v>4210701</v>
+      </c>
+      <c r="D189" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F189" t="s">
+        <v>70</v>
+      </c>
+      <c r="G189">
+        <v>317947.7</v>
+      </c>
+      <c r="I189" t="s">
+        <v>71</v>
+      </c>
+      <c r="J189">
+        <v>262766.7</v>
+      </c>
+      <c r="K189">
+        <v>55181</v>
+      </c>
+      <c r="L189" t="s">
+        <v>14</v>
+      </c>
+      <c r="M189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>355</v>
+      </c>
+      <c r="B190" t="s">
+        <v>40</v>
+      </c>
+      <c r="C190">
+        <v>4210206</v>
+      </c>
+      <c r="D190" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F190" t="s">
+        <v>72</v>
+      </c>
+      <c r="G190">
+        <v>32000</v>
+      </c>
+      <c r="I190" t="s">
+        <v>42</v>
+      </c>
+      <c r="J190">
+        <v>32000</v>
+      </c>
+      <c r="L190" t="s">
+        <v>22</v>
+      </c>
+      <c r="M190">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>355</v>
+      </c>
+      <c r="B191" t="s">
+        <v>40</v>
+      </c>
+      <c r="C191">
+        <v>4210206</v>
+      </c>
+      <c r="D191" t="s">
+        <v>41</v>
+      </c>
+      <c r="E191" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F191" t="s">
+        <v>329</v>
+      </c>
+      <c r="G191">
+        <v>32000</v>
+      </c>
+      <c r="I191" t="s">
+        <v>42</v>
+      </c>
+      <c r="J191">
+        <v>32000</v>
+      </c>
+      <c r="L191" t="s">
+        <v>22</v>
+      </c>
+      <c r="M191">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>355</v>
+      </c>
+      <c r="B192" t="s">
+        <v>40</v>
+      </c>
+      <c r="C192">
+        <v>4210206</v>
+      </c>
+      <c r="D192" t="s">
+        <v>41</v>
+      </c>
+      <c r="E192" s="2">
+        <v>46239</v>
+      </c>
+      <c r="F192" t="s">
+        <v>186</v>
+      </c>
+      <c r="G192">
+        <v>21500</v>
+      </c>
+      <c r="I192" t="s">
+        <v>187</v>
+      </c>
+      <c r="J192">
+        <v>21500</v>
+      </c>
+      <c r="L192" t="s">
+        <v>22</v>
+      </c>
+      <c r="M192">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>355</v>
+      </c>
+      <c r="B193" t="s">
+        <v>40</v>
+      </c>
+      <c r="C193">
+        <v>4210206</v>
+      </c>
+      <c r="D193" t="s">
+        <v>41</v>
+      </c>
+      <c r="E193" s="2">
+        <v>46240</v>
+      </c>
+      <c r="F193" t="s">
+        <v>188</v>
+      </c>
+      <c r="G193">
+        <v>31000</v>
+      </c>
+      <c r="I193" t="s">
+        <v>42</v>
+      </c>
+      <c r="J193">
+        <v>31000</v>
+      </c>
+      <c r="L193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M193">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>355</v>
+      </c>
+      <c r="B194" t="s">
+        <v>40</v>
+      </c>
+      <c r="C194">
+        <v>4210206</v>
+      </c>
+      <c r="D194" t="s">
+        <v>41</v>
+      </c>
+      <c r="E194" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F194" t="s">
+        <v>189</v>
+      </c>
+      <c r="G194">
+        <v>31500</v>
+      </c>
+      <c r="I194" t="s">
+        <v>190</v>
+      </c>
+      <c r="J194">
+        <v>31500</v>
+      </c>
+      <c r="L194" t="s">
+        <v>22</v>
+      </c>
+      <c r="M194">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>355</v>
+      </c>
+      <c r="B195" t="s">
+        <v>40</v>
+      </c>
+      <c r="C195">
+        <v>4210206</v>
+      </c>
+      <c r="D195" t="s">
+        <v>41</v>
+      </c>
+      <c r="E195" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F195" t="s">
+        <v>330</v>
+      </c>
+      <c r="G195">
+        <v>23000</v>
+      </c>
+      <c r="I195" t="s">
+        <v>331</v>
+      </c>
+      <c r="J195">
+        <v>23000</v>
+      </c>
+      <c r="L195" t="s">
+        <v>22</v>
+      </c>
+      <c r="M195">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>355</v>
+      </c>
+      <c r="B196" t="s">
+        <v>40</v>
+      </c>
+      <c r="C196">
+        <v>4210206</v>
+      </c>
+      <c r="D196" t="s">
+        <v>41</v>
+      </c>
+      <c r="E196" s="2">
+        <v>46245</v>
+      </c>
+      <c r="F196" t="s">
+        <v>332</v>
+      </c>
+      <c r="G196">
+        <v>60000</v>
+      </c>
+      <c r="I196" t="s">
+        <v>333</v>
+      </c>
+      <c r="J196">
+        <v>60000</v>
+      </c>
+      <c r="L196" t="s">
+        <v>22</v>
+      </c>
+      <c r="M196">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>355</v>
+      </c>
+      <c r="B197" t="s">
+        <v>40</v>
+      </c>
+      <c r="C197">
+        <v>4210206</v>
+      </c>
+      <c r="D197" t="s">
+        <v>41</v>
+      </c>
+      <c r="E197" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F197" t="s">
+        <v>334</v>
+      </c>
+      <c r="G197">
+        <v>31000</v>
+      </c>
+      <c r="I197" t="s">
+        <v>42</v>
+      </c>
+      <c r="J197">
+        <v>31000</v>
+      </c>
+      <c r="L197" t="s">
+        <v>22</v>
+      </c>
+      <c r="M197">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>355</v>
+      </c>
+      <c r="B198" t="s">
+        <v>40</v>
+      </c>
+      <c r="C198">
+        <v>4210206</v>
+      </c>
+      <c r="D198" t="s">
+        <v>41</v>
+      </c>
+      <c r="E198" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F198" t="s">
+        <v>335</v>
+      </c>
+      <c r="G198">
+        <v>32000</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J198">
+        <v>32000</v>
+      </c>
+      <c r="L198" t="s">
+        <v>22</v>
+      </c>
+      <c r="M198">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>355</v>
+      </c>
+      <c r="B199" t="s">
+        <v>40</v>
+      </c>
+      <c r="C199">
+        <v>4210206</v>
+      </c>
+      <c r="D199" t="s">
+        <v>41</v>
+      </c>
+      <c r="E199" s="2">
+        <v>46254</v>
+      </c>
+      <c r="F199" t="s">
+        <v>337</v>
+      </c>
+      <c r="G199">
+        <v>35000</v>
+      </c>
+      <c r="I199" t="s">
+        <v>336</v>
+      </c>
+      <c r="J199">
+        <v>35000</v>
+      </c>
+      <c r="L199" t="s">
+        <v>22</v>
+      </c>
+      <c r="M199">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>382</v>
+      </c>
+      <c r="B200" t="s">
+        <v>191</v>
+      </c>
+      <c r="C200">
+        <v>4210101</v>
+      </c>
+      <c r="D200" t="s">
+        <v>192</v>
+      </c>
+      <c r="E200" s="2">
+        <v>46242</v>
+      </c>
+      <c r="F200" t="s">
+        <v>193</v>
+      </c>
+      <c r="G200">
+        <v>150000</v>
+      </c>
+      <c r="H200">
+        <v>331</v>
+      </c>
+      <c r="J200">
+        <v>150000</v>
+      </c>
+      <c r="L200" t="s">
+        <v>20</v>
+      </c>
+      <c r="M200">
+        <v>4</v>
+      </c>
+      <c r="N200">
+        <v>10780</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>382</v>
+      </c>
+      <c r="B201" t="s">
+        <v>191</v>
+      </c>
+      <c r="C201">
+        <v>4210101</v>
+      </c>
+      <c r="D201" t="s">
+        <v>192</v>
+      </c>
+      <c r="E201" s="2">
+        <v>46249</v>
+      </c>
+      <c r="F201" t="s">
+        <v>338</v>
+      </c>
+      <c r="G201">
+        <v>150000</v>
+      </c>
+      <c r="H201">
+        <v>331</v>
+      </c>
+      <c r="I201" t="s">
+        <v>339</v>
+      </c>
+      <c r="J201">
+        <v>150000</v>
+      </c>
+      <c r="L201" t="s">
+        <v>20</v>
+      </c>
+      <c r="M201">
+        <v>4</v>
+      </c>
+      <c r="N201">
+        <v>10937</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A202">
         <v>396</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B202" t="s">
         <v>43</v>
       </c>
-      <c r="C106">
+      <c r="C202">
         <v>4210301</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D202" t="s">
         <v>44</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E202" s="2">
+        <v>46237</v>
+      </c>
+      <c r="F202" t="s">
+        <v>73</v>
+      </c>
+      <c r="G202">
+        <v>209400</v>
+      </c>
+      <c r="I202" t="s">
+        <v>27</v>
+      </c>
+      <c r="J202">
+        <v>209400</v>
+      </c>
+      <c r="L202" t="s">
+        <v>22</v>
+      </c>
+      <c r="M202">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>396</v>
+      </c>
+      <c r="B203" t="s">
+        <v>43</v>
+      </c>
+      <c r="C203">
+        <v>4210301</v>
+      </c>
+      <c r="D203" t="s">
+        <v>44</v>
+      </c>
+      <c r="E203" s="2">
+        <v>46238</v>
+      </c>
+      <c r="F203" t="s">
+        <v>74</v>
+      </c>
+      <c r="G203">
+        <v>60000</v>
+      </c>
+      <c r="I203" t="s">
+        <v>45</v>
+      </c>
+      <c r="J203">
+        <v>60000</v>
+      </c>
+      <c r="L203" t="s">
+        <v>22</v>
+      </c>
+      <c r="M203">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>396</v>
+      </c>
+      <c r="B204" t="s">
+        <v>43</v>
+      </c>
+      <c r="C204">
+        <v>4210301</v>
+      </c>
+      <c r="D204" t="s">
+        <v>44</v>
+      </c>
+      <c r="E204" s="2">
         <v>46241</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F204" t="s">
+        <v>194</v>
+      </c>
+      <c r="G204">
+        <v>2815200</v>
+      </c>
+      <c r="I204" t="s">
+        <v>195</v>
+      </c>
+      <c r="J204">
+        <v>2815200</v>
+      </c>
+      <c r="L204" t="s">
+        <v>22</v>
+      </c>
+      <c r="M204">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>396</v>
+      </c>
+      <c r="B205" t="s">
+        <v>43</v>
+      </c>
+      <c r="C205">
+        <v>4210301</v>
+      </c>
+      <c r="D205" t="s">
+        <v>44</v>
+      </c>
+      <c r="E205" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F205" t="s">
+        <v>196</v>
+      </c>
+      <c r="G205">
+        <v>6000</v>
+      </c>
+      <c r="I205" t="s">
+        <v>197</v>
+      </c>
+      <c r="J205">
+        <v>6000</v>
+      </c>
+      <c r="L205" t="s">
+        <v>22</v>
+      </c>
+      <c r="M205">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>396</v>
+      </c>
+      <c r="B206" t="s">
+        <v>43</v>
+      </c>
+      <c r="C206">
+        <v>4210301</v>
+      </c>
+      <c r="D206" t="s">
+        <v>44</v>
+      </c>
+      <c r="E206" s="2">
+        <v>46241</v>
+      </c>
+      <c r="F206" t="s">
         <v>198</v>
       </c>
-      <c r="G106">
+      <c r="G206">
         <v>74500</v>
       </c>
-      <c r="I106" t="s">
+      <c r="I206" t="s">
         <v>199</v>
       </c>
-      <c r="J106">
+      <c r="J206">
         <v>74500</v>
       </c>
-      <c r="L106" t="s">
+      <c r="L206" t="s">
         <v>22</v>
       </c>
-      <c r="M106">
+      <c r="M206">
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E107" s="2"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E108" s="2"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E109" s="2"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E110" s="2"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E111" s="2"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E112" s="2"/>
-    </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E115" s="2"/>
-    </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E116" s="2"/>
-    </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E118" s="2"/>
-    </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E119" s="2"/>
-    </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E120" s="2"/>
-    </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E121" s="2"/>
-    </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E126" s="2"/>
-    </row>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E127" s="2"/>
-    </row>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E128" s="2"/>
-    </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E129" s="2"/>
-    </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E134" s="2"/>
-    </row>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E135" s="2"/>
-    </row>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E136" s="2"/>
-    </row>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E137" s="2"/>
-    </row>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E138" s="2"/>
-    </row>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E139" s="2"/>
-    </row>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E140" s="2"/>
-    </row>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E141" s="2"/>
-    </row>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E142" s="2"/>
-    </row>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E143" s="2"/>
-    </row>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E144" s="2"/>
-    </row>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E145" s="2"/>
-    </row>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E146" s="2"/>
-    </row>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E147" s="2"/>
-    </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E148" s="2"/>
-    </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E149" s="2"/>
-    </row>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E150" s="2"/>
-    </row>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E151" s="2"/>
-    </row>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E152" s="2"/>
-    </row>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E153" s="2"/>
-    </row>
-    <row r="154" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E154" s="2"/>
-    </row>
-    <row r="155" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E155" s="2"/>
-    </row>
-    <row r="156" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E156" s="2"/>
-    </row>
-    <row r="157" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E157" s="2"/>
-    </row>
-    <row r="158" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E158" s="2"/>
-    </row>
-    <row r="159" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E159" s="2"/>
-    </row>
-    <row r="160" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E160" s="2"/>
-    </row>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E161" s="2"/>
-    </row>
-    <row r="162" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E162" s="2"/>
-    </row>
-    <row r="163" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E163" s="2"/>
-    </row>
-    <row r="164" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E164" s="2"/>
-    </row>
-    <row r="165" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E165" s="2"/>
-    </row>
-    <row r="166" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E166" s="2"/>
-    </row>
-    <row r="167" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E167" s="2"/>
-    </row>
-    <row r="168" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E168" s="2"/>
-    </row>
-    <row r="169" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E169" s="2"/>
-    </row>
-    <row r="170" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E170" s="2"/>
-    </row>
-    <row r="171" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E171" s="2"/>
-    </row>
-    <row r="172" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E172" s="2"/>
-    </row>
-    <row r="173" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E173" s="2"/>
-    </row>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E174" s="2"/>
-    </row>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E175" s="2"/>
-    </row>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E176" s="2"/>
-    </row>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E177" s="2"/>
-    </row>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E178" s="2"/>
-    </row>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E179" s="2"/>
-    </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E180" s="2"/>
-    </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E181" s="2"/>
-    </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E182" s="2"/>
-    </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E183" s="2"/>
-    </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E184" s="2"/>
-    </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E185" s="2"/>
-    </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E186" s="2"/>
-    </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E187" s="2"/>
-    </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E188" s="2"/>
-    </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E189" s="2"/>
-    </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E190" s="2"/>
-    </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E191" s="2"/>
-    </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E192" s="2"/>
-    </row>
-    <row r="193" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E193" s="2"/>
-    </row>
-    <row r="194" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E194" s="2"/>
-    </row>
-    <row r="195" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E195" s="2"/>
-    </row>
-    <row r="196" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E196" s="2"/>
-    </row>
-    <row r="197" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E197" s="2"/>
-    </row>
-    <row r="198" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E198" s="2"/>
-      <c r="I198" s="1"/>
-    </row>
-    <row r="199" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E199" s="2"/>
-    </row>
-    <row r="200" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E200" s="2"/>
-    </row>
-    <row r="201" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E201" s="2"/>
-    </row>
-    <row r="202" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E202" s="2"/>
-    </row>
-    <row r="203" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E203" s="2"/>
-    </row>
-    <row r="204" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E204" s="2"/>
-    </row>
-    <row r="205" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E205" s="2"/>
-    </row>
-    <row r="206" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E206" s="2"/>
-    </row>
-    <row r="207" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E207" s="2"/>
-    </row>
-    <row r="208" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E208" s="2"/>
-    </row>
-    <row r="209" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E209" s="2"/>
-    </row>
-    <row r="210" spans="5:9" x14ac:dyDescent="0.25">
-      <c r="E210" s="2"/>
-    </row>
-    <row r="211" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>396</v>
+      </c>
+      <c r="B207" t="s">
+        <v>43</v>
+      </c>
+      <c r="C207">
+        <v>4210301</v>
+      </c>
+      <c r="D207" t="s">
+        <v>44</v>
+      </c>
+      <c r="E207" s="2">
+        <v>46246</v>
+      </c>
+      <c r="F207" t="s">
+        <v>340</v>
+      </c>
+      <c r="G207">
+        <v>109200</v>
+      </c>
+      <c r="I207" t="s">
+        <v>25</v>
+      </c>
+      <c r="J207">
+        <v>109200</v>
+      </c>
+      <c r="L207" t="s">
+        <v>22</v>
+      </c>
+      <c r="M207">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>396</v>
+      </c>
+      <c r="B208" t="s">
+        <v>43</v>
+      </c>
+      <c r="C208">
+        <v>4210301</v>
+      </c>
+      <c r="D208" t="s">
+        <v>44</v>
+      </c>
+      <c r="E208" s="2">
+        <v>46247</v>
+      </c>
+      <c r="F208" t="s">
+        <v>341</v>
+      </c>
+      <c r="G208">
+        <v>50000</v>
+      </c>
+      <c r="I208" t="s">
+        <v>45</v>
+      </c>
+      <c r="J208">
+        <v>50000</v>
+      </c>
+      <c r="L208" t="s">
+        <v>22</v>
+      </c>
+      <c r="M208">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>396</v>
+      </c>
+      <c r="B209" t="s">
+        <v>43</v>
+      </c>
+      <c r="C209">
+        <v>4210301</v>
+      </c>
+      <c r="D209" t="s">
+        <v>44</v>
+      </c>
+      <c r="E209" s="2">
+        <v>46252</v>
+      </c>
+      <c r="F209" t="s">
+        <v>342</v>
+      </c>
+      <c r="G209">
+        <v>50000</v>
+      </c>
+      <c r="I209" t="s">
+        <v>45</v>
+      </c>
+      <c r="J209">
+        <v>50000</v>
+      </c>
+      <c r="L209" t="s">
+        <v>22</v>
+      </c>
+      <c r="M209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>396</v>
+      </c>
+      <c r="B210" t="s">
+        <v>43</v>
+      </c>
+      <c r="C210">
+        <v>4210301</v>
+      </c>
+      <c r="D210" t="s">
+        <v>44</v>
+      </c>
+      <c r="E210" s="2">
+        <v>46253</v>
+      </c>
+      <c r="F210" t="s">
+        <v>343</v>
+      </c>
+      <c r="G210">
+        <v>23500</v>
+      </c>
+      <c r="I210" t="s">
+        <v>344</v>
+      </c>
+      <c r="J210">
+        <v>23500</v>
+      </c>
+      <c r="L210" t="s">
+        <v>22</v>
+      </c>
+      <c r="M210">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E211" s="2"/>
     </row>
-    <row r="212" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E212" s="2"/>
     </row>
-    <row r="213" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E213" s="2"/>
     </row>
-    <row r="214" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E214" s="2"/>
     </row>
-    <row r="215" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E215" s="2"/>
     </row>
-    <row r="216" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E216" s="2"/>
     </row>
-    <row r="217" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E217" s="2"/>
       <c r="I217" s="1"/>
     </row>
-    <row r="218" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E218" s="2"/>
       <c r="I218" s="1"/>
     </row>
-    <row r="219" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E219" s="2"/>
     </row>
-    <row r="220" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E220" s="2"/>
     </row>
-    <row r="221" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E221" s="2"/>
     </row>
-    <row r="222" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E222" s="2"/>
     </row>
-    <row r="223" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E223" s="2"/>
     </row>
-    <row r="224" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E224" s="2"/>
       <c r="I224" s="1"/>
     </row>
